--- a/tame_output/ON/bt/strategyON_20240814.xlsx
+++ b/tame_output/ON/bt/strategyON_20240814.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>15.7%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>77.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.9%</t>
+          <t>-78.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>124.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.2%</t>
+          <t>-47.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.3%</t>
+          <t>428.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-32.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-244.1%</t>
+          <t>-304.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-162.9%</t>
+          <t>-159.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>82.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>1.6%</t>
         </is>
       </c>
     </row>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191732</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.37443904309411</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.44775050131761</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737164</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341307</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.501052558539458</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.490059241608598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770576</v>
+        <v>3.676841549770575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615279</v>
+        <v>3.685161381615278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646213</v>
+        <v>3.710935533646212</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611564</v>
+        <v>3.768951674611563</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955324</v>
+        <v>3.728577929955323</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.747702660232408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436225</v>
+        <v>3.766317079436224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311945</v>
+        <v>3.784684521311944</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082935409724</v>
+        <v>3.800829354097239</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017767</v>
+        <v>3.789311112017766</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839721</v>
+        <v>3.83325274783972</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388723</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626468</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.787330429291809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.78471879410595</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960983</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607641</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987899</v>
+        <v>3.770422583987897</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409203</v>
+        <v>3.723566229409201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.782922533493417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722814</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792043</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919903</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057522</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.82635497427918</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011494</v>
+        <v>3.835957987011493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392981</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632777</v>
+        <v>3.773765222632775</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883069</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.798814771074777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242289</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367679</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.82232699787996</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.848616626502332</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675933</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.845047386496257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.7358392229421</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.743220196003596</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.7109067314177</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.75357116580319</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.923615119189145</v>
+        <v>-4.125344377738771</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.193264742881066</v>
+        <v>1.112573039461215</v>
       </c>
       <c r="F1955" t="n">
         <v>0.6794960294619854</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.96870736402269</v>
+        <v>-4.170436622572317</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.175911236709561</v>
+        <v>1.09521953328971</v>
       </c>
       <c r="F1956" t="n">
         <v>0.6175999862925956</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.789331942783923</v>
+        <v>-3.991061201333549</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.241448380511482</v>
+        <v>1.160756677091632</v>
       </c>
       <c r="F1957" t="n">
         <v>0.7743767444633143</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.834346156304529</v>
+        <v>-4.036075414854155</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.20425015043483</v>
+        <v>1.123558447014979</v>
       </c>
       <c r="F1958" t="n">
         <v>0.7440278491487097</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.101350666576964</v>
+        <v>-4.30307992512659</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.103139908664801</v>
+        <v>1.022448205244951</v>
       </c>
       <c r="F1959" t="n">
         <v>0.5496648111057612</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.202548448014137</v>
+        <v>-4.404277706563763</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.061864717986433</v>
+        <v>0.9811730145665831</v>
       </c>
       <c r="F1960" t="n">
         <v>0.481255997560442</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815454</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.196037481399824</v>
+        <v>-4.39776673994945</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.062069066186475</v>
+        <v>0.9813773627666249</v>
       </c>
       <c r="F1961" t="n">
         <v>0.481255997560442</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.176999353692527</v>
+        <v>-4.378728612242153</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.066209036477639</v>
+        <v>0.9855173330577889</v>
       </c>
       <c r="F1962" t="n">
         <v>0.4230723862292474</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.229515155967348</v>
+        <v>-4.431244414516973</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.164497117201901</v>
+        <v>1.083805413782051</v>
       </c>
       <c r="F1963" t="n">
         <v>0.4230723862292474</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067861</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.243381917301265</v>
+        <v>-4.445111175850891</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.159783741654468</v>
+        <v>1.079092038234617</v>
       </c>
       <c r="F1964" t="n">
         <v>0.3852144694954245</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789118</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.198577745761336</v>
+        <v>-4.400307004310961</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.183713940667366</v>
+        <v>1.103022237247515</v>
       </c>
       <c r="F1965" t="n">
         <v>0.3852144694954245</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.050834775526333</v>
+        <v>-4.252564034075959</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.140761350038566</v>
+        <v>1.060069646618716</v>
       </c>
       <c r="F1966" t="n">
         <v>0.5530218267303076</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181168</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.134655996801031</v>
+        <v>-4.336385255350657</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.110026483060168</v>
+        <v>1.029334779640317</v>
       </c>
       <c r="F1967" t="n">
         <v>0.5530218267303076</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.128503290748247</v>
+        <v>-4.330232549297873</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.11314991387294</v>
+        <v>1.032458210453089</v>
       </c>
       <c r="F1968" t="n">
         <v>0.5591745327830919</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.145312588898749</v>
+        <v>-4.347041847448375</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.105506671352849</v>
+        <v>1.024814967932999</v>
       </c>
       <c r="F1969" t="n">
         <v>0.5423652346325902</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798422</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.083014590122627</v>
+        <v>-4.284743848672252</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.196761424660119</v>
+        <v>1.116069721240269</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5876594989070323</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.881224392457469</v>
+        <v>-4.082953651007094</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.079769505440309</v>
+        <v>0.9990778020204591</v>
       </c>
       <c r="F1971" t="n">
         <v>0.7856776910761867</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.932111105143663</v>
+        <v>-4.133840363693289</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.129705052688007</v>
+        <v>1.049013349268156</v>
       </c>
       <c r="F1972" t="n">
         <v>0.7347909783899922</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.845500362493856</v>
+        <v>-4.047229621043482</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.178977085863973</v>
+        <v>1.098285382444123</v>
       </c>
       <c r="F1973" t="n">
         <v>0.8134167095951504</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489384</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.905709660499141</v>
+        <v>-4.107438919048767</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.153429347486531</v>
+        <v>1.07273764406668</v>
       </c>
       <c r="F1974" t="n">
         <v>0.7532074115898659</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.829287614067214</v>
+        <v>-4.03101687261684</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.18248978409923</v>
+        <v>1.10179808067938</v>
       </c>
       <c r="F1975" t="n">
         <v>0.7532074115898659</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316248</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.784914482428645</v>
+        <v>-3.986643740978272</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.200101904190094</v>
+        <v>1.119410200770243</v>
       </c>
       <c r="F1976" t="n">
         <v>0.7975805432284345</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.80739483328753</v>
+        <v>-4.009124091837156</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.185503557985131</v>
+        <v>1.10481185456528</v>
       </c>
       <c r="F1977" t="n">
         <v>0.7975805432284345</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.759739102726474</v>
+        <v>-3.961468361276101</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.210947607237358</v>
+        <v>1.130255903817507</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8452362737894902</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.659220944227719</v>
+        <v>-3.860950202777346</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.256047244011584</v>
+        <v>1.175355540591734</v>
       </c>
       <c r="F1979" t="n">
         <v>0.9457544322882447</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.643315614795367</v>
+        <v>-3.845044873344993</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.249164048260397</v>
+        <v>1.168472344840547</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8666417715790058</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932768</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.598477213186969</v>
+        <v>-3.800206471736595</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.271197111514385</v>
+        <v>1.190505408094535</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8711852045238753</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.617975669428977</v>
+        <v>-3.819704927978604</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.26755866864866</v>
+        <v>1.18686696522881</v>
       </c>
       <c r="F1982" t="n">
         <v>0.823100563243971</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.573772832343077</v>
+        <v>-3.775502090892703</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.291119406010857</v>
+        <v>1.210427702591007</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8673034003298714</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.581332498180124</v>
+        <v>-3.78306175672975</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.286505540145286</v>
+        <v>1.205813836725436</v>
       </c>
       <c r="F1984" t="n">
         <v>0.9221068043396907</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.423041080640851</v>
+        <v>-3.624770339190478</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.401069872344035</v>
+        <v>1.320378168924184</v>
       </c>
       <c r="F1985" t="n">
         <v>0.9221068043396907</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321022</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.215399077006375</v>
+        <v>-3.417128335556002</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.482567378392078</v>
+        <v>1.401875674972228</v>
       </c>
       <c r="F1986" t="n">
         <v>1.129748807974167</v>
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475138</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.196416584663209</v>
+        <v>-3.366096242833474</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.485108603567615</v>
+        <v>1.417236740299509</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.148731300317334</v>
+        <v>1.180780900696695</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.453270441937046</v>
+        <v>3.472500202164663</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404853</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.131192403536003</v>
+        <v>-3.300872061706268</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.528385680111202</v>
+        <v>1.460513816843096</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.213955481444539</v>
+        <v>1.246005081823901</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.509592354706074</v>
+        <v>3.528822114933691</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882558</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.09376538346487</v>
+        <v>-3.263445041635134</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.539317460438936</v>
+        <v>1.47144559717083</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.219207019473721</v>
+        <v>1.251256619853082</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.508704249822864</v>
+        <v>3.527934010050481</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992661</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.113877039499578</v>
+        <v>-3.283556697669842</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.532529590356293</v>
+        <v>1.464657727088187</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.23023436447114</v>
+        <v>1.262283964850502</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.516577449152555</v>
+        <v>3.535807209380172</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636287</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.060132225072373</v>
+        <v>-3.229811883242637</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.714585287148386</v>
+        <v>1.64671342388028</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.240297673911602</v>
+        <v>1.272347274290964</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.683173205838044</v>
+        <v>3.702402966065661</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957626</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.98534996404736</v>
+        <v>-3.155029622217625</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.864611100776208</v>
+        <v>1.796739237508102</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.315079934936615</v>
+        <v>1.347129535315976</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.848155471670868</v>
+        <v>3.867385231898485</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998756</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.959265879783552</v>
+        <v>-3.128945537953817</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.86675271049559</v>
+        <v>1.798880847227484</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.315079934936615</v>
+        <v>1.347129535315976</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.839863447684727</v>
+        <v>3.859093207912344</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896929</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.871387966674432</v>
+        <v>-3.041067624844696</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.900097071323018</v>
+        <v>1.832225208054912</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.431005577359966</v>
+        <v>1.463055177739327</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.907612028722518</v>
+        <v>3.926841788950134</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959857</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.862495505281148</v>
+        <v>-3.032175163451413</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.921208461607122</v>
+        <v>1.853336598339017</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.431005577359966</v>
+        <v>1.463055177739327</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.925166434449308</v>
+        <v>3.944396194676925</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.030971622251026</v>
+        <v>-3.200651280421291</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.845673062223755</v>
+        <v>1.777801198955649</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.403057741643385</v>
+        <v>1.435107342022747</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.900252780423944</v>
+        <v>3.919482540651561</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.584715429621586</v>
+        <v>-2.754395087791851</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.005445236463393</v>
+        <v>1.937573373195288</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.308339071973752</v>
+        <v>1.340388672353114</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.824691275810026</v>
+        <v>3.843921036037643</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632637</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.561994325938434</v>
+        <v>-2.731673984108698</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.005197700433559</v>
+        <v>1.937325837165453</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.308339071973752</v>
+        <v>1.340388672353114</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.815355298306931</v>
+        <v>3.834585058534548</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.691196139232476</v>
+        <v>-2.860875797402741</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.112423100967111</v>
+        <v>2.044551237699005</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.17913725867971</v>
+        <v>1.211186859059072</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.896740336181675</v>
+        <v>3.915970096409292</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.845977146010732</v>
+        <v>-3.015656804180996</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.087588520749455</v>
+        <v>2.019716657481349</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.145769584625234</v>
+        <v>1.177819185004596</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.913797554242636</v>
+        <v>3.933027314470253</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799964</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.838922455795558</v>
+        <v>-3.008602113965823</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.087085752825069</v>
+        <v>2.019213889556964</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.152824274840408</v>
+        <v>1.184873875219769</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.914705724361285</v>
+        <v>3.933935484588902</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.81197123146907</v>
+        <v>-2.981650889639335</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.107872396200406</v>
+        <v>2.040000532932301</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.167704620868127</v>
+        <v>1.199754221247489</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.933640085622658</v>
+        <v>3.952869845850275</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.947924239525387</v>
+        <v>-3.117603897695651</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.237594325122839</v>
+        <v>2.169722461854734</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.167704620868127</v>
+        <v>1.199754221247489</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.117743217767618</v>
+        <v>4.136972977995235</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714426</v>
+        <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.970332357330259</v>
+        <v>-3.140012015500523</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.220747772903884</v>
+        <v>2.152875909635778</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.167704620868127</v>
+        <v>1.199754221247489</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.109859912670611</v>
+        <v>4.129089672898228</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.998556592907859</v>
+        <v>-3.168236251078123</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.211512078222481</v>
+        <v>2.143640214954375</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.185681373319436</v>
+        <v>1.217730973698797</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.122699963691034</v>
+        <v>4.141929723918651</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.007997518796389</v>
+        <v>-3.177677176966653</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.263989425588917</v>
+        <v>2.19611756232081</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.308108490862827</v>
+        <v>1.340158091242189</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.252409951938915</v>
+        <v>4.271639712166532</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321635</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.06027112613203</v>
+        <v>-3.229950784302295</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.245971077199961</v>
+        <v>2.178099213931855</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.255834883527186</v>
+        <v>1.287884483906547</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.223936882082832</v>
+        <v>4.243166642310449</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347704</v>
+        <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.136601103732936</v>
+        <v>-3.306280761903201</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.213550899053374</v>
+        <v>2.145679035785268</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.255834883527186</v>
+        <v>1.287884483906547</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.222048694976607</v>
+        <v>4.241278455204224</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.33885482405729</v>
+        <v>-3.508534482227554</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.127469640526495</v>
+        <v>2.059597777258388</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.053581163202832</v>
+        <v>1.085630763582194</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.095516692384857</v>
+        <v>4.114746452612474</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343067</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.500423249584545</v>
+        <v>-3.670102907754809</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.061276280525745</v>
+        <v>1.993404417257639</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9267982394049529</v>
+        <v>0.9588478397843144</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.017880948316281</v>
+        <v>4.037110708543898</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.75459613538935</v>
+        <v>3.754596135389348</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.632724541682098</v>
+        <v>-3.802404199852362</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.021429170552642</v>
+        <v>1.953557307284536</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9267982394049529</v>
+        <v>0.9588478397843144</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.0309543551822</v>
+        <v>4.050184115409817</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378392</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.818592852521328</v>
+        <v>-3.988272510691592</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.93908704299989</v>
+        <v>1.871215179731784</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7682326460850052</v>
+        <v>0.8002822464643667</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.927820195973172</v>
+        <v>3.947049956200789</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006975</v>
+        <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.846493639630801</v>
+        <v>-4.016173297801065</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.926450769283103</v>
+        <v>1.858578906014997</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7336357219420704</v>
+        <v>0.7656853223214319</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.905586082614413</v>
+        <v>3.92481584284203</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787386</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.969019742333695</v>
+        <v>-4.138699400503959</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.874204772179144</v>
+        <v>1.806332908911038</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6111096192391765</v>
+        <v>0.6431592196185381</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.828834864969875</v>
+        <v>3.848064625197492</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.199534238519283</v>
+        <v>-4.369213896689548</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.848704933295412</v>
+        <v>1.780833070027307</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3805951230535878</v>
+        <v>0.4126447234329493</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.757232126849026</v>
+        <v>3.776461887076643</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814663</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.456255056514108</v>
+        <v>-4.625934714684371</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.886328325099329</v>
+        <v>1.818456461831224</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2721805489097729</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.832495101364584</v>
+        <v>3.851724861592201</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237091</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.610241474290248</v>
+        <v>-4.779921132460512</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.893714027134513</v>
+        <v>1.825842163866408</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2721805489097729</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.901475370510224</v>
+        <v>3.920705130737841</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423386</v>
+        <v>3.619923016423384</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.559719570462582</v>
+        <v>-4.729399228632846</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.8999739907857</v>
+        <v>1.832102127517595</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2721805489097729</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.887526572630345</v>
+        <v>3.906756332857962</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.812194724470307</v>
+        <v>-4.98187438264057</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.810854418238025</v>
+        <v>1.742982554969919</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2721805489097729</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.899397061685759</v>
+        <v>3.918626821913375</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973157</v>
+        <v>3.674028535973155</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.105090480949719</v>
+        <v>-5.274770139119982</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.694906650165203</v>
+        <v>1.627034786897098</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2721805489097729</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.900607596204702</v>
+        <v>3.919837356432319</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.26263455267916</v>
+        <v>-5.432314210849424</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.636010763700748</v>
+        <v>1.568138900432643</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2052787437694985</v>
+        <v>0.23732834414886</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.864588255347859</v>
+        <v>3.883818015575476</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916202</v>
+        <v>3.6521491529162</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.540598948262434</v>
+        <v>-5.710278606432698</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.519902858203628</v>
+        <v>1.452030994935523</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1156590094840142</v>
+        <v>0.1477086098633758</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.805894267512758</v>
+        <v>3.825124027740375</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.657566640901325</v>
+        <v>-5.827246299071589</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.635319837847116</v>
+        <v>1.56744797457901</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1156590094840142</v>
+        <v>0.1477086098633758</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.968098324211802</v>
+        <v>3.987328084439419</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071551</v>
+        <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.742284583122278</v>
+        <v>-5.911964241292542</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.596279298922549</v>
+        <v>1.528407435654443</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.03054298055596782</v>
+        <v>0.06259258093532938</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.911875344818788</v>
+        <v>3.931105105046405</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868147</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.824219401391161</v>
+        <v>-5.993899059561425</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.573734789183487</v>
+        <v>1.505862925915381</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.02060823496888764</v>
+        <v>0.05265783534824919</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.916143915035032</v>
+        <v>3.935373675262649</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332692</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.926195523639569</v>
+        <v>-6.095875181809832</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.541869978740026</v>
+        <v>1.473998115471921</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.08136788727951993</v>
+        <v>-0.04931828690015838</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.863883880141889</v>
+        <v>3.883113640369506</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231809</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.816189240162347</v>
+        <v>-5.985868898332611</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.57802537937509</v>
+        <v>1.510153516106985</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.05816331536224473</v>
+        <v>-0.02611371498288317</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.86995951053643</v>
+        <v>3.889189270764047</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818522</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.673129664421422</v>
+        <v>-5.842809322591686</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.639499220393434</v>
+        <v>1.571627357125329</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.05014988877226545</v>
+        <v>-0.0181002883929039</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.879017577212392</v>
+        <v>3.898247337440008</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051788</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.371682938949585</v>
+        <v>-5.541362597119848</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.767338793464706</v>
+        <v>1.6994669301966</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2512968366995718</v>
+        <v>0.2833464370789334</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.06714649537803</v>
+        <v>4.086376255605647</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679624</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.396273183184769</v>
+        <v>-5.565952841355032</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.758473873523343</v>
+        <v>1.690602010255237</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2512968366995718</v>
+        <v>0.2833464370789334</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.06811767313074</v>
+        <v>4.087347433358357</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.345234807178248</v>
+        <v>-5.514914465348512</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.779732128305706</v>
+        <v>1.7118602650376</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2512968366995718</v>
+        <v>0.2833464370789334</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.068960577510496</v>
+        <v>4.088190337738113</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969544</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.304095512311617</v>
+        <v>-5.473775170481881</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.815225945126504</v>
+        <v>1.747354081858398</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.2924361315662026</v>
+        <v>0.3244857319455642</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.112682253304619</v>
+        <v>4.131912013532236</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700479</v>
+        <v>3.825752932700477</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.193489372232015</v>
+        <v>-5.363169030402279</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.675652397282279</v>
+        <v>1.607780534014173</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4030422716458046</v>
+        <v>0.4350918720251662</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.995229933476315</v>
+        <v>4.014459693703932</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077641</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.324070106762858</v>
+        <v>-5.493749764933122</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.626922147543906</v>
+        <v>1.5590502842758</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.2724615371149621</v>
+        <v>0.3045111374943237</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.920383536831774</v>
+        <v>3.939613297059391</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833459</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.159573772571896</v>
+        <v>-5.32925343074216</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.677147500296373</v>
+        <v>1.609275637028267</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.2724615371149621</v>
+        <v>0.3045111374943237</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.904810355907856</v>
+        <v>3.924040116135473</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.186943705256328</v>
+        <v>-5.356623363426592</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.66538723765903</v>
+        <v>1.597515374390925</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.2724615371149621</v>
+        <v>0.3045111374943237</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.903998066344286</v>
+        <v>3.923227826571903</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147908</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.197328900146218</v>
+        <v>-5.367008558316481</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.671101938828147</v>
+        <v>1.603230075560041</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.2620763422250728</v>
+        <v>0.2941259426044344</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.907635728535425</v>
+        <v>3.926865488763042</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735283</v>
+        <v>3.834415493735282</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.215917058868443</v>
+        <v>-5.385596717038706</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.734503681115682</v>
+        <v>1.666631817847576</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.2434881835028475</v>
+        <v>0.275537783882209</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.967319839078515</v>
+        <v>3.986549599306132</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.216215605564479</v>
+        <v>-5.385895263734742</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.731253273255566</v>
+        <v>1.66338140998746</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.2434881835028475</v>
+        <v>0.275537783882209</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.964188849896813</v>
+        <v>3.98341861012443</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108858</v>
+        <v>3.815643212108857</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.115392471874051</v>
+        <v>-5.285072130044314</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.776113421671128</v>
+        <v>1.708241558403023</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.2559523989872013</v>
+        <v>0.2880019993665628</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.976198274126816</v>
+        <v>3.995428034354433</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121467</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.924611111121644</v>
+        <v>-5.094290769291907</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.852555219450634</v>
+        <v>1.784683356182529</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.4467337597396087</v>
+        <v>0.4787833601189702</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.090796344056804</v>
+        <v>4.110026104284421</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906081</v>
+        <v>3.77523303390608</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.906094257079824</v>
+        <v>-5.075773915250087</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.839798806804959</v>
+        <v>1.771926943536854</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.4596638891648169</v>
+        <v>0.4917134895441784</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.078391267449526</v>
+        <v>4.097621027677143</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912985</v>
+        <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.880901072578506</v>
+        <v>-5.050580730748769</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.884843017217545</v>
+        <v>1.816971153949439</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.4848570736661352</v>
+        <v>0.5169066740454967</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.128474114762375</v>
+        <v>4.147703874989992</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.868846945665543</v>
+        <v>-5.038526603835806</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.883351235884168</v>
+        <v>1.815479372616062</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.4969112005790981</v>
+        <v>0.5289608009584595</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.129393158811591</v>
+        <v>4.148622919039208</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811009</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.875470192355901</v>
+        <v>-5.045149850526164</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.88258256739216</v>
+        <v>1.814710704124054</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.4902879538887397</v>
+        <v>0.5223375542681012</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.127299840981512</v>
+        <v>4.146529601209129</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.61232244438292</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.772589602827308</v>
+        <v>-4.942269260997572</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.93658582908148</v>
+        <v>1.868713965813374</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.5931685434173326</v>
+        <v>0.6252181437966942</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.20187922057655</v>
+        <v>4.221108980804167</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760315</v>
+        <v>3.646857607760314</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.796031642007395</v>
+        <v>-4.965711300177658</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.947411683583039</v>
+        <v>1.879539820314934</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.5931685434173326</v>
+        <v>0.6252181437966942</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.222081890750144</v>
+        <v>4.241311650977761</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.814104150299007</v>
+        <v>-4.98378380846927</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.940182680266394</v>
+        <v>1.872310816998289</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.5931685434173326</v>
+        <v>0.6252181437966942</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.222081890750144</v>
+        <v>4.241311650977761</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.045277944175639</v>
+        <v>-5.214957602345902</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.807965076309208</v>
+        <v>1.740093213041103</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.5931685434173326</v>
+        <v>0.6252181437966942</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.182333804343611</v>
+        <v>4.201563564571228</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.013991923635183</v>
+        <v>-5.183671581805447</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.82750210352233</v>
+        <v>1.759630240254225</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.624454563957788</v>
+        <v>0.6565041643371495</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.208128035664824</v>
+        <v>4.227357795892441</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.860966531521899</v>
+        <v>-5.030646189692162</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.987883259940548</v>
+        <v>1.920011396672443</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.7774799560710721</v>
+        <v>0.8095295564504337</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.399114270505699</v>
+        <v>4.418344030733316</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.889273845395169</v>
+        <v>-5.058953503565433</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.164026559299533</v>
+        <v>2.096154696031427</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.7774799560710721</v>
+        <v>0.8095295564504337</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.586580495413991</v>
+        <v>4.605810255641608</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.055867070508691</v>
+        <v>-5.225546728678955</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.066792220608206</v>
+        <v>1.998920357340101</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.6108867309575496</v>
+        <v>0.6429363313369112</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.456027511699959</v>
+        <v>4.475257271927576</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.882802691126392</v>
+        <v>-5.052482349296655</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.139694375022843</v>
+        <v>2.071822511754738</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.6108867309575496</v>
+        <v>0.6429363313369112</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.459703914361677</v>
+        <v>4.478933674589294</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.823175943050769</v>
+        <v>3.437927467441012</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.81819439615188</v>
+        <v>-4.818460139246049</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.163155748136143</v>
+        <v>2.163049450898476</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.6108867309575496</v>
+        <v>0.6429363313369112</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.457321969485172</v>
+        <v>4.476551729712789</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240814.xlsx
+++ b/tame_output/ON/bt/strategyON_20240814.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>57.8%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>75.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.0%</t>
+          <t>-77.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.3%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.0%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>428.0%</t>
+          <t>430.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-643.4%</t>
+          <t>-636.2%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.2%</t>
+          <t>-34.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-159.9%</t>
+          <t>-157.0%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-304.9%</t>
+          <t>-303.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>82.3%</t>
+          <t>81.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097815</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131761</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539458</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729889</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440632</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608598</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764394</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940715</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770575</v>
+        <v>3.676841549770576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615278</v>
+        <v>3.685161381615279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646212</v>
+        <v>3.710935533646213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611563</v>
+        <v>3.768951674611564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955323</v>
+        <v>3.728577929955324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232408</v>
+        <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436224</v>
+        <v>3.766317079436225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.565781363752526</v>
+        <v>-8.490679767185721</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2598734609493243</v>
+        <v>-0.2298328223226025</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.322632628680952</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311944</v>
+        <v>3.784684521311945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.467874325076036</v>
+        <v>-8.392772728509231</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.221010960452189</v>
+        <v>-0.1909703218254672</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.254646878820395</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097239</v>
+        <v>3.80082935409724</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.443920784100078</v>
+        <v>-8.368819187533273</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2107610379163121</v>
+        <v>-0.1807203992895903</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.230693337844438</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017766</v>
+        <v>3.789311112017768</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.179860845777281</v>
+        <v>-8.104759249210476</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1183973787489458</v>
+        <v>-0.08835674012222361</v>
       </c>
       <c r="F1899" t="n">
         <v>-0.9666333995216414</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.83325274783972</v>
+        <v>3.833252747839721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.472781222272443</v>
+        <v>-7.397679625705638</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1616474369926886</v>
+        <v>0.1916880756194108</v>
       </c>
       <c r="F1900" t="n">
         <v>-0.9666333995216414</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388723</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.432596923906252</v>
+        <v>-7.357495327339447</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1780647802270061</v>
+        <v>0.2081054188537284</v>
       </c>
       <c r="F1901" t="n">
         <v>-0.9264491011554506</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626468</v>
+        <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.26919705296689</v>
+        <v>-7.194095456400085</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.242791549823508</v>
+        <v>0.2728321884502303</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.7630492302160882</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291809</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.035715830737291</v>
+        <v>-6.960614234170486</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3441084675532</v>
+        <v>0.3741491061799218</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.5295680079864896</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785785</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.886049439729776</v>
+        <v>-6.810947843162971</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4010828136432467</v>
+        <v>0.431123452269969</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.4366645167439537</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390425</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.75377396609889</v>
+        <v>-6.678672369532085</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4493604898426287</v>
+        <v>0.4794011284693505</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.304389043113067</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471879410595</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.598035633539148</v>
+        <v>-6.522934036972343</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.514470883554162</v>
+        <v>0.5445115221808838</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.1486507105533255</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960983</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.513070966809828</v>
+        <v>-6.437969370243023</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5613630914695489</v>
+        <v>0.5914037300962707</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.06368604382400589</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607641</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.618660956582932</v>
+        <v>-6.543559360016127</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3911511659610882</v>
+        <v>0.42119180458781</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.1692760335971102</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987897</v>
+        <v>3.770422583987899</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.550426371957505</v>
+        <v>-6.4753247753907</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4669893416883455</v>
+        <v>0.4970299803150677</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.1508607107245742</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710809</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.402486330549905</v>
+        <v>-6.3273847339831</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4062864355632176</v>
+        <v>0.4363270741899399</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.1305397948160167</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409201</v>
+        <v>3.723566229409203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.349516808295917</v>
+        <v>-6.274415211729112</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4187602582113348</v>
+        <v>0.448800896838057</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.07757027256202781</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098106</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.183728612335626</v>
+        <v>-6.108627015768821</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4781149245003582</v>
+        <v>0.50815556312708</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.07757027256202781</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493417</v>
+        <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.150365405856857</v>
+        <v>-6.075263809290052</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5059225614730085</v>
+        <v>0.5359632000997308</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.07757027256202781</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722814</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.042106268734336</v>
+        <v>-5.967004672167531</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5437583367812122</v>
+        <v>0.5737989754079345</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.07757027256202781</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792043</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.918815133917205</v>
+        <v>-5.8437135373504</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5905728847186418</v>
+        <v>0.6206135233453636</v>
       </c>
       <c r="F1915" t="n">
         <v>0.04572086225510269</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919903</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.866118266785914</v>
+        <v>-5.791016670219109</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6193526098084834</v>
+        <v>0.6493932484352052</v>
       </c>
       <c r="F1916" t="n">
         <v>0.09841772938639387</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318089</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.622352824802469</v>
+        <v>-5.547251228235664</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7126394949489119</v>
+        <v>0.7426801335756337</v>
       </c>
       <c r="F1917" t="n">
         <v>0.09841772938639387</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057522</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.532577152425997</v>
+        <v>-5.457475555859192</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7506740778195167</v>
+        <v>0.7807147164462385</v>
       </c>
       <c r="F1918" t="n">
         <v>0.1600171743007039</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635497427918</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.282726758476922</v>
+        <v>-5.207625161910117</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8433563103828488</v>
+        <v>0.8733969490095705</v>
       </c>
       <c r="F1919" t="n">
         <v>0.1600171743007039</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011493</v>
+        <v>3.835957987011494</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.10683466600949</v>
+        <v>-5.031733069442685</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9173122708904704</v>
+        <v>0.9473529095171922</v>
       </c>
       <c r="F1920" t="n">
         <v>0.1600171743007039</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392981</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.935388202987027</v>
+        <v>-4.860286606420222</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9992183621540094</v>
+        <v>1.029259000780731</v>
       </c>
       <c r="F1921" t="n">
         <v>0.331463637323167</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632775</v>
+        <v>3.773765222632777</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.855365915877906</v>
+        <v>-4.780264319311101</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.030247754613955</v>
+        <v>1.060288393240677</v>
       </c>
       <c r="F1922" t="n">
         <v>0.411485924432288</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883069</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.791730173643971</v>
+        <v>-4.716628577077167</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.060396852561846</v>
+        <v>1.090437491188568</v>
       </c>
       <c r="F1923" t="n">
         <v>0.4751216666662225</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074777</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.698032855427576</v>
+        <v>-4.622931258860771</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.079070038632199</v>
+        <v>1.109110677258921</v>
       </c>
       <c r="F1924" t="n">
         <v>0.4751216666662225</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242289</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.708535478492865</v>
+        <v>-4.63343388192606</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.076612066030961</v>
+        <v>1.106652704657683</v>
       </c>
       <c r="F1925" t="n">
         <v>0.4646190436009336</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367679</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.636292910321671</v>
+        <v>-4.561191313754866</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.109438407134259</v>
+        <v>1.139479045760981</v>
       </c>
       <c r="F1926" t="n">
         <v>0.4646190436009336</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232699787996</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.618579223443805</v>
+        <v>-4.543477626877</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.117202465802746</v>
+        <v>1.147243104429467</v>
       </c>
       <c r="F1927" t="n">
         <v>0.4678003724978504</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502332</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.509774337964078</v>
+        <v>-4.434672741397273</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.15772249121463</v>
+        <v>1.187763129841352</v>
       </c>
       <c r="F1928" t="n">
         <v>0.4678003724978504</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675933</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.289753539927068</v>
+        <v>-4.214651943360263</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.247309847440048</v>
+        <v>1.27735048606677</v>
       </c>
       <c r="F1929" t="n">
         <v>0.6090202175658307</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.15688585086379</v>
+        <v>-4.081784254296985</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.316351105867182</v>
+        <v>1.346391744493904</v>
       </c>
       <c r="F1930" t="n">
         <v>0.6090202175658307</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496257</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.036712767499291</v>
+        <v>-3.961611170932486</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.365566183653284</v>
+        <v>1.395606822280006</v>
       </c>
       <c r="F1931" t="n">
         <v>0.7291933009303296</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576994</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.901459406169314</v>
+        <v>-3.826357809602509</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.429755630746715</v>
+        <v>1.459796269373437</v>
       </c>
       <c r="F1932" t="n">
         <v>0.8644466622603068</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.7358392229421</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.961334233527007</v>
+        <v>-3.886232636960202</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.391843191205064</v>
+        <v>1.421883829831785</v>
       </c>
       <c r="F1933" t="n">
         <v>0.8045718349026146</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.841514002616169</v>
+        <v>-3.766412406049364</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.455060452803607</v>
+        <v>1.485101091430329</v>
       </c>
       <c r="F1934" t="n">
         <v>0.8045718349026146</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430689</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.843983709077975</v>
+        <v>-3.76888211251117</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.361716769541326</v>
+        <v>1.391757408168048</v>
       </c>
       <c r="F1935" t="n">
         <v>0.8021021284408085</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003596</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.912353895401985</v>
+        <v>-3.83725229883518</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.253630556497024</v>
+        <v>1.283671195123746</v>
       </c>
       <c r="F1936" t="n">
         <v>0.8113778274770235</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508365</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.926141948249032</v>
+        <v>-3.851040351682227</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.238552043990096</v>
+        <v>1.268592682616818</v>
       </c>
       <c r="F1937" t="n">
         <v>0.8113778274770235</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.981662024141621</v>
+        <v>-3.906560427574816</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.353374850325263</v>
+        <v>1.383415488951985</v>
       </c>
       <c r="F1938" t="n">
         <v>0.8113778274770235</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.806187764349152</v>
+        <v>-3.731086167782347</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.428131786234038</v>
+        <v>1.45817242486076</v>
       </c>
       <c r="F1939" t="n">
         <v>0.8113778274770235</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322544</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.9171240169904</v>
+        <v>-3.842022420423596</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.359499313938746</v>
+        <v>1.389539952565468</v>
       </c>
       <c r="F1940" t="n">
         <v>0.8113778274770235</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.883460471518119</v>
+        <v>-3.808358874951314</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.301503045529108</v>
+        <v>1.33154368415583</v>
       </c>
       <c r="F1941" t="n">
         <v>0.8450413729493054</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.823607852314395</v>
+        <v>-3.748506255747591</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.33561647964273</v>
+        <v>1.365657118269452</v>
       </c>
       <c r="F1942" t="n">
         <v>0.8450413729493054</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.737364389288018</v>
+        <v>-3.662262792721213</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.365060135427141</v>
+        <v>1.395100774053863</v>
       </c>
       <c r="F1943" t="n">
         <v>0.8450413729493054</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.782671208686998</v>
+        <v>-3.707569612120193</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.338713183112075</v>
+        <v>1.368753821738797</v>
       </c>
       <c r="F1944" t="n">
         <v>0.8042312099400746</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.75357116580319</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.8117043133893</v>
+        <v>-3.736602716822495</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.327651814264256</v>
+        <v>1.357692452890978</v>
       </c>
       <c r="F1945" t="n">
         <v>0.8042312099400746</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.71889383193844</v>
+        <v>-3.643792235371635</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.294048698735965</v>
+        <v>1.324089337362687</v>
       </c>
       <c r="F1946" t="n">
         <v>0.8970416913909339</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.763283301267868</v>
+        <v>-3.688181704701063</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.278166386928795</v>
+        <v>1.308207025555517</v>
       </c>
       <c r="F1947" t="n">
         <v>0.8526522220615063</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.879824906373211</v>
+        <v>-3.804723309806406</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.226625453398381</v>
+        <v>1.256666092025103</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7361106169561635</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.919749000955782</v>
+        <v>-3.844647404388978</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.216147111396019</v>
+        <v>1.246187750022741</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7361106169561635</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.947529398857136</v>
+        <v>-3.872427802290331</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.216532154004017</v>
+        <v>1.246572792630739</v>
       </c>
       <c r="F1950" t="n">
         <v>0.7083302190548104</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.065910071587274</v>
+        <v>-3.990808475020469</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.007535604912615</v>
+        <v>1.037576243539337</v>
       </c>
       <c r="F1951" t="n">
         <v>0.6411123669038342</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.174524150030605</v>
+        <v>-4.0994225534638</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.084239634254488</v>
+        <v>1.11428027288121</v>
       </c>
       <c r="F1952" t="n">
         <v>0.6411123669038342</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.139115111782462</v>
+        <v>-4.064013515215657</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.112916275656068</v>
+        <v>1.14295691428279</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6411123669038342</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.100731449224311</v>
+        <v>-4.025629852657506</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.125689182021698</v>
+        <v>1.15572982064842</v>
       </c>
       <c r="F1954" t="n">
         <v>0.6794960294619854</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.125344377738771</v>
+        <v>-3.84851352262234</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.112573039461215</v>
+        <v>1.223305381507788</v>
       </c>
       <c r="F1955" t="n">
         <v>0.6794960294619854</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.170436622572317</v>
+        <v>-3.893605767455885</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.09521953328971</v>
+        <v>1.205951875336283</v>
       </c>
       <c r="F1956" t="n">
         <v>0.6175999862925956</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.991061201333549</v>
+        <v>-3.714230346217118</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.160756677091632</v>
+        <v>1.271489019138204</v>
       </c>
       <c r="F1957" t="n">
         <v>0.7743767444633143</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.036075414854155</v>
+        <v>-3.759244559737724</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.123558447014979</v>
+        <v>1.234290789061552</v>
       </c>
       <c r="F1958" t="n">
         <v>0.7440278491487097</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.30307992512659</v>
+        <v>-4.026249070010159</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.022448205244951</v>
+        <v>1.133180547291523</v>
       </c>
       <c r="F1959" t="n">
         <v>0.5496648111057612</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.404277706563763</v>
+        <v>-4.127446851447332</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9811730145665831</v>
+        <v>1.091905356613155</v>
       </c>
       <c r="F1960" t="n">
         <v>0.481255997560442</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815454</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.39776673994945</v>
+        <v>-4.12093588483302</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9813773627666249</v>
+        <v>1.092109704813197</v>
       </c>
       <c r="F1961" t="n">
         <v>0.481255997560442</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.378728612242153</v>
+        <v>-4.101897757125722</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9855173330577889</v>
+        <v>1.096249675104361</v>
       </c>
       <c r="F1962" t="n">
         <v>0.4230723862292474</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.431244414516973</v>
+        <v>-4.154413559400543</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.083805413782051</v>
+        <v>1.194537755828623</v>
       </c>
       <c r="F1963" t="n">
         <v>0.4230723862292474</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067861</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.445111175850891</v>
+        <v>-4.168280320734461</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.079092038234617</v>
+        <v>1.18982438028119</v>
       </c>
       <c r="F1964" t="n">
         <v>0.3852144694954245</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789118</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.400307004310961</v>
+        <v>-4.123476149194531</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.103022237247515</v>
+        <v>1.213754579294088</v>
       </c>
       <c r="F1965" t="n">
         <v>0.3852144694954245</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.252564034075959</v>
+        <v>-3.975733178959528</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.060069646618716</v>
+        <v>1.170801988665288</v>
       </c>
       <c r="F1966" t="n">
         <v>0.5530218267303076</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181168</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.336385255350657</v>
+        <v>-4.059554400234227</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.029334779640317</v>
+        <v>1.14006712168689</v>
       </c>
       <c r="F1967" t="n">
         <v>0.5530218267303076</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.330232549297873</v>
+        <v>-4.053401694181442</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.032458210453089</v>
+        <v>1.143190552499662</v>
       </c>
       <c r="F1968" t="n">
         <v>0.5591745327830919</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.347041847448375</v>
+        <v>-4.070210992331944</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.024814967932999</v>
+        <v>1.135547309979571</v>
       </c>
       <c r="F1969" t="n">
         <v>0.5423652346325902</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798422</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.284743848672252</v>
+        <v>-4.007912993555822</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.116069721240269</v>
+        <v>1.226802063286841</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5876594989070323</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.082953651007094</v>
+        <v>-3.806122795890664</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9990778020204591</v>
+        <v>1.109810144067031</v>
       </c>
       <c r="F1971" t="n">
         <v>0.7856776910761867</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.133840363693289</v>
+        <v>-3.857009508576859</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.049013349268156</v>
+        <v>1.159745691314728</v>
       </c>
       <c r="F1972" t="n">
         <v>0.7347909783899922</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.047229621043482</v>
+        <v>-3.770398765927051</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.098285382444123</v>
+        <v>1.209017724490695</v>
       </c>
       <c r="F1973" t="n">
         <v>0.8134167095951504</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.107438919048767</v>
+        <v>-3.830608063932336</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.07273764406668</v>
+        <v>1.183469986113253</v>
       </c>
       <c r="F1974" t="n">
         <v>0.7532074115898659</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.03101687261684</v>
+        <v>-3.754186017500409</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.10179808067938</v>
+        <v>1.212530422725952</v>
       </c>
       <c r="F1975" t="n">
         <v>0.7532074115898659</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.986643740978272</v>
+        <v>-3.70981288586184</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.119410200770243</v>
+        <v>1.230142542816816</v>
       </c>
       <c r="F1976" t="n">
         <v>0.7975805432284345</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.009124091837156</v>
+        <v>-3.732293236720725</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.10481185456528</v>
+        <v>1.215544196611852</v>
       </c>
       <c r="F1977" t="n">
         <v>0.7975805432284345</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.961468361276101</v>
+        <v>-3.68463750615967</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.130255903817507</v>
+        <v>1.240988245864079</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8452362737894902</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.860950202777346</v>
+        <v>-3.584119347660915</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.175355540591734</v>
+        <v>1.286087882638306</v>
       </c>
       <c r="F1979" t="n">
         <v>0.9457544322882447</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557295</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.845044873344993</v>
+        <v>-3.568214018228562</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.168472344840547</v>
+        <v>1.279204686887119</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8666417715790058</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.81683703393277</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.800206471736595</v>
+        <v>-3.523375616620164</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.190505408094535</v>
+        <v>1.301237750141107</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8711852045238753</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917053</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.819704927978604</v>
+        <v>-3.542874072862173</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.18686696522881</v>
+        <v>1.297599307275382</v>
       </c>
       <c r="F1982" t="n">
         <v>0.823100563243971</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405961</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.775502090892703</v>
+        <v>-3.498671235776272</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.210427702591007</v>
+        <v>1.321160044637579</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8673034003298714</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265645</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.78306175672975</v>
+        <v>-3.506230901613319</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.205813836725436</v>
+        <v>1.316546178772008</v>
       </c>
       <c r="F1984" t="n">
         <v>0.9221068043396907</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.624770339190478</v>
+        <v>-3.347939484074047</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.320378168924184</v>
+        <v>1.431110510970756</v>
       </c>
       <c r="F1985" t="n">
         <v>0.9221068043396907</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321024</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.417128335556002</v>
+        <v>-3.140297480439571</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.401875674972228</v>
+        <v>1.5126080170188</v>
       </c>
       <c r="F1986" t="n">
         <v>1.129748807974167</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.86448984247514</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.366096242833474</v>
+        <v>-3.089265387717043</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.417236740299509</v>
+        <v>1.527969082346081</v>
       </c>
       <c r="F1987" t="n">
         <v>1.180780900696695</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404854</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.300872061706268</v>
+        <v>-3.024041206589837</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.460513816843096</v>
+        <v>1.571246158889668</v>
       </c>
       <c r="F1988" t="n">
         <v>1.246005081823901</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882559</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.263445041635134</v>
+        <v>-2.986614186518703</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.47144559717083</v>
+        <v>1.582177939217402</v>
       </c>
       <c r="F1989" t="n">
         <v>1.251256619853082</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992659</v>
+        <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.283556697669842</v>
+        <v>-3.006725842553411</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.464657727088187</v>
+        <v>1.575390069134759</v>
       </c>
       <c r="F1990" t="n">
         <v>1.262283964850502</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636288</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.229811883242637</v>
+        <v>-2.952981028126207</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.64671342388028</v>
+        <v>1.757445765926852</v>
       </c>
       <c r="F1991" t="n">
         <v>1.272347274290964</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957627</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.155029622217625</v>
+        <v>-2.878198767101194</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.796739237508102</v>
+        <v>1.907471579554674</v>
       </c>
       <c r="F1992" t="n">
         <v>1.347129535315976</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.814230727998758</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.128945537953817</v>
+        <v>-2.852114682837386</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.798880847227484</v>
+        <v>1.909613189274056</v>
       </c>
       <c r="F1993" t="n">
         <v>1.347129535315976</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896933</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.041067624844696</v>
+        <v>-2.764236769728265</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.832225208054912</v>
+        <v>1.942957550101484</v>
       </c>
       <c r="F1994" t="n">
         <v>1.463055177739327</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959861</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.032175163451413</v>
+        <v>-2.755344308334982</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.853336598339017</v>
+        <v>1.964068940385589</v>
       </c>
       <c r="F1995" t="n">
         <v>1.463055177739327</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945363</v>
+        <v>3.794424941945368</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.200651280421291</v>
+        <v>-2.92382042530486</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.777801198955649</v>
+        <v>1.888533541002222</v>
       </c>
       <c r="F1996" t="n">
         <v>1.435107342022747</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782712</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.754395087791851</v>
+        <v>-2.47756423267542</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.937573373195288</v>
+        <v>2.04830571524186</v>
       </c>
       <c r="F1997" t="n">
         <v>1.340388672353114</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632639</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.731673984108698</v>
+        <v>-2.454843128992267</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.937325837165453</v>
+        <v>2.048058179212025</v>
       </c>
       <c r="F1998" t="n">
         <v>1.340388672353114</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777676</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.860875797402741</v>
+        <v>-2.58404494228631</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.044551237699005</v>
+        <v>2.155283579745577</v>
       </c>
       <c r="F1999" t="n">
         <v>1.211186859059072</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644415</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.015656804180996</v>
+        <v>-2.738825949064565</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.019716657481349</v>
+        <v>2.130448999527921</v>
       </c>
       <c r="F2000" t="n">
         <v>1.177819185004596</v>
@@ -47568,16 +47568,16 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799968</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.008602113965823</v>
+        <v>-2.731771258849392</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.019213889556964</v>
+        <v>2.129946231603536</v>
       </c>
       <c r="F2001" t="n">
         <v>1.184873875219769</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331118</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.981650889639335</v>
+        <v>-2.704820034522904</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.040000532932301</v>
+        <v>2.150732874978873</v>
       </c>
       <c r="F2002" t="n">
         <v>1.199754221247489</v>
@@ -47614,16 +47614,16 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784111</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.117603897695651</v>
+        <v>-2.84077304257922</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.169722461854734</v>
+        <v>2.280454803901306</v>
       </c>
       <c r="F2003" t="n">
         <v>1.199754221247489</v>
@@ -47637,16 +47637,16 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714429</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.140012015500523</v>
+        <v>-2.863181160384092</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.152875909635778</v>
+        <v>2.26360825168235</v>
       </c>
       <c r="F2004" t="n">
         <v>1.199754221247489</v>
@@ -47660,16 +47660,16 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155035</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.168236251078123</v>
+        <v>-2.891405395961693</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.143640214954375</v>
+        <v>2.254372557000948</v>
       </c>
       <c r="F2005" t="n">
         <v>1.217730973698797</v>
@@ -47683,16 +47683,16 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.72945228516198</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.177677176966653</v>
+        <v>-2.900846321850223</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.19611756232081</v>
+        <v>2.306849904367382</v>
       </c>
       <c r="F2006" t="n">
         <v>1.340158091242189</v>
@@ -47706,16 +47706,16 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321637</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.229950784302295</v>
+        <v>-2.953119929185864</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.178099213931855</v>
+        <v>2.288831555978427</v>
       </c>
       <c r="F2007" t="n">
         <v>1.287884483906547</v>
@@ -47729,16 +47729,16 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.727898186347707</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.306280761903201</v>
+        <v>-3.02944990678677</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.145679035785268</v>
+        <v>2.25641137783184</v>
       </c>
       <c r="F2008" t="n">
         <v>1.287884483906547</v>
@@ -47752,16 +47752,16 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887751</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.508534482227554</v>
+        <v>-3.231703627111123</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.059597777258388</v>
+        <v>2.170330119304961</v>
       </c>
       <c r="F2009" t="n">
         <v>1.085630763582194</v>
@@ -47775,16 +47775,16 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343069</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.670102907754809</v>
+        <v>-3.393272052638378</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.993404417257639</v>
+        <v>2.104136759304211</v>
       </c>
       <c r="F2010" t="n">
         <v>0.9588478397843144</v>
@@ -47798,16 +47798,16 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389348</v>
+        <v>3.754596135389352</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.802404199852362</v>
+        <v>-3.525573344735931</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.953557307284536</v>
+        <v>2.064289649331108</v>
       </c>
       <c r="F2011" t="n">
         <v>0.9588478397843144</v>
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378396</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.988272510691592</v>
+        <v>-3.711441655575161</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.871215179731784</v>
+        <v>1.981947521778356</v>
       </c>
       <c r="F2012" t="n">
         <v>0.8002822464643667</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006973</v>
+        <v>3.715819895006979</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.016173297801065</v>
+        <v>-3.739342442684634</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.858578906014997</v>
+        <v>1.969311248061569</v>
       </c>
       <c r="F2013" t="n">
         <v>0.7656853223214319</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.68489577878739</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.138699400503959</v>
+        <v>-3.861868545387528</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.806332908911038</v>
+        <v>1.91706525095761</v>
       </c>
       <c r="F2014" t="n">
         <v>0.6431592196185381</v>
@@ -47890,16 +47890,16 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585936</v>
+        <v>3.619348081585941</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.369213896689548</v>
+        <v>-4.092383041573116</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.780833070027307</v>
+        <v>1.891565412073879</v>
       </c>
       <c r="F2015" t="n">
         <v>0.4126447234329493</v>
@@ -47913,16 +47913,16 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814663</v>
+        <v>3.640750087814668</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.625934714684371</v>
+        <v>-4.349103859567941</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.818456461831224</v>
+        <v>1.929188803877796</v>
       </c>
       <c r="F2016" t="n">
         <v>0.3042301492891345</v>
@@ -47936,16 +47936,16 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237091</v>
+        <v>3.668289004237097</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.779921132460512</v>
+        <v>-4.503090277344081</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.825842163866408</v>
+        <v>1.936574505912979</v>
       </c>
       <c r="F2017" t="n">
         <v>0.3042301492891345</v>
@@ -47959,16 +47959,16 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423384</v>
+        <v>3.61992301642339</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.729399228632846</v>
+        <v>-4.452568373516415</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.832102127517595</v>
+        <v>1.942834469564167</v>
       </c>
       <c r="F2018" t="n">
         <v>0.3042301492891345</v>
@@ -47982,16 +47982,16 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609751</v>
+        <v>3.656332733609756</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.98187438264057</v>
+        <v>-4.70504352752414</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.742982554969919</v>
+        <v>1.853714897016491</v>
       </c>
       <c r="F2019" t="n">
         <v>0.3042301492891345</v>
@@ -48005,16 +48005,16 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973155</v>
+        <v>3.67402853597316</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.274770139119982</v>
+        <v>-4.997939284003552</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.627034786897098</v>
+        <v>1.73776712894367</v>
       </c>
       <c r="F2020" t="n">
         <v>0.3042301492891345</v>
@@ -48028,16 +48028,16 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251943</v>
+        <v>3.663509457251948</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.432314210849424</v>
+        <v>-5.155483355732994</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.568138900432643</v>
+        <v>1.678871242479214</v>
       </c>
       <c r="F2021" t="n">
         <v>0.23732834414886</v>
@@ -48051,16 +48051,16 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.6521491529162</v>
+        <v>3.652149152916205</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.710278606432698</v>
+        <v>-5.433447751316267</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.452030994935523</v>
+        <v>1.562763336982095</v>
       </c>
       <c r="F2022" t="n">
         <v>0.1477086098633758</v>
@@ -48074,16 +48074,16 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830327</v>
+        <v>3.667962306830331</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.827246299071589</v>
+        <v>-5.550415443955158</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.56744797457901</v>
+        <v>1.678180316625582</v>
       </c>
       <c r="F2023" t="n">
         <v>0.1477086098633758</v>
@@ -48097,16 +48097,16 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071549</v>
+        <v>3.696539468071554</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.911964241292542</v>
+        <v>-5.635133386176111</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.528407435654443</v>
+        <v>1.639139777701015</v>
       </c>
       <c r="F2024" t="n">
         <v>0.06259258093532938</v>
@@ -48120,16 +48120,16 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868149</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.993899059561425</v>
+        <v>-5.717068204444995</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.505862925915381</v>
+        <v>1.616595267961953</v>
       </c>
       <c r="F2025" t="n">
         <v>0.05265783534824919</v>
@@ -48143,16 +48143,16 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332693</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.095875181809832</v>
+        <v>-5.819044326693402</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.473998115471921</v>
+        <v>1.584730457518492</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.04931828690015838</v>
@@ -48166,16 +48166,16 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231811</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.985868898332611</v>
+        <v>-5.70903804321618</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.510153516106985</v>
+        <v>1.620885858153557</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.02611371498288317</v>
@@ -48189,16 +48189,16 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78556392481852</v>
+        <v>3.785563924818525</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.842809322591686</v>
+        <v>-5.565978467475255</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.571627357125329</v>
+        <v>1.682359699171901</v>
       </c>
       <c r="F2028" t="n">
         <v>-0.0181002883929039</v>
@@ -48212,16 +48212,16 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.77723741205179</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.541362597119848</v>
+        <v>-5.264531742003418</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.6994669301966</v>
+        <v>1.810199272243172</v>
       </c>
       <c r="F2029" t="n">
         <v>0.2833464370789334</v>
@@ -48235,16 +48235,16 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679627</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.565952841355032</v>
+        <v>-5.289121986238602</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.690602010255237</v>
+        <v>1.801334352301809</v>
       </c>
       <c r="F2030" t="n">
         <v>0.2833464370789334</v>
@@ -48258,16 +48258,16 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474162</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.514914465348512</v>
+        <v>-5.238083610232081</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.7118602650376</v>
+        <v>1.822592607084172</v>
       </c>
       <c r="F2031" t="n">
         <v>0.2833464370789334</v>
@@ -48281,16 +48281,16 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969545</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.473775170481881</v>
+        <v>-5.19694431536545</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.747354081858398</v>
+        <v>1.85808642390497</v>
       </c>
       <c r="F2032" t="n">
         <v>0.3244857319455642</v>
@@ -48304,16 +48304,16 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700477</v>
+        <v>3.825752932700481</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.363169030402279</v>
+        <v>-5.086338175285849</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.607780534014173</v>
+        <v>1.718512876060745</v>
       </c>
       <c r="F2033" t="n">
         <v>0.4350918720251662</v>
@@ -48327,16 +48327,16 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.804688961077643</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.493749764933122</v>
+        <v>-5.216918909816691</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.5590502842758</v>
+        <v>1.669782626322372</v>
       </c>
       <c r="F2034" t="n">
         <v>0.3045111374943237</v>
@@ -48350,16 +48350,16 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.77502886083346</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.32925343074216</v>
+        <v>-5.052422575625729</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.609275637028267</v>
+        <v>1.720007979074839</v>
       </c>
       <c r="F2035" t="n">
         <v>0.3045111374943237</v>
@@ -48373,16 +48373,16 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077631</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.356623363426592</v>
+        <v>-5.079792508310161</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.597515374390925</v>
+        <v>1.708247716437496</v>
       </c>
       <c r="F2036" t="n">
         <v>0.3045111374943237</v>
@@ -48396,16 +48396,16 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147908</v>
+        <v>3.832307024147912</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.367008558316481</v>
+        <v>-5.090177703200051</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.603230075560041</v>
+        <v>1.713962417606613</v>
       </c>
       <c r="F2037" t="n">
         <v>0.2941259426044344</v>
@@ -48419,16 +48419,16 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735282</v>
+        <v>3.834415493735285</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.385596717038706</v>
+        <v>-5.108765861922276</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.666631817847576</v>
+        <v>1.777364159894148</v>
       </c>
       <c r="F2038" t="n">
         <v>0.275537783882209</v>
@@ -48442,16 +48442,16 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496557</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.385895263734742</v>
+        <v>-5.109064408618312</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.66338140998746</v>
+        <v>1.774113752034032</v>
       </c>
       <c r="F2039" t="n">
         <v>0.275537783882209</v>
@@ -48465,16 +48465,16 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108857</v>
+        <v>3.81564321210886</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.285072130044314</v>
+        <v>-5.008241274927884</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.708241558403023</v>
+        <v>1.818973900449595</v>
       </c>
       <c r="F2040" t="n">
         <v>0.2880019993665628</v>
@@ -48488,16 +48488,16 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121469</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.094290769291907</v>
+        <v>-4.817459914175477</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.784683356182529</v>
+        <v>1.895415698229101</v>
       </c>
       <c r="F2041" t="n">
         <v>0.4787833601189702</v>
@@ -48511,16 +48511,16 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.77523303390608</v>
+        <v>3.775233033906082</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.075773915250087</v>
+        <v>-4.798943060133657</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.771926943536854</v>
+        <v>1.882659285583425</v>
       </c>
       <c r="F2042" t="n">
         <v>0.4917134895441784</v>
@@ -48534,16 +48534,16 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912984</v>
+        <v>3.785761685912988</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-5.050580730748769</v>
+        <v>-4.773749875632339</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.816971153949439</v>
+        <v>1.927703495996011</v>
       </c>
       <c r="F2043" t="n">
         <v>0.5169066740454967</v>
@@ -48557,16 +48557,16 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539897</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-5.038526603835806</v>
+        <v>-4.761695748719376</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.815479372616062</v>
+        <v>1.926211714662634</v>
       </c>
       <c r="F2044" t="n">
         <v>0.5289608009584595</v>
@@ -48580,16 +48580,16 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.725010844811012</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.045149850526164</v>
+        <v>-4.768318995409734</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.814710704124054</v>
+        <v>1.925443046170626</v>
       </c>
       <c r="F2045" t="n">
         <v>0.5223375542681012</v>
@@ -48603,16 +48603,16 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.612322444382922</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.942269260997572</v>
+        <v>-4.665438405881141</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.868713965813374</v>
+        <v>1.979446307859946</v>
       </c>
       <c r="F2046" t="n">
         <v>0.6252181437966942</v>
@@ -48626,16 +48626,16 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760314</v>
+        <v>3.646857607760318</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.965711300177658</v>
+        <v>-4.688880445061228</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.879539820314934</v>
+        <v>1.990272162361506</v>
       </c>
       <c r="F2047" t="n">
         <v>0.6252181437966942</v>
@@ -48649,16 +48649,16 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781705</v>
+        <v>3.666767386781709</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.98378380846927</v>
+        <v>-4.70695295335284</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.872310816998289</v>
+        <v>1.983043159044861</v>
       </c>
       <c r="F2048" t="n">
         <v>0.6252181437966942</v>
@@ -48672,16 +48672,16 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082834</v>
+        <v>3.670068888082838</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.214957602345902</v>
+        <v>-4.938126747229472</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.740093213041103</v>
+        <v>1.850825555087675</v>
       </c>
       <c r="F2049" t="n">
         <v>0.6252181437966942</v>
@@ -48695,16 +48695,16 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943585</v>
+        <v>3.745593333943589</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.183671581805447</v>
+        <v>-4.906840726689016</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.759630240254225</v>
+        <v>1.870362582300797</v>
       </c>
       <c r="F2050" t="n">
         <v>0.6565041643371495</v>
@@ -48718,16 +48718,16 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677824</v>
+        <v>3.730590658677827</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.030646189692162</v>
+        <v>-4.753815334575732</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.920011396672443</v>
+        <v>2.030743738719015</v>
       </c>
       <c r="F2051" t="n">
         <v>0.8095295564504337</v>
@@ -48741,16 +48741,16 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073883</v>
+        <v>3.741298518073886</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.058953503565433</v>
+        <v>-4.782122648449002</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.096154696031427</v>
+        <v>2.206887038077999</v>
       </c>
       <c r="F2052" t="n">
         <v>0.8095295564504337</v>
@@ -48764,16 +48764,16 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903168</v>
+        <v>3.699135800903171</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.225546728678955</v>
+        <v>-4.948715873562525</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.998920357340101</v>
+        <v>2.109652699386673</v>
       </c>
       <c r="F2053" t="n">
         <v>0.6429363313369112</v>
@@ -48787,16 +48787,16 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568382</v>
+        <v>3.708202704568386</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.052482349296655</v>
+        <v>-4.775651494180225</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.071822511754738</v>
+        <v>2.18255485380131</v>
       </c>
       <c r="F2054" t="n">
         <v>0.6429363313369112</v>
@@ -48810,16 +48810,16 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.437927467441012</v>
+        <v>3.858405956600907</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.818460139246049</v>
+        <v>-4.746405513724528</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.163049450898476</v>
+        <v>2.191871301107084</v>
       </c>
       <c r="F2055" t="n">
         <v>0.6429363313369112</v>

--- a/tame_output/ON/bt/strategyON_20240814.xlsx
+++ b/tame_output/ON/bt/strategyON_20240814.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>73.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>111.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.7%</t>
+          <t>-77.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>107.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,11 +931,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>123.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.0%</t>
+          <t>-46.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-73.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.3%</t>
+          <t>430.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-636.2%</t>
+          <t>-626.7%</t>
         </is>
       </c>
     </row>
@@ -1074,26 +1074,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-31.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-157.0%</t>
+          <t>-153.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-13.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>-26.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>-27.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-303.9%</t>
+          <t>-422.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-159.7%</t>
+          <t>-167.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,22 +1418,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>81.3%</t>
+          <t>78.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>-23.2%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2055"/>
+  <dimension ref="A1:G2056"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44383,10 +44383,10 @@
         <v>1.209489783080714</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.03508905844176807</v>
+        <v>-0.11553456753543</v>
       </c>
       <c r="G1862" t="n">
-        <v>3.096371025858021</v>
+        <v>3.048103720401823</v>
       </c>
     </row>
     <row r="1863">
@@ -44406,10 +44406,10 @@
         <v>1.062693345031047</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.3313998427407806</v>
+        <v>-0.4118453518344425</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.917839070284444</v>
+        <v>2.869571764828247</v>
       </c>
     </row>
     <row r="1864">
@@ -44429,10 +44429,10 @@
         <v>0.8980193781735339</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.8204341290151209</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.671447347990797</v>
+        <v>2.623180042534599</v>
       </c>
     </row>
     <row r="1865">
@@ -44452,10 +44452,10 @@
         <v>0.8477006458358489</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.8204341290151209</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.666632780462257</v>
+        <v>2.61836547500606</v>
       </c>
     </row>
     <row r="1866">
@@ -44475,10 +44475,10 @@
         <v>0.6791379467299272</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.8204341290151209</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.664626831071135</v>
+        <v>2.616359525614937</v>
       </c>
     </row>
     <row r="1867">
@@ -44498,10 +44498,10 @@
         <v>0.5449271854718107</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.8204341290151209</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.674885521739814</v>
+        <v>2.626618216283616</v>
       </c>
     </row>
     <row r="1868">
@@ -44521,10 +44521,10 @@
         <v>0.4037233427602986</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.8204341290151209</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.670985086885509</v>
+        <v>2.622717781429312</v>
       </c>
     </row>
     <row r="1869">
@@ -44544,10 +44544,10 @@
         <v>0.3828471359183618</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.8204341290151209</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.669390006940509</v>
+        <v>2.621122701484313</v>
       </c>
     </row>
     <row r="1870">
@@ -44567,10 +44567,10 @@
         <v>0.2679615751234912</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.8087317556553376</v>
+        <v>-0.8891772647489995</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.631923101429391</v>
+        <v>2.583655795973193</v>
       </c>
     </row>
     <row r="1871">
@@ -44590,10 +44590,10 @@
         <v>0.1892473872653668</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.8087317556553376</v>
+        <v>-0.8891772647489995</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.627896796894988</v>
+        <v>2.57962949143879</v>
       </c>
     </row>
     <row r="1872">
@@ -44613,10 +44613,10 @@
         <v>0.03594473044673041</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.8087317556553376</v>
+        <v>-0.8891772647489995</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.627794695573404</v>
+        <v>2.579527390117206</v>
       </c>
     </row>
     <row r="1873">
@@ -44636,10 +44636,10 @@
         <v>0.03672166833760526</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.8132182008567264</v>
+        <v>-0.8936637099503881</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.627674344424</v>
+        <v>2.579407038967803</v>
       </c>
     </row>
     <row r="1874">
@@ -44659,10 +44659,10 @@
         <v>-0.1017401573659455</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.8132182008567264</v>
+        <v>-0.8936637099503881</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.63302464772205</v>
+        <v>2.584757342265854</v>
       </c>
     </row>
     <row r="1875">
@@ -44682,10 +44682,10 @@
         <v>-0.1139637627904571</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.8635672643109484</v>
+        <v>-0.9440127734046102</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.610731229606695</v>
+        <v>2.562463924150498</v>
       </c>
     </row>
     <row r="1876">
@@ -44705,10 +44705,10 @@
         <v>-0.1499697231372465</v>
       </c>
       <c r="F1876" t="n">
-        <v>-0.9611865417323451</v>
+        <v>-1.041632050826007</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.555201413775626</v>
+        <v>2.506934108319429</v>
       </c>
     </row>
     <row r="1877">
@@ -44728,10 +44728,10 @@
         <v>-0.168704766619018</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.015258041240704</v>
+        <v>-1.095703550334366</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.525652070392182</v>
+        <v>2.477384764935985</v>
       </c>
     </row>
     <row r="1878">
@@ -44751,10 +44751,10 @@
         <v>-0.2448948396323209</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.142896985854693</v>
+        <v>-1.223342494948355</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.454581900742431</v>
+        <v>2.406314595286234</v>
       </c>
     </row>
     <row r="1879">
@@ -44774,10 +44774,10 @@
         <v>-0.2538734205512743</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.243310353771731</v>
+        <v>-1.323755862865393</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.398816434476645</v>
+        <v>2.350549129020448</v>
       </c>
     </row>
     <row r="1880">
@@ -44797,10 +44797,10 @@
         <v>-0.2091137863908736</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.169840522104282</v>
+        <v>-1.250286031197944</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.458270034970535</v>
+        <v>2.410002729514338</v>
       </c>
     </row>
     <row r="1881">
@@ -44820,10 +44820,10 @@
         <v>-0.264608332597974</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.344964939490826</v>
+        <v>-1.425410448584488</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.367750605286126</v>
+        <v>2.319483299829928</v>
       </c>
     </row>
     <row r="1882">
@@ -44843,10 +44843,10 @@
         <v>-0.3656083351053661</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.344964939490826</v>
+        <v>-1.425410448584488</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.36053144038453</v>
+        <v>2.312264134928332</v>
       </c>
     </row>
     <row r="1883">
@@ -44866,10 +44866,10 @@
         <v>-0.4140304182899208</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.449339670517272</v>
+        <v>-1.529785179610934</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.291234410994686</v>
+        <v>2.242967105538489</v>
       </c>
     </row>
     <row r="1884">
@@ -44889,10 +44889,10 @@
         <v>-0.477920014730798</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.546973100935959</v>
+        <v>-1.627418610029621</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.23377014258203</v>
+        <v>2.185502837125833</v>
       </c>
     </row>
     <row r="1885">
@@ -44912,10 +44912,10 @@
         <v>-0.5256410034489991</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.521721478126216</v>
+        <v>-1.602166987219878</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.25161484489699</v>
+        <v>2.203347539440793</v>
       </c>
     </row>
     <row r="1886">
@@ -44935,10 +44935,10 @@
         <v>-0.4988219590042262</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.521721478126216</v>
+        <v>-1.602166987219878</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.255605180583391</v>
+        <v>2.207337875127194</v>
       </c>
     </row>
     <row r="1887">
@@ -44958,10 +44958,10 @@
         <v>-0.556965922592616</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.521721478126216</v>
+        <v>-1.602166987219878</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.254129953684649</v>
+        <v>2.205862648228452</v>
       </c>
     </row>
     <row r="1888">
@@ -44981,10 +44981,10 @@
         <v>-0.5220761746578098</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.472130633701382</v>
+        <v>-1.552576142795044</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.298937870504422</v>
+        <v>2.250670565048225</v>
       </c>
     </row>
     <row r="1889">
@@ -45004,10 +45004,10 @@
         <v>-0.4755599745157504</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.440881042966209</v>
+        <v>-1.521326552059871</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.304636491298843</v>
+        <v>2.256369185842646</v>
       </c>
     </row>
     <row r="1890">
@@ -45027,10 +45027,10 @@
         <v>-0.3756428403917771</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.398954367379046</v>
+        <v>-1.479399876472708</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.33937156968735</v>
+        <v>2.291104264231152</v>
       </c>
     </row>
     <row r="1891">
@@ -45050,10 +45050,10 @@
         <v>-0.3246722333006811</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.398954367379046</v>
+        <v>-1.479399876472708</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.340510714243409</v>
+        <v>2.292243408787211</v>
       </c>
     </row>
     <row r="1892">
@@ -45073,10 +45073,10 @@
         <v>-0.3431965743562881</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.393999021290599</v>
+        <v>-1.474444530384261</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.346117696058584</v>
+        <v>2.297850390602387</v>
       </c>
     </row>
     <row r="1893">
@@ -45096,10 +45096,10 @@
         <v>-0.3086096000024994</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.393999021290599</v>
+        <v>-1.474444530384261</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.351851400297221</v>
+        <v>2.303584094841023</v>
       </c>
     </row>
     <row r="1894">
@@ -45119,10 +45119,10 @@
         <v>-0.2898003053525056</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.403078137774614</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.384933973469144</v>
+        <v>2.336666668012947</v>
       </c>
     </row>
     <row r="1895">
@@ -45142,10 +45142,10 @@
         <v>-0.2623001730713233</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.403078137774614</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.375050492156237</v>
+        <v>2.326783186700039</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.490679767185721</v>
+        <v>-8.496857907430027</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2298328223226025</v>
+        <v>-0.2323040784203245</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.403078137774614</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.373215931656863</v>
+        <v>2.324948626200666</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.392772728509231</v>
+        <v>-8.398950868753536</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1909703218254672</v>
+        <v>-0.1934415779231893</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.254646878820395</v>
+        <v>-1.335092387914057</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.413707066599736</v>
+        <v>2.365439761143539</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.368819187533273</v>
+        <v>-8.374997327777578</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1807203992895903</v>
+        <v>-0.1831916553873123</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.230693337844438</v>
+        <v>-1.3111388469381</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.428747697330804</v>
+        <v>2.380480391874607</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.104759249210476</v>
+        <v>-8.110937389454781</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.08835674012222361</v>
+        <v>-0.09082799621994564</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.9666333995216414</v>
+        <v>-1.047078908615303</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.57392334416273</v>
+        <v>2.525656038706532</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.397679625705638</v>
+        <v>-7.403857765949943</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1916880756194108</v>
+        <v>0.1892168195216888</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.9666333995216414</v>
+        <v>-1.047078908615303</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.571136310502429</v>
+        <v>2.522869005046231</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.357495327339447</v>
+        <v>-7.363673467583753</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2081054188537284</v>
+        <v>0.2056341627560063</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.9264491011554506</v>
+        <v>-1.006894610249113</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.595590513409984</v>
+        <v>2.547323207953787</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.194095456400085</v>
+        <v>-7.20027359664439</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2728321884502303</v>
+        <v>0.2703609323525082</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.7630492302160882</v>
+        <v>-0.8434947393097501</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.692997257194359</v>
+        <v>2.644729951738161</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.960614234170486</v>
+        <v>-6.966792374414791</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3741491061799218</v>
+        <v>0.3716778500821998</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5295680079864896</v>
+        <v>-0.6100135170801515</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.841010419369971</v>
+        <v>2.792743113913773</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.810947843162971</v>
+        <v>-6.817125983407276</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.431123452269969</v>
+        <v>0.4286521961722469</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.4366645167439537</v>
+        <v>-0.5171100258376156</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.893860303802533</v>
+        <v>2.845592998346336</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.678672369532085</v>
+        <v>-6.68485050977639</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4794011284693505</v>
+        <v>0.4769298723716284</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.304389043113067</v>
+        <v>-0.3848345522067289</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.968593074728092</v>
+        <v>2.920325769271895</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.522934036972343</v>
+        <v>-6.529112177216648</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5445115221808838</v>
+        <v>0.5420402660831618</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1486507105533255</v>
+        <v>-0.2290962196469873</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.064851134951573</v>
+        <v>3.016583829495376</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.437969370243023</v>
+        <v>-6.444147510487328</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5914037300962707</v>
+        <v>0.5889324739985486</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.06368604382400589</v>
+        <v>-0.1441315529176678</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.128736276212824</v>
+        <v>3.080468970756627</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.543559360016127</v>
+        <v>-6.549737500260433</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.42119180458781</v>
+        <v>0.418720548490088</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.1692760335971102</v>
+        <v>-0.2497215426907721</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.937406352749742</v>
+        <v>2.889139047293545</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.4753247753907</v>
+        <v>-6.481502915635005</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4970299803150677</v>
+        <v>0.4945587242173453</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1508607107245742</v>
+        <v>-0.2313062198182361</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.99699988835035</v>
+        <v>2.948732582894154</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.3273847339831</v>
+        <v>-6.333562874227406</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4363270741899399</v>
+        <v>0.4338558180922174</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1305397948160167</v>
+        <v>-0.2109853039096786</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.889313515207317</v>
+        <v>2.84104620975112</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.274415211729112</v>
+        <v>-6.280593351973417</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.448800896838057</v>
+        <v>0.446329640740335</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.1580157816556897</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.912381242306233</v>
+        <v>2.864113936850035</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.108627015768821</v>
+        <v>-6.114805156013126</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.50815556312708</v>
+        <v>0.505684307029358</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.1580157816556897</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.90542063021114</v>
+        <v>2.857153324754942</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.075263809290052</v>
+        <v>-6.081441949534358</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5359632000997308</v>
+        <v>0.5334919440020087</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.1580157816556897</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.919882984592283</v>
+        <v>2.871615679136085</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.967004672167531</v>
+        <v>-5.973182812411836</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5737989754079345</v>
+        <v>0.5713277193102124</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.1580157816556897</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.914415105051478</v>
+        <v>2.86614779959528</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.8437135373504</v>
+        <v>-5.849891677594705</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6206135233453636</v>
+        <v>0.6181422672476415</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.04572086225510269</v>
+        <v>-0.03472464683855919</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.985887879952333</v>
+        <v>2.937620574496135</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.791016670219109</v>
+        <v>-5.797194810463414</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6493932484352052</v>
+        <v>0.6469219923374832</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.09841772938639387</v>
+        <v>0.01797222029273199</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.025206978468433</v>
+        <v>2.976939673012235</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.547251228235664</v>
+        <v>-5.55342936847997</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7426801335756337</v>
+        <v>0.7402088774779116</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.09841772938639387</v>
+        <v>0.01797222029273199</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.020987686815483</v>
+        <v>2.972720381359286</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.457475555859192</v>
+        <v>-5.463653696103497</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7807147164462385</v>
+        <v>0.7782434603485164</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.07957166520704201</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.060071667684086</v>
+        <v>3.011804362227888</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.207625161910117</v>
+        <v>-5.213803302154423</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8733969490095705</v>
+        <v>0.8709256929118485</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.07957166520704201</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.052813742667788</v>
+        <v>3.00454643721159</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.031733069442685</v>
+        <v>-5.037911209686991</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9473529095171922</v>
+        <v>0.9448816534194702</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.07957166520704201</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.056412866188436</v>
+        <v>3.008145560732239</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.860286606420222</v>
+        <v>-4.866464746664527</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.029259000780731</v>
+        <v>1.026787744683009</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.331463637323167</v>
+        <v>0.2510181282295051</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.172608250056468</v>
+        <v>3.124340944600271</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.780264319311101</v>
+        <v>-4.786442459555406</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.060288393240677</v>
+        <v>1.057817137142955</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.411485924432288</v>
+        <v>0.3310404153386261</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.219642099938238</v>
+        <v>3.17137479448204</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.716628577077167</v>
+        <v>-4.722806717321472</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.090437491188568</v>
+        <v>1.087966235090846</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4751216666662225</v>
+        <v>0.3946761575725606</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.262518346332915</v>
+        <v>3.214251040876718</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.622931258860771</v>
+        <v>-4.629109399105077</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.109110677258921</v>
+        <v>1.106639421161199</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4751216666662225</v>
+        <v>0.3946761575725606</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.243712605116711</v>
+        <v>3.195445299660514</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.63343388192606</v>
+        <v>-4.639612022170366</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.106652704657683</v>
+        <v>1.104181448559961</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4646190436009336</v>
+        <v>0.3841735345072718</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.239154107902415</v>
+        <v>3.190886802446218</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.561191313754866</v>
+        <v>-4.567369453999171</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.139479045760981</v>
+        <v>1.137007789663259</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4646190436009336</v>
+        <v>0.3841735345072718</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.243083421737235</v>
+        <v>3.194816116281038</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.543477626877</v>
+        <v>-4.549655767121306</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.147243104429467</v>
+        <v>1.144771848331745</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4678003724978504</v>
+        <v>0.3873548634041886</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.245670802992725</v>
+        <v>3.197403497536528</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.434672741397273</v>
+        <v>-4.440850881641579</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.187763129841352</v>
+        <v>1.18529187374363</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4678003724978504</v>
+        <v>0.3873548634041886</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.242668874212719</v>
+        <v>3.194401568756521</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.214651943360263</v>
+        <v>-4.220830083604568</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.27735048606677</v>
+        <v>1.274879229969048</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.6090202175658307</v>
+        <v>0.5285747084721688</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.328979818264121</v>
+        <v>3.280712512807924</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.081784254296985</v>
+        <v>-4.08796239454129</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.346391744493904</v>
+        <v>1.343920488396182</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.6090202175658307</v>
+        <v>0.5285747084721688</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.344874001065945</v>
+        <v>3.296606695609747</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.961611170932486</v>
+        <v>-3.967789311176792</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.395606822280006</v>
+        <v>1.393135566182284</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7291933009303296</v>
+        <v>0.6487477918366678</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.418123695524946</v>
+        <v>3.369856390068748</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.826357809602509</v>
+        <v>-3.832535949846815</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.459796269373437</v>
+        <v>1.457325013275714</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8644466622603068</v>
+        <v>0.7840011531666449</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.509363814884372</v>
+        <v>3.461096509428175</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.886232636960202</v>
+        <v>-3.892410777204507</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.421883829831785</v>
+        <v>1.419412573734063</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.8045718349026146</v>
+        <v>0.7241263258089528</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.459476409871182</v>
+        <v>3.411209104414985</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.766412406049364</v>
+        <v>-3.77259054629367</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.485101091430329</v>
+        <v>1.482629835332607</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.8045718349026146</v>
+        <v>0.7241263258089528</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.474765579105391</v>
+        <v>3.426498273649194</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.76888211251117</v>
+        <v>-3.775060252755476</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.391757408168048</v>
+        <v>1.389286152070326</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.8021021284408085</v>
+        <v>0.7216566193471466</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.380927954550749</v>
+        <v>3.332660649094552</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.83725229883518</v>
+        <v>-3.843430439079485</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.283671195123746</v>
+        <v>1.281199939026023</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.7309323183833616</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.305755235457779</v>
+        <v>3.257487930001582</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.851040351682227</v>
+        <v>-3.857218491926532</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.268592682616818</v>
+        <v>1.266121426519096</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.7309323183833616</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.29619194408967</v>
+        <v>3.247924638633473</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.906560427574816</v>
+        <v>-3.912738567819122</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.383415488951985</v>
+        <v>1.380944232854262</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.7309323183833616</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.433222780781873</v>
+        <v>3.384955475325675</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.731086167782347</v>
+        <v>-3.737264308026652</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.45817242486076</v>
+        <v>1.455701168763038</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.7309323183833616</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.43779001277366</v>
+        <v>3.389522707317463</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.842022420423596</v>
+        <v>-3.848200560667901</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.389539952565468</v>
+        <v>1.387068696467746</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.7309323183833616</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.413532041534868</v>
+        <v>3.36526473607867</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.808358874951314</v>
+        <v>-3.814537015195619</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.33154368415583</v>
+        <v>1.329072428058108</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8450413729493054</v>
+        <v>0.7645958638556435</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.362268482219687</v>
+        <v>3.314001176763489</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.748506255747591</v>
+        <v>-3.754684395991896</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.365657118269452</v>
+        <v>1.36318586217173</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8450413729493054</v>
+        <v>0.7645958638556435</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.372440868651819</v>
+        <v>3.324173563195622</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.662262792721213</v>
+        <v>-3.668440932965519</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.395100774053863</v>
+        <v>1.392629517956141</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8450413729493054</v>
+        <v>0.7645958638556435</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.367387139225679</v>
+        <v>3.319119833769482</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.707569612120193</v>
+        <v>-3.713747752364498</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.368753821738797</v>
+        <v>1.366282565641075</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.8042312099400746</v>
+        <v>0.7237857008464127</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.334676816864667</v>
+        <v>3.286409511408469</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.736602716822495</v>
+        <v>-3.7427808570668</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.357692452890978</v>
+        <v>1.355221196793256</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.8042312099400746</v>
+        <v>0.7237857008464127</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.335228689897768</v>
+        <v>3.286961384441571</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.643792235371635</v>
+        <v>-3.649970375615941</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.324089337362687</v>
+        <v>1.321618081264965</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8970416913909339</v>
+        <v>0.816596182297272</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.320187670659649</v>
+        <v>3.271920365203452</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.688181704701063</v>
+        <v>-3.694359844945368</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.308207025555517</v>
+        <v>1.305735769457795</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8526522220615063</v>
+        <v>0.7722067129678444</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.295427464986593</v>
+        <v>3.247160159530396</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.804723309806406</v>
+        <v>-3.810901450050711</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.256666092025103</v>
+        <v>1.254194835927381</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7361106169561635</v>
+        <v>0.6556651078625017</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.220578210435111</v>
+        <v>3.172310904978914</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.844647404388978</v>
+        <v>-3.850825544633283</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.246187750022741</v>
+        <v>1.243716493925019</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7361106169561635</v>
+        <v>0.6556651078625017</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.226069506265778</v>
+        <v>3.177802200809581</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.872427802290331</v>
+        <v>-3.878605942534636</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.246572792630739</v>
+        <v>1.244101536533017</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7083302190548104</v>
+        <v>0.6278847099611485</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.220898469293505</v>
+        <v>3.172631163837308</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.990808475020469</v>
+        <v>-3.996986615264774</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.037576243539337</v>
+        <v>1.035104987441615</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6411123669038342</v>
+        <v>0.5606668578101723</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.018923478003573</v>
+        <v>2.970656172547375</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.0994225534638</v>
+        <v>-4.105600693708105</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.11428027288121</v>
+        <v>1.111809016783488</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6411123669038342</v>
+        <v>0.5606668578101723</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.139073138722778</v>
+        <v>3.090805833266581</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.064013515215657</v>
+        <v>-4.070191655459962</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.14295691428279</v>
+        <v>1.140485658185068</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6411123669038342</v>
+        <v>0.5606668578101723</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.153586164825101</v>
+        <v>3.105318859368904</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.025629852657506</v>
+        <v>-4.031807992901811</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.15572982064842</v>
+        <v>1.153258564550697</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6794960294619854</v>
+        <v>0.5990505203683235</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.174035803702361</v>
+        <v>3.125768498246163</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.84851352262234</v>
+        <v>-4.056420921416271</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.223305381507788</v>
+        <v>1.140142421990215</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6794960294619854</v>
+        <v>0.5990505203683235</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.170764832547663</v>
+        <v>3.122497527091466</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.893605767455885</v>
+        <v>-4.101513166249817</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.205951875336283</v>
+        <v>1.12278891581871</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6175999862925956</v>
+        <v>0.5371544771989337</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.134310598407942</v>
+        <v>3.086043292951745</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.714230346217118</v>
+        <v>-3.92213774501105</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.271489019138204</v>
+        <v>1.188326059620632</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7743767444633143</v>
+        <v>0.6939312353696524</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.222163628616787</v>
+        <v>3.17389632316059</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.759244559737724</v>
+        <v>-3.967151958531656</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.234290789061552</v>
+        <v>1.151127829543979</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7440278491487097</v>
+        <v>0.6635823400550478</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.184761746759615</v>
+        <v>3.136494441303417</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.026249070010159</v>
+        <v>-4.234156468804091</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.133180547291523</v>
+        <v>1.05001758777395</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5496648111057612</v>
+        <v>0.4692193020120992</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.073835486272791</v>
+        <v>3.025568180816594</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.127446851447332</v>
+        <v>-4.335354250241264</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.091905356613155</v>
+        <v>1.008742397095583</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.481255997560442</v>
+        <v>0.40081048846678</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.031994120042101</v>
+        <v>2.983726814585903</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.12093588483302</v>
+        <v>-4.328843283626951</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.092109704813197</v>
+        <v>1.008946745295624</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.481255997560442</v>
+        <v>0.40081048846678</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.029594081596418</v>
+        <v>2.981326776140221</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.101897757125722</v>
+        <v>-4.309805155919654</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.096249675104361</v>
+        <v>1.013086715586788</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4230723862292474</v>
+        <v>0.3426268771355855</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.991208634005946</v>
+        <v>2.942941328549749</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.154413559400543</v>
+        <v>-4.362320958194474</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.194537755828623</v>
+        <v>1.111374796311051</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4230723862292474</v>
+        <v>0.3426268771355855</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.110503035640136</v>
+        <v>3.062235730183939</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.168280320734461</v>
+        <v>-4.376187719528392</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.18982438028119</v>
+        <v>1.106661420763617</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3852144694954245</v>
+        <v>0.3047689604017625</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.088621614585976</v>
+        <v>3.040354309129779</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.123476149194531</v>
+        <v>-4.331383547988462</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.213754579294088</v>
+        <v>1.130591619776515</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3852144694954245</v>
+        <v>0.3047689604017625</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.094630144982902</v>
+        <v>3.046362839526705</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.975733178959528</v>
+        <v>-4.18364057775346</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.170801988665288</v>
+        <v>1.087639029147715</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5530218267303076</v>
+        <v>0.4725763176366457</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.093264780601031</v>
+        <v>3.044997475144834</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.059554400234227</v>
+        <v>-4.267461799028158</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.14006712168689</v>
+        <v>1.056904162169317</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5530218267303076</v>
+        <v>0.4725763176366457</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.096058402132512</v>
+        <v>3.047791096676315</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.053401694181442</v>
+        <v>-4.261309092975374</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.143190552499662</v>
+        <v>1.060027592982089</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5591745327830919</v>
+        <v>0.47872902368943</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.100412374155841</v>
+        <v>3.052145068699644</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.070210992331944</v>
+        <v>-4.278118391125876</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.135547309979571</v>
+        <v>1.052384350461999</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5423652346325902</v>
+        <v>0.4619197255389283</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.08940727200565</v>
+        <v>3.041139966549453</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.007912993555822</v>
+        <v>-4.215820392349753</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.226802063286841</v>
+        <v>1.143639103769268</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5876594989070323</v>
+        <v>0.5072139898133704</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.182919384367136</v>
+        <v>3.13465207891094</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.806122795890664</v>
+        <v>-4.014030194684596</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.109810144067031</v>
+        <v>1.026647184549458</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7856776910761867</v>
+        <v>0.7052321819825248</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.104022301382756</v>
+        <v>3.055754995926559</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.857009508576859</v>
+        <v>-4.06491690737079</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.159745691314728</v>
+        <v>1.076582731797156</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7347909783899922</v>
+        <v>0.6543454692963303</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.143780506093215</v>
+        <v>3.095513200637018</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.770398765927051</v>
+        <v>-3.978306164720983</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.209017724490695</v>
+        <v>1.125854764973123</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8134167095951504</v>
+        <v>0.7329712005014886</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.205583680932353</v>
+        <v>3.157316375476156</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.830608063932336</v>
+        <v>-4.038515462726267</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.183469986113253</v>
+        <v>1.10030702659568</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7532074115898659</v>
+        <v>0.672761902496204</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.167994082953854</v>
+        <v>3.119726777497657</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.754186017500409</v>
+        <v>-3.962093416294341</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.212530422725952</v>
+        <v>1.12936746320838</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7532074115898659</v>
+        <v>0.672761902496204</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.166485700993783</v>
+        <v>3.118218395537586</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.70981288586184</v>
+        <v>-3.917720284655772</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.230142542816816</v>
+        <v>1.146979583299243</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7975805432284345</v>
+        <v>0.7171350341347726</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.19297244741236</v>
+        <v>3.144705141956163</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.732293236720725</v>
+        <v>-3.940200635514657</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.215544196611852</v>
+        <v>1.13238123709428</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7975805432284345</v>
+        <v>0.7171350341347726</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.187366241550951</v>
+        <v>3.139098936094753</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.68463750615967</v>
+        <v>-3.892544904953601</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.240988245864079</v>
+        <v>1.157825286346507</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8452362737894902</v>
+        <v>0.7647907646958283</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.222341436915389</v>
+        <v>3.174074131459192</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.584119347660915</v>
+        <v>-3.792026746454846</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.286087882638306</v>
+        <v>1.202924923120734</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9457544322882447</v>
+        <v>0.8653089231945829</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.287544705389366</v>
+        <v>3.239277399933169</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.568214018228562</v>
+        <v>-3.776121417022494</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.279204686887119</v>
+        <v>1.196041727369547</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8666417715790058</v>
+        <v>0.7861962624853439</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.226831781439695</v>
+        <v>3.178564475983498</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.523375616620164</v>
+        <v>-3.731283015414096</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.301237750141107</v>
+        <v>1.218074790623535</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8711852045238753</v>
+        <v>0.7907396954302134</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.233655543817246</v>
+        <v>3.185388238361048</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.542874072862173</v>
+        <v>-3.750781471656104</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.297599307275382</v>
+        <v>1.214436347757809</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.823100563243971</v>
+        <v>0.7426550541503091</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.208965698680381</v>
+        <v>3.160698393224184</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.498671235776272</v>
+        <v>-3.706578634570203</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.321160044637579</v>
+        <v>1.237997085120007</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8673034003298714</v>
+        <v>0.7868578912362095</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.241367003459758</v>
+        <v>3.193099698003561</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.506230901613319</v>
+        <v>-3.71413830040725</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.316546178772008</v>
+        <v>1.233383219254435</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9221068043396907</v>
+        <v>0.8416612952460288</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.272659046334898</v>
+        <v>3.2243917408787</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.347939484074047</v>
+        <v>-3.555846882867978</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.431110510970756</v>
+        <v>1.347947551453184</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9221068043396907</v>
+        <v>0.8416612952460288</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.323906811517937</v>
+        <v>3.27563950606174</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.140297480439571</v>
+        <v>-3.348204879233502</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.5126080170188</v>
+        <v>1.429445057501228</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.129748807974167</v>
+        <v>1.049303298880505</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.446932718292876</v>
+        <v>3.398665412836679</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.089265387717043</v>
+        <v>-3.297172786510974</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.527969082346081</v>
+        <v>1.444806122828509</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.180780900696695</v>
+        <v>1.100335391603033</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.472500202164663</v>
+        <v>3.424232896708466</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.024041206589837</v>
+        <v>-3.231948605383768</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.571246158889668</v>
+        <v>1.488083199372096</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.246005081823901</v>
+        <v>1.165559572730239</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.528822114933691</v>
+        <v>3.480554809477494</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.986614186518703</v>
+        <v>-3.194521585312634</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.582177939217402</v>
+        <v>1.49901497969983</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.251256619853082</v>
+        <v>1.17081111075942</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.527934010050481</v>
+        <v>3.479666704594283</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.006725842553411</v>
+        <v>-3.214633241347343</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.575390069134759</v>
+        <v>1.492227109617187</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.262283964850502</v>
+        <v>1.18183845575684</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.535807209380172</v>
+        <v>3.487539903923975</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.952981028126207</v>
+        <v>-3.160888426920138</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.757445765926852</v>
+        <v>1.67428280640928</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.272347274290964</v>
+        <v>1.191901765197302</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.702402966065661</v>
+        <v>3.654135660609463</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.878198767101194</v>
+        <v>-3.086106165895125</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.907471579554674</v>
+        <v>1.824308620037102</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.347129535315976</v>
+        <v>1.266684026222314</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.867385231898485</v>
+        <v>3.819117926442288</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.852114682837386</v>
+        <v>-3.060022081631317</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.909613189274056</v>
+        <v>1.826450229756484</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.347129535315976</v>
+        <v>1.266684026222314</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.859093207912344</v>
+        <v>3.810825902456147</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.764236769728265</v>
+        <v>-2.972144168522197</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.942957550101484</v>
+        <v>1.859794590583912</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.463055177739327</v>
+        <v>1.382609668645665</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.926841788950134</v>
+        <v>3.878574483493937</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.755344308334982</v>
+        <v>-2.963251707128913</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.964068940385589</v>
+        <v>1.880905980868016</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.463055177739327</v>
+        <v>1.382609668645665</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.944396194676925</v>
+        <v>3.896128889220729</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.92382042530486</v>
+        <v>-3.131727824098791</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.888533541002222</v>
+        <v>1.805370581484649</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.435107342022747</v>
+        <v>1.354661832929085</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.919482540651561</v>
+        <v>3.871215235195364</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.47756423267542</v>
+        <v>-2.685471631469351</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.04830571524186</v>
+        <v>1.965142755724287</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.340388672353114</v>
+        <v>1.259943163259452</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.843921036037643</v>
+        <v>3.795653730581446</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.454843128992267</v>
+        <v>-2.662750527786199</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.048058179212025</v>
+        <v>1.964895219694453</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.340388672353114</v>
+        <v>1.259943163259452</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.834585058534548</v>
+        <v>3.786317753078351</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.58404494228631</v>
+        <v>-2.791952341080241</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.155283579745577</v>
+        <v>2.072120620228005</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.211186859059072</v>
+        <v>1.13074134996541</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.915970096409292</v>
+        <v>3.867702790953095</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.738825949064565</v>
+        <v>-2.946733347858497</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.130448999527921</v>
+        <v>2.047286040010349</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.177819185004596</v>
+        <v>1.097373675910934</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.933027314470253</v>
+        <v>3.884760009014055</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.731771258849392</v>
+        <v>-2.939678657643323</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.129946231603536</v>
+        <v>2.046783272085964</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.184873875219769</v>
+        <v>1.104428366126107</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.933935484588902</v>
+        <v>3.885668179132705</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.704820034522904</v>
+        <v>-2.912727433316835</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.150732874978873</v>
+        <v>2.0675699154613</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.199754221247489</v>
+        <v>1.119308712153827</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.952869845850275</v>
+        <v>3.904602540394078</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.84077304257922</v>
+        <v>-3.048680441373151</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.280454803901306</v>
+        <v>2.197291844383733</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.199754221247489</v>
+        <v>1.119308712153827</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.136972977995235</v>
+        <v>4.088705672539038</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.863181160384092</v>
+        <v>-3.071088559178023</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.26360825168235</v>
+        <v>2.180445292164778</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.199754221247489</v>
+        <v>1.119308712153827</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.129089672898228</v>
+        <v>4.080822367442031</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.891405395961693</v>
+        <v>-3.099312794755624</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.254372557000948</v>
+        <v>2.171209597483375</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.217730973698797</v>
+        <v>1.137285464605135</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.141929723918651</v>
+        <v>4.093662418462453</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.900846321850223</v>
+        <v>-3.108753720644154</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.306849904367382</v>
+        <v>2.22368694484981</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.340158091242189</v>
+        <v>1.259712582148527</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.271639712166532</v>
+        <v>4.223372406710335</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.953119929185864</v>
+        <v>-3.161027327979795</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.288831555978427</v>
+        <v>2.205668596460855</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.287884483906547</v>
+        <v>1.207438974812885</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.243166642310449</v>
+        <v>4.194899336854252</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.02944990678677</v>
+        <v>-3.237357305580701</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.25641137783184</v>
+        <v>2.173248418314268</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.287884483906547</v>
+        <v>1.207438974812885</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.241278455204224</v>
+        <v>4.193011149748027</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.231703627111123</v>
+        <v>-3.439611025905054</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.170330119304961</v>
+        <v>2.087167159787389</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.085630763582194</v>
+        <v>1.005185254488532</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.114746452612474</v>
+        <v>4.066479147156277</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.393272052638378</v>
+        <v>-3.601179451432309</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.104136759304211</v>
+        <v>2.020973799786639</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9588478397843144</v>
+        <v>0.8784023306906524</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.037110708543898</v>
+        <v>3.988843403087701</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.525573344735931</v>
+        <v>-3.733480743529863</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.064289649331108</v>
+        <v>1.981126689813536</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9588478397843144</v>
+        <v>0.8784023306906524</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.050184115409817</v>
+        <v>4.00191680995362</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.711441655575161</v>
+        <v>-3.919349054369093</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.981947521778356</v>
+        <v>1.898784562260784</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8002822464643667</v>
+        <v>0.7198367373707047</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.947049956200789</v>
+        <v>3.898782650744591</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.739342442684634</v>
+        <v>-3.947249841478566</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.969311248061569</v>
+        <v>1.886148288543997</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7656853223214319</v>
+        <v>0.6852398132277699</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.92481584284203</v>
+        <v>3.876548537385832</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.861868545387528</v>
+        <v>-4.06977594418146</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.91706525095761</v>
+        <v>1.833902291440038</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6431592196185381</v>
+        <v>0.5627137105248761</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.848064625197492</v>
+        <v>3.799797319741295</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.092383041573116</v>
+        <v>-4.300290440367049</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.891565412073879</v>
+        <v>1.808402452556306</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4126447234329493</v>
+        <v>0.3321992143392873</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.776461887076643</v>
+        <v>3.728194581620445</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.349103859567941</v>
+        <v>-4.557011258361873</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.929188803877796</v>
+        <v>1.846025844360223</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.2237846401954725</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.851724861592201</v>
+        <v>3.803457556136004</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.503090277344081</v>
+        <v>-4.710997676138014</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.936574505912979</v>
+        <v>1.853411546395407</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.2237846401954725</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.920705130737841</v>
+        <v>3.872437825281644</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.452568373516415</v>
+        <v>-4.660475772310348</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.942834469564167</v>
+        <v>1.859671510046594</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.2237846401954725</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.906756332857962</v>
+        <v>3.858489027401764</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.70504352752414</v>
+        <v>-4.912950926318072</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.853714897016491</v>
+        <v>1.770551937498918</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.2237846401954725</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.918626821913375</v>
+        <v>3.870359516457178</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.997939284003552</v>
+        <v>-5.100588481456414</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.73776712894367</v>
+        <v>1.696707449962525</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.2237846401954725</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.919837356432319</v>
+        <v>3.871570050976122</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.155483355732994</v>
+        <v>-5.258132553185855</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.678871242479214</v>
+        <v>1.637811563498071</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.23732834414886</v>
+        <v>0.156882835055198</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.883818015575476</v>
+        <v>3.835550710119279</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.433447751316267</v>
+        <v>-5.536096948769129</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.562763336982095</v>
+        <v>1.52170365800095</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1477086098633758</v>
+        <v>0.06726310076971376</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.825124027740375</v>
+        <v>3.776856722284178</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.550415443955158</v>
+        <v>-5.65306464140802</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.678180316625582</v>
+        <v>1.637120637644438</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1477086098633758</v>
+        <v>0.06726310076971376</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.987328084439419</v>
+        <v>3.939060778983221</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.635133386176111</v>
+        <v>-5.737782583628973</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.639139777701015</v>
+        <v>1.598080098719871</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.06259258093532938</v>
+        <v>-0.01785292815833261</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.931105105046405</v>
+        <v>3.882837799590208</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.717068204444995</v>
+        <v>-5.819717401897856</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.616595267961953</v>
+        <v>1.575535588980809</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.05265783534824919</v>
+        <v>-0.0277876737454128</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.935373675262649</v>
+        <v>3.887106369806451</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.819044326693402</v>
+        <v>-5.921693524146264</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.584730457518492</v>
+        <v>1.543670778537348</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.04931828690015838</v>
+        <v>-0.1297637959938204</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.883113640369506</v>
+        <v>3.834846334913309</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.70903804321618</v>
+        <v>-5.811687240669042</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.620885858153557</v>
+        <v>1.579826179172412</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.02611371498288317</v>
+        <v>-0.1065592240765452</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.889189270764047</v>
+        <v>3.840921965307849</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.565978467475255</v>
+        <v>-5.668627664928117</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.682359699171901</v>
+        <v>1.641300020190757</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.0181002883929039</v>
+        <v>-0.09854579748656589</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.898247337440008</v>
+        <v>3.849980031983812</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.264531742003418</v>
+        <v>-5.367180939456279</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.810199272243172</v>
+        <v>1.769139593262028</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2833464370789334</v>
+        <v>0.2029009279852714</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.086376255605647</v>
+        <v>4.03810895014945</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.289121986238602</v>
+        <v>-5.391771183691463</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.801334352301809</v>
+        <v>1.760274673320665</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2833464370789334</v>
+        <v>0.2029009279852714</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.087347433358357</v>
+        <v>4.03908012790216</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.238083610232081</v>
+        <v>-5.340732807684943</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.822592607084172</v>
+        <v>1.781532928103028</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2833464370789334</v>
+        <v>0.2029009279852714</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.088190337738113</v>
+        <v>4.039923032281916</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.19694431536545</v>
+        <v>-5.299593512818312</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.85808642390497</v>
+        <v>1.817026744923826</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3244857319455642</v>
+        <v>0.2440402228519022</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.131912013532236</v>
+        <v>4.083644708076039</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.086338175285849</v>
+        <v>-5.18898737273871</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.718512876060745</v>
+        <v>1.677453197079601</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4350918720251662</v>
+        <v>0.3546463629315042</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.014459693703932</v>
+        <v>3.966192388247735</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.216918909816691</v>
+        <v>-5.319568107269553</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.669782626322372</v>
+        <v>1.628722947341228</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3045111374943237</v>
+        <v>0.2240656284006617</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.939613297059391</v>
+        <v>3.891345991603193</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.052422575625729</v>
+        <v>-5.155071773078591</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.720007979074839</v>
+        <v>1.678948300093695</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3045111374943237</v>
+        <v>0.2240656284006617</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.924040116135473</v>
+        <v>3.875772810679276</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.079792508310161</v>
+        <v>-5.182441705763023</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.708247716437496</v>
+        <v>1.667188037456352</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3045111374943237</v>
+        <v>0.2240656284006617</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.923227826571903</v>
+        <v>3.874960521115705</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.090177703200051</v>
+        <v>-5.192826900652912</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.713962417606613</v>
+        <v>1.672902738625468</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.2941259426044344</v>
+        <v>0.2136804335107724</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.926865488763042</v>
+        <v>3.878598183306845</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.108765861922276</v>
+        <v>-5.211415059375137</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.777364159894148</v>
+        <v>1.736304480913004</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.275537783882209</v>
+        <v>0.195092274788547</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.986549599306132</v>
+        <v>3.938282293849935</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.109064408618312</v>
+        <v>-5.211713606071173</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.774113752034032</v>
+        <v>1.733054073052888</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.275537783882209</v>
+        <v>0.195092274788547</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.98341861012443</v>
+        <v>3.935151304668233</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.008241274927884</v>
+        <v>-5.110890472380746</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.818973900449595</v>
+        <v>1.77791422146845</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.2880019993665628</v>
+        <v>0.2075564902729009</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.995428034354433</v>
+        <v>3.947160728898236</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.817459914175477</v>
+        <v>-4.920109111628339</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.895415698229101</v>
+        <v>1.854356019247956</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.4787833601189702</v>
+        <v>0.3983378510253082</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.110026104284421</v>
+        <v>4.061758798828224</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.798943060133657</v>
+        <v>-4.901592257586518</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.882659285583425</v>
+        <v>1.841599606602281</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.4917134895441784</v>
+        <v>0.4112679804505164</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.097621027677143</v>
+        <v>4.049353722220946</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.773749875632339</v>
+        <v>-4.8763990730852</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.927703495996011</v>
+        <v>1.886643817014867</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.5169066740454967</v>
+        <v>0.4364611649518348</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.147703874989992</v>
+        <v>4.099436569533795</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.761695748719376</v>
+        <v>-4.864344946172237</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.926211714662634</v>
+        <v>1.885152035681489</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.5289608009584595</v>
+        <v>0.4485152918647976</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.148622919039208</v>
+        <v>4.100355613583011</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.768318995409734</v>
+        <v>-4.870968192862596</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.925443046170626</v>
+        <v>1.884383367189482</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5223375542681012</v>
+        <v>0.4418920451744393</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.146529601209129</v>
+        <v>4.098262295752932</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.665438405881141</v>
+        <v>-4.768087603334003</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.979446307859946</v>
+        <v>1.938386628878802</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6252181437966942</v>
+        <v>0.5447726347030322</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.221108980804167</v>
+        <v>4.17284167534797</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.688880445061228</v>
+        <v>-4.79152964251409</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.990272162361506</v>
+        <v>1.949212483380361</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6252181437966942</v>
+        <v>0.5447726347030322</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.241311650977761</v>
+        <v>4.193044345521564</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.70695295335284</v>
+        <v>-4.809602150805701</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.983043159044861</v>
+        <v>1.941983480063716</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6252181437966942</v>
+        <v>0.5447726347030322</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.241311650977761</v>
+        <v>4.193044345521564</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.938126747229472</v>
+        <v>-5.040775944682333</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.850825555087675</v>
+        <v>1.809765876106531</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6252181437966942</v>
+        <v>0.5447726347030322</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.201563564571228</v>
+        <v>4.153296259115031</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.906840726689016</v>
+        <v>-5.009489924141878</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.870362582300797</v>
+        <v>1.829302903319653</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.6565041643371495</v>
+        <v>0.5760586552434875</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.227357795892441</v>
+        <v>4.179090490436244</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.753815334575732</v>
+        <v>-4.856464532028594</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.030743738719015</v>
+        <v>1.98968405973787</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.8095295564504337</v>
+        <v>0.7290840473567717</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.418344030733316</v>
+        <v>4.370076725277118</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.782122648449002</v>
+        <v>-4.884771845901864</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.206887038077999</v>
+        <v>2.165827359096855</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.8095295564504337</v>
+        <v>0.7290840473567717</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.605810255641608</v>
+        <v>4.557542950185411</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.948715873562525</v>
+        <v>-5.051365071015386</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.109652699386673</v>
+        <v>2.068593020405528</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.6429363313369112</v>
+        <v>0.5624908222432492</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.475257271927576</v>
+        <v>4.426989966471379</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.775651494180225</v>
+        <v>-4.878300691633086</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.18255485380131</v>
+        <v>2.141495174820166</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.6429363313369112</v>
+        <v>0.5624908222432492</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.478933674589294</v>
+        <v>4.430666369133097</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,45 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.858405956600907</v>
+        <v>3.440186952535867</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.746405513724528</v>
+        <v>-4.651714325434441</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.191871301107084</v>
+        <v>2.229747776423119</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.6429363313369112</v>
+        <v>0.5624908222432492</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.476551729712789</v>
+        <v>4.428284424256592</v>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" s="2" t="n">
+        <v>45518</v>
+      </c>
+      <c r="B2056" t="n">
+        <v>4.011536684755269</v>
+      </c>
+      <c r="C2056" t="n">
+        <v>4.235672898969511</v>
+      </c>
+      <c r="D2056" t="n">
+        <v>-4.651714325434441</v>
+      </c>
+      <c r="E2056" t="n">
+        <v>2.229747776423119</v>
+      </c>
+      <c r="F2056" t="n">
+        <v>0.5624908222432492</v>
+      </c>
+      <c r="G2056" t="n">
+        <v>4.228736695955879</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240814.xlsx
+++ b/tame_output/ON/bt/strategyON_20240814.xlsx
@@ -605,17 +605,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>57.4%</t>
         </is>
       </c>
     </row>
@@ -849,22 +849,22 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>78.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.2%</t>
+          <t>-77.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.7%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.5%</t>
+          <t>124.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.7%</t>
+          <t>-47.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.0%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.4%</t>
+          <t>430.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-626.7%</t>
+          <t>-636.2%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.9%</t>
+          <t>-34.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-153.2%</t>
+          <t>-157.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.6%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.9%</t>
+          <t>-26.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-27.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-422.6%</t>
+          <t>-303.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-167.7%</t>
+          <t>-159.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>73.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -44383,10 +44383,10 @@
         <v>1.209489783080714</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.11553456753543</v>
+        <v>-0.03508905844176807</v>
       </c>
       <c r="G1862" t="n">
-        <v>3.048103720401823</v>
+        <v>3.096371025858021</v>
       </c>
     </row>
     <row r="1863">
@@ -44406,10 +44406,10 @@
         <v>1.062693345031047</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.4118453518344425</v>
+        <v>-0.3313998427407806</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.869571764828247</v>
+        <v>2.917839070284444</v>
       </c>
     </row>
     <row r="1864">
@@ -44429,10 +44429,10 @@
         <v>0.8980193781735339</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.8204341290151209</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.623180042534599</v>
+        <v>2.671447347990797</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191732</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44452,10 +44452,10 @@
         <v>0.8477006458358489</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.8204341290151209</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.61836547500606</v>
+        <v>2.666632780462257</v>
       </c>
     </row>
     <row r="1866">
@@ -44475,10 +44475,10 @@
         <v>0.6791379467299272</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.8204341290151209</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.616359525614937</v>
+        <v>2.664626831071135</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097815</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44498,10 +44498,10 @@
         <v>0.5449271854718107</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.8204341290151209</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.626618216283616</v>
+        <v>2.674885521739814</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309411</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44521,10 +44521,10 @@
         <v>0.4037233427602986</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.8204341290151209</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.622717781429312</v>
+        <v>2.670985086885509</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44544,10 +44544,10 @@
         <v>0.3828471359183618</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.8204341290151209</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.621122701484313</v>
+        <v>2.669390006940509</v>
       </c>
     </row>
     <row r="1870">
@@ -44567,10 +44567,10 @@
         <v>0.2679615751234912</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.8891772647489995</v>
+        <v>-0.8087317556553376</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.583655795973193</v>
+        <v>2.631923101429391</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44590,10 +44590,10 @@
         <v>0.1892473872653668</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.8891772647489995</v>
+        <v>-0.8087317556553376</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.57962949143879</v>
+        <v>2.627896796894988</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44613,10 +44613,10 @@
         <v>0.03594473044673041</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.8891772647489995</v>
+        <v>-0.8087317556553376</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.579527390117206</v>
+        <v>2.627794695573404</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44636,10 +44636,10 @@
         <v>0.03672166833760526</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.8936637099503881</v>
+        <v>-0.8132182008567264</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.579407038967803</v>
+        <v>2.627674344424</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737164</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44659,10 +44659,10 @@
         <v>-0.1017401573659455</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.8936637099503881</v>
+        <v>-0.8132182008567264</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.584757342265854</v>
+        <v>2.63302464772205</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341307</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44682,10 +44682,10 @@
         <v>-0.1139637627904571</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.9440127734046102</v>
+        <v>-0.8635672643109484</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.562463924150498</v>
+        <v>2.610731229606695</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44705,10 +44705,10 @@
         <v>-0.1499697231372465</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.041632050826007</v>
+        <v>-0.9611865417323451</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.506934108319429</v>
+        <v>2.555201413775626</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44728,10 +44728,10 @@
         <v>-0.168704766619018</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.095703550334366</v>
+        <v>-1.015258041240704</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.477384764935985</v>
+        <v>2.525652070392182</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44751,10 +44751,10 @@
         <v>-0.2448948396323209</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.223342494948355</v>
+        <v>-1.142896985854693</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.406314595286234</v>
+        <v>2.454581900742431</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44774,10 +44774,10 @@
         <v>-0.2538734205512743</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.323755862865393</v>
+        <v>-1.243310353771731</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.350549129020448</v>
+        <v>2.398816434476645</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44797,10 +44797,10 @@
         <v>-0.2091137863908736</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.250286031197944</v>
+        <v>-1.169840522104282</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.410002729514338</v>
+        <v>2.458270034970535</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44820,10 +44820,10 @@
         <v>-0.264608332597974</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.425410448584488</v>
+        <v>-1.344964939490826</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.319483299829928</v>
+        <v>2.367750605286126</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44843,10 +44843,10 @@
         <v>-0.3656083351053661</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.425410448584488</v>
+        <v>-1.344964939490826</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.312264134928332</v>
+        <v>2.36053144038453</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44866,10 +44866,10 @@
         <v>-0.4140304182899208</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.529785179610934</v>
+        <v>-1.449339670517272</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.242967105538489</v>
+        <v>2.291234410994686</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44889,10 +44889,10 @@
         <v>-0.477920014730798</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.627418610029621</v>
+        <v>-1.546973100935959</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.185502837125833</v>
+        <v>2.23377014258203</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44912,10 +44912,10 @@
         <v>-0.5256410034489991</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.602166987219878</v>
+        <v>-1.521721478126216</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.203347539440793</v>
+        <v>2.25161484489699</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44935,10 +44935,10 @@
         <v>-0.4988219590042262</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.602166987219878</v>
+        <v>-1.521721478126216</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.207337875127194</v>
+        <v>2.255605180583391</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44958,10 +44958,10 @@
         <v>-0.556965922592616</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.602166987219878</v>
+        <v>-1.521721478126216</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.205862648228452</v>
+        <v>2.254129953684649</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44981,10 +44981,10 @@
         <v>-0.5220761746578098</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.552576142795044</v>
+        <v>-1.472130633701382</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.250670565048225</v>
+        <v>2.298937870504422</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770576</v>
+        <v>3.676841549770577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45004,10 +45004,10 @@
         <v>-0.4755599745157504</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.521326552059871</v>
+        <v>-1.440881042966209</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.256369185842646</v>
+        <v>2.304636491298843</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615279</v>
+        <v>3.68516138161528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45027,10 +45027,10 @@
         <v>-0.3756428403917771</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.479399876472708</v>
+        <v>-1.398954367379046</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.291104264231152</v>
+        <v>2.33937156968735</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812098</v>
+        <v>3.684843823812099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45050,10 +45050,10 @@
         <v>-0.3246722333006811</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.479399876472708</v>
+        <v>-1.398954367379046</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.292243408787211</v>
+        <v>2.340510714243409</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646213</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45073,10 +45073,10 @@
         <v>-0.3431965743562881</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.474444530384261</v>
+        <v>-1.393999021290599</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.297850390602387</v>
+        <v>2.346117696058584</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611564</v>
+        <v>3.768951674611565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45096,10 +45096,10 @@
         <v>-0.3086096000024994</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.474444530384261</v>
+        <v>-1.393999021290599</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.303584094841023</v>
+        <v>2.351851400297221</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955324</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45119,10 +45119,10 @@
         <v>-0.2898003053525056</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.403078137774614</v>
+        <v>-1.322632628680952</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.336666668012947</v>
+        <v>2.384933973469144</v>
       </c>
     </row>
     <row r="1895">
@@ -45142,10 +45142,10 @@
         <v>-0.2623001730713233</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.403078137774614</v>
+        <v>-1.322632628680952</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.326783186700039</v>
+        <v>2.375050492156237</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436225</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.496857907430027</v>
+        <v>-8.490679767185721</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2323040784203245</v>
+        <v>-0.2298328223226025</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.403078137774614</v>
+        <v>-1.322632628680952</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.324948626200666</v>
+        <v>2.373215931656863</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311945</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.398950868753536</v>
+        <v>-8.392772728509231</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1934415779231893</v>
+        <v>-0.1909703218254672</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.335092387914057</v>
+        <v>-1.254646878820395</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.365439761143539</v>
+        <v>2.413707066599736</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082935409724</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.374997327777578</v>
+        <v>-8.368819187533273</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1831916553873123</v>
+        <v>-0.1807203992895903</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.3111388469381</v>
+        <v>-1.230693337844438</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.380480391874607</v>
+        <v>2.428747697330804</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017768</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.110937389454781</v>
+        <v>-8.104759249210476</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.09082799621994564</v>
+        <v>-0.08835674012222361</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.047078908615303</v>
+        <v>-0.9666333995216414</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.525656038706532</v>
+        <v>2.57392334416273</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839721</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.403857765949943</v>
+        <v>-7.397679625705638</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1892168195216888</v>
+        <v>0.1916880756194108</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.047078908615303</v>
+        <v>-0.9666333995216414</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.522869005046231</v>
+        <v>2.571136310502429</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.363673467583753</v>
+        <v>-7.357495327339447</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2056341627560063</v>
+        <v>0.2081054188537284</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.006894610249113</v>
+        <v>-0.9264491011554506</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.547323207953787</v>
+        <v>2.595590513409984</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.20027359664439</v>
+        <v>-7.194095456400085</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2703609323525082</v>
+        <v>0.2728321884502303</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.8434947393097501</v>
+        <v>-0.7630492302160882</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.644729951738161</v>
+        <v>2.692997257194359</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.966792374414791</v>
+        <v>-6.960614234170486</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3716778500821998</v>
+        <v>0.3741491061799218</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.6100135170801515</v>
+        <v>-0.5295680079864896</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.792743113913773</v>
+        <v>2.841010419369971</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.817125983407276</v>
+        <v>-6.810947843162971</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4286521961722469</v>
+        <v>0.431123452269969</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.5171100258376156</v>
+        <v>-0.4366645167439537</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.845592998346336</v>
+        <v>2.893860303802533</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.68485050977639</v>
+        <v>-6.678672369532085</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4769298723716284</v>
+        <v>0.4794011284693505</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.3848345522067289</v>
+        <v>-0.304389043113067</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.920325769271895</v>
+        <v>2.968593074728092</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.529112177216648</v>
+        <v>-6.522934036972343</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5420402660831618</v>
+        <v>0.5445115221808838</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.2290962196469873</v>
+        <v>-0.1486507105533255</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.016583829495376</v>
+        <v>3.064851134951573</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.444147510487328</v>
+        <v>-6.437969370243023</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5889324739985486</v>
+        <v>0.5914037300962707</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.1441315529176678</v>
+        <v>-0.06368604382400589</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.080468970756627</v>
+        <v>3.128736276212824</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.549737500260433</v>
+        <v>-6.543559360016127</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.418720548490088</v>
+        <v>0.42119180458781</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.2497215426907721</v>
+        <v>-0.1692760335971102</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.889139047293545</v>
+        <v>2.937406352749742</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987899</v>
+        <v>3.770422583987901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.481502915635005</v>
+        <v>-6.4753247753907</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4945587242173453</v>
+        <v>0.4970299803150677</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.2313062198182361</v>
+        <v>-0.1508607107245742</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.948732582894154</v>
+        <v>2.99699988835035</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.333562874227406</v>
+        <v>-6.3273847339831</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4338558180922174</v>
+        <v>0.4363270741899399</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.2109853039096786</v>
+        <v>-0.1305397948160167</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.84104620975112</v>
+        <v>2.889313515207317</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409203</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.280593351973417</v>
+        <v>-6.274415211729112</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.446329640740335</v>
+        <v>0.448800896838057</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1580157816556897</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.864113936850035</v>
+        <v>2.912381242306233</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.114805156013126</v>
+        <v>-6.108627015768821</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.505684307029358</v>
+        <v>0.50815556312708</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1580157816556897</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.857153324754942</v>
+        <v>2.90542063021114</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.081441949534358</v>
+        <v>-6.075263809290052</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5334919440020087</v>
+        <v>0.5359632000997308</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1580157816556897</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.871615679136085</v>
+        <v>2.919882984592283</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.973182812411836</v>
+        <v>-5.967004672167531</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5713277193102124</v>
+        <v>0.5737989754079345</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1580157816556897</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.86614779959528</v>
+        <v>2.914415105051478</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.849891677594705</v>
+        <v>-5.8437135373504</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6181422672476415</v>
+        <v>0.6206135233453636</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.03472464683855919</v>
+        <v>0.04572086225510269</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.937620574496135</v>
+        <v>2.985887879952333</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.797194810463414</v>
+        <v>-5.791016670219109</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6469219923374832</v>
+        <v>0.6493932484352052</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.01797222029273199</v>
+        <v>0.09841772938639387</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.976939673012235</v>
+        <v>3.025206978468433</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.55342936847997</v>
+        <v>-5.547251228235664</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7402088774779116</v>
+        <v>0.7426801335756337</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.01797222029273199</v>
+        <v>0.09841772938639387</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.972720381359286</v>
+        <v>3.020987686815483</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.463653696103497</v>
+        <v>-5.457475555859192</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7782434603485164</v>
+        <v>0.7807147164462385</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.07957166520704201</v>
+        <v>0.1600171743007039</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.011804362227888</v>
+        <v>3.060071667684086</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.213803302154423</v>
+        <v>-5.207625161910117</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8709256929118485</v>
+        <v>0.8733969490095705</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.07957166520704201</v>
+        <v>0.1600171743007039</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.00454643721159</v>
+        <v>3.052813742667788</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011494</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.037911209686991</v>
+        <v>-5.031733069442685</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9448816534194702</v>
+        <v>0.9473529095171922</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.07957166520704201</v>
+        <v>0.1600171743007039</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.008145560732239</v>
+        <v>3.056412866188436</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.866464746664527</v>
+        <v>-4.860286606420222</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.026787744683009</v>
+        <v>1.029259000780731</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.2510181282295051</v>
+        <v>0.331463637323167</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.124340944600271</v>
+        <v>3.172608250056468</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632777</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.786442459555406</v>
+        <v>-4.780264319311101</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.057817137142955</v>
+        <v>1.060288393240677</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3310404153386261</v>
+        <v>0.411485924432288</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.17137479448204</v>
+        <v>3.219642099938238</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.722806717321472</v>
+        <v>-4.716628577077167</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.087966235090846</v>
+        <v>1.090437491188568</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.3946761575725606</v>
+        <v>0.4751216666662225</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.214251040876718</v>
+        <v>3.262518346332915</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.629109399105077</v>
+        <v>-4.622931258860771</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.106639421161199</v>
+        <v>1.109110677258921</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.3946761575725606</v>
+        <v>0.4751216666662225</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.195445299660514</v>
+        <v>3.243712605116711</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.639612022170366</v>
+        <v>-4.63343388192606</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.104181448559961</v>
+        <v>1.106652704657683</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.3841735345072718</v>
+        <v>0.4646190436009336</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.190886802446218</v>
+        <v>3.239154107902415</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.567369453999171</v>
+        <v>-4.561191313754866</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.137007789663259</v>
+        <v>1.139479045760981</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.3841735345072718</v>
+        <v>0.4646190436009336</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.194816116281038</v>
+        <v>3.243083421737235</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.549655767121306</v>
+        <v>-4.543477626877</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.144771848331745</v>
+        <v>1.147243104429467</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.3873548634041886</v>
+        <v>0.4678003724978504</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.197403497536528</v>
+        <v>3.245670802992725</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.440850881641579</v>
+        <v>-4.434672741397273</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.18529187374363</v>
+        <v>1.187763129841352</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.3873548634041886</v>
+        <v>0.4678003724978504</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.194401568756521</v>
+        <v>3.242668874212719</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.220830083604568</v>
+        <v>-4.214651943360263</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.274879229969048</v>
+        <v>1.27735048606677</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5285747084721688</v>
+        <v>0.6090202175658307</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.280712512807924</v>
+        <v>3.328979818264121</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.08796239454129</v>
+        <v>-4.081784254296985</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.343920488396182</v>
+        <v>1.346391744493904</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5285747084721688</v>
+        <v>0.6090202175658307</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.296606695609747</v>
+        <v>3.344874001065945</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.967789311176792</v>
+        <v>-3.961611170932486</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.393135566182284</v>
+        <v>1.395606822280006</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6487477918366678</v>
+        <v>0.7291933009303296</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.369856390068748</v>
+        <v>3.418123695524946</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.832535949846815</v>
+        <v>-3.826357809602509</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.457325013275714</v>
+        <v>1.459796269373437</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.7840011531666449</v>
+        <v>0.8644466622603068</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.461096509428175</v>
+        <v>3.509363814884372</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.892410777204507</v>
+        <v>-3.886232636960202</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.419412573734063</v>
+        <v>1.421883829831785</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7241263258089528</v>
+        <v>0.8045718349026146</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.411209104414985</v>
+        <v>3.459476409871182</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.77259054629367</v>
+        <v>-3.766412406049364</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.482629835332607</v>
+        <v>1.485101091430329</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7241263258089528</v>
+        <v>0.8045718349026146</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.426498273649194</v>
+        <v>3.474765579105391</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.775060252755476</v>
+        <v>-3.76888211251117</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.389286152070326</v>
+        <v>1.391757408168048</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7216566193471466</v>
+        <v>0.8021021284408085</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.332660649094552</v>
+        <v>3.380927954550749</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.843430439079485</v>
+        <v>-3.83725229883518</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.281199939026023</v>
+        <v>1.283671195123746</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.7309323183833616</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.257487930001582</v>
+        <v>3.305755235457779</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.857218491926532</v>
+        <v>-3.851040351682227</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.266121426519096</v>
+        <v>1.268592682616818</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.7309323183833616</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.247924638633473</v>
+        <v>3.29619194408967</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.912738567819122</v>
+        <v>-3.906560427574816</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.380944232854262</v>
+        <v>1.383415488951985</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.7309323183833616</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.384955475325675</v>
+        <v>3.433222780781873</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.737264308026652</v>
+        <v>-3.731086167782347</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.455701168763038</v>
+        <v>1.45817242486076</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.7309323183833616</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.389522707317463</v>
+        <v>3.43779001277366</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.848200560667901</v>
+        <v>-3.842022420423596</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.387068696467746</v>
+        <v>1.389539952565468</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.7309323183833616</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.36526473607867</v>
+        <v>3.413532041534868</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111297</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.814537015195619</v>
+        <v>-3.808358874951314</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.329072428058108</v>
+        <v>1.33154368415583</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.7645958638556435</v>
+        <v>0.8450413729493054</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.314001176763489</v>
+        <v>3.362268482219687</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.754684395991896</v>
+        <v>-3.748506255747591</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.36318586217173</v>
+        <v>1.365657118269452</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.7645958638556435</v>
+        <v>0.8450413729493054</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.324173563195622</v>
+        <v>3.372440868651819</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.668440932965519</v>
+        <v>-3.662262792721213</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.392629517956141</v>
+        <v>1.395100774053863</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.7645958638556435</v>
+        <v>0.8450413729493054</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.319119833769482</v>
+        <v>3.367387139225679</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.713747752364498</v>
+        <v>-3.707569612120193</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.366282565641075</v>
+        <v>1.368753821738797</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7237857008464127</v>
+        <v>0.8042312099400746</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.286409511408469</v>
+        <v>3.334676816864667</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803193</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.7427808570668</v>
+        <v>-3.736602716822495</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.355221196793256</v>
+        <v>1.357692452890978</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7237857008464127</v>
+        <v>0.8042312099400746</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.286961384441571</v>
+        <v>3.335228689897768</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.649970375615941</v>
+        <v>-3.643792235371635</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.321618081264965</v>
+        <v>1.324089337362687</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.816596182297272</v>
+        <v>0.8970416913909339</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.271920365203452</v>
+        <v>3.320187670659649</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.694359844945368</v>
+        <v>-3.688181704701063</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.305735769457795</v>
+        <v>1.308207025555517</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7722067129678444</v>
+        <v>0.8526522220615063</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.247160159530396</v>
+        <v>3.295427464986593</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.810901450050711</v>
+        <v>-3.804723309806406</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.254194835927381</v>
+        <v>1.256666092025103</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6556651078625017</v>
+        <v>0.7361106169561635</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.172310904978914</v>
+        <v>3.220578210435111</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.850825544633283</v>
+        <v>-3.844647404388978</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.243716493925019</v>
+        <v>1.246187750022741</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6556651078625017</v>
+        <v>0.7361106169561635</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.177802200809581</v>
+        <v>3.226069506265778</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.878605942534636</v>
+        <v>-3.872427802290331</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.244101536533017</v>
+        <v>1.246572792630739</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6278847099611485</v>
+        <v>0.7083302190548104</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.172631163837308</v>
+        <v>3.220898469293505</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.996986615264774</v>
+        <v>-3.990808475020469</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.035104987441615</v>
+        <v>1.037576243539337</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5606668578101723</v>
+        <v>0.6411123669038342</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.970656172547375</v>
+        <v>3.018923478003573</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.105600693708105</v>
+        <v>-4.0994225534638</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.111809016783488</v>
+        <v>1.11428027288121</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5606668578101723</v>
+        <v>0.6411123669038342</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.090805833266581</v>
+        <v>3.139073138722778</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.070191655459962</v>
+        <v>-4.064013515215657</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.140485658185068</v>
+        <v>1.14295691428279</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5606668578101723</v>
+        <v>0.6411123669038342</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.105318859368904</v>
+        <v>3.153586164825101</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.031807992901811</v>
+        <v>-4.025629852657506</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.153258564550697</v>
+        <v>1.15572982064842</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.5990505203683235</v>
+        <v>0.6794960294619854</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.125768498246163</v>
+        <v>3.174035803702361</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532487</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.056420921416271</v>
+        <v>-3.84851352262234</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.140142421990215</v>
+        <v>1.223305381507788</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.5990505203683235</v>
+        <v>0.6794960294619854</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.122497527091466</v>
+        <v>3.170764832547663</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.101513166249817</v>
+        <v>-3.893605767455885</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.12278891581871</v>
+        <v>1.205951875336283</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5371544771989337</v>
+        <v>0.6175999862925956</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.086043292951745</v>
+        <v>3.134310598407942</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.92213774501105</v>
+        <v>-3.714230346217118</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.188326059620632</v>
+        <v>1.271489019138204</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6939312353696524</v>
+        <v>0.7743767444633143</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.17389632316059</v>
+        <v>3.222163628616787</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.967151958531656</v>
+        <v>-3.759244559737724</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.151127829543979</v>
+        <v>1.234290789061552</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6635823400550478</v>
+        <v>0.7440278491487097</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.136494441303417</v>
+        <v>3.184761746759615</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.234156468804091</v>
+        <v>-4.026249070010159</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.05001758777395</v>
+        <v>1.133180547291523</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4692193020120992</v>
+        <v>0.5496648111057612</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.025568180816594</v>
+        <v>3.073835486272791</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760815</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.335354250241264</v>
+        <v>-4.127446851447332</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.008742397095583</v>
+        <v>1.091905356613155</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.40081048846678</v>
+        <v>0.481255997560442</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.983726814585903</v>
+        <v>3.031994120042101</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815459</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.328843283626951</v>
+        <v>-4.12093588483302</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.008946745295624</v>
+        <v>1.092109704813197</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.40081048846678</v>
+        <v>0.481255997560442</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.981326776140221</v>
+        <v>3.029594081596418</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.309805155919654</v>
+        <v>-4.101897757125722</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.013086715586788</v>
+        <v>1.096249675104361</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3426268771355855</v>
+        <v>0.4230723862292474</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.942941328549749</v>
+        <v>2.991208634005946</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.362320958194474</v>
+        <v>-4.154413559400543</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.111374796311051</v>
+        <v>1.194537755828623</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3426268771355855</v>
+        <v>0.4230723862292474</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.062235730183939</v>
+        <v>3.110503035640136</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.376187719528392</v>
+        <v>-4.168280320734461</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.106661420763617</v>
+        <v>1.18982438028119</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3047689604017625</v>
+        <v>0.3852144694954245</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.040354309129779</v>
+        <v>3.088621614585976</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.331383547988462</v>
+        <v>-4.123476149194531</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.130591619776515</v>
+        <v>1.213754579294088</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3047689604017625</v>
+        <v>0.3852144694954245</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.046362839526705</v>
+        <v>3.094630144982902</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.78150125051991</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.18364057775346</v>
+        <v>-3.975733178959528</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.087639029147715</v>
+        <v>1.170801988665288</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4725763176366457</v>
+        <v>0.5530218267303076</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.044997475144834</v>
+        <v>3.093264780601031</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181172</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.267461799028158</v>
+        <v>-4.059554400234227</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.056904162169317</v>
+        <v>1.14006712168689</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4725763176366457</v>
+        <v>0.5530218267303076</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.047791096676315</v>
+        <v>3.096058402132512</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.261309092975374</v>
+        <v>-4.053401694181442</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.060027592982089</v>
+        <v>1.143190552499662</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.47872902368943</v>
+        <v>0.5591745327830919</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.052145068699644</v>
+        <v>3.100412374155841</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890614</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.278118391125876</v>
+        <v>-4.070210992331944</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.052384350461999</v>
+        <v>1.135547309979571</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4619197255389283</v>
+        <v>0.5423652346325902</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.041139966549453</v>
+        <v>3.08940727200565</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.215820392349753</v>
+        <v>-4.007912993555822</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.143639103769268</v>
+        <v>1.226802063286841</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5072139898133704</v>
+        <v>0.5876594989070323</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.13465207891094</v>
+        <v>3.182919384367136</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.014030194684596</v>
+        <v>-3.806122795890664</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.026647184549458</v>
+        <v>1.109810144067031</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7052321819825248</v>
+        <v>0.7856776910761867</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.055754995926559</v>
+        <v>3.104022301382756</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852428</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.06491690737079</v>
+        <v>-3.857009508576859</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.076582731797156</v>
+        <v>1.159745691314728</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6543454692963303</v>
+        <v>0.7347909783899922</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.095513200637018</v>
+        <v>3.143780506093215</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319547</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.978306164720983</v>
+        <v>-3.770398765927051</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.125854764973123</v>
+        <v>1.209017724490695</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7329712005014886</v>
+        <v>0.8134167095951504</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.157316375476156</v>
+        <v>3.205583680932353</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.038515462726267</v>
+        <v>-3.830608063932336</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.10030702659568</v>
+        <v>1.183469986113253</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.672761902496204</v>
+        <v>0.7532074115898659</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.119726777497657</v>
+        <v>3.167994082953854</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.962093416294341</v>
+        <v>-3.754186017500409</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.12936746320838</v>
+        <v>1.212530422725952</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.672761902496204</v>
+        <v>0.7532074115898659</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.118218395537586</v>
+        <v>3.166485700993783</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316251</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.917720284655772</v>
+        <v>-3.70981288586184</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.146979583299243</v>
+        <v>1.230142542816816</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7171350341347726</v>
+        <v>0.7975805432284345</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.144705141956163</v>
+        <v>3.19297244741236</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105969</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.940200635514657</v>
+        <v>-3.732293236720725</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.13238123709428</v>
+        <v>1.215544196611852</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7171350341347726</v>
+        <v>0.7975805432284345</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.139098936094753</v>
+        <v>3.187366241550951</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190326</v>
+        <v>3.833011148190328</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.892544904953601</v>
+        <v>-3.68463750615967</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.157825286346507</v>
+        <v>1.240988245864079</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7647907646958283</v>
+        <v>0.8452362737894902</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.174074131459192</v>
+        <v>3.222341436915389</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.82267821056962</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.792026746454846</v>
+        <v>-3.584119347660915</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.202924923120734</v>
+        <v>1.286087882638306</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8653089231945829</v>
+        <v>0.9457544322882447</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.239277399933169</v>
+        <v>3.287544705389366</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557295</v>
+        <v>3.828808877557297</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.776121417022494</v>
+        <v>-3.568214018228562</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.196041727369547</v>
+        <v>1.279204686887119</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7861962624853439</v>
+        <v>0.8666417715790058</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.178564475983498</v>
+        <v>3.226831781439695</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.81683703393277</v>
+        <v>3.816837033932772</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.731283015414096</v>
+        <v>-3.523375616620164</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.218074790623535</v>
+        <v>1.301237750141107</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7907396954302134</v>
+        <v>0.8711852045238753</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.185388238361048</v>
+        <v>3.233655543817246</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917053</v>
+        <v>3.817932354917055</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.750781471656104</v>
+        <v>-3.542874072862173</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.214436347757809</v>
+        <v>1.297599307275382</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7426550541503091</v>
+        <v>0.823100563243971</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.160698393224184</v>
+        <v>3.208965698680381</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405961</v>
+        <v>3.826684745405963</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.706578634570203</v>
+        <v>-3.498671235776272</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.237997085120007</v>
+        <v>1.321160044637579</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7868578912362095</v>
+        <v>0.8673034003298714</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.193099698003561</v>
+        <v>3.241367003459758</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265645</v>
+        <v>3.838199629265647</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.71413830040725</v>
+        <v>-3.506230901613319</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.233383219254435</v>
+        <v>1.316546178772008</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8416612952460288</v>
+        <v>0.9221068043396907</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.2243917408787</v>
+        <v>3.272659046334898</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284882</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.555846882867978</v>
+        <v>-3.347939484074047</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.347947551453184</v>
+        <v>1.431110510970756</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8416612952460288</v>
+        <v>0.9221068043396907</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.27563950606174</v>
+        <v>3.323906811517937</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321024</v>
+        <v>3.865338681321026</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.348204879233502</v>
+        <v>-3.140297480439571</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.429445057501228</v>
+        <v>1.5126080170188</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.049303298880505</v>
+        <v>1.129748807974167</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.398665412836679</v>
+        <v>3.446932718292876</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.86448984247514</v>
+        <v>3.864489842475142</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.297172786510974</v>
+        <v>-3.089265387717043</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.444806122828509</v>
+        <v>1.527969082346081</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.100335391603033</v>
+        <v>1.180780900696695</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.424232896708466</v>
+        <v>3.472500202164663</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404854</v>
+        <v>3.842547360404856</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.231948605383768</v>
+        <v>-3.024041206589837</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.488083199372096</v>
+        <v>1.571246158889668</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.165559572730239</v>
+        <v>1.246005081823901</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.480554809477494</v>
+        <v>3.528822114933691</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882559</v>
+        <v>3.84006118688256</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.194521585312634</v>
+        <v>-2.986614186518703</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.49901497969983</v>
+        <v>1.582177939217402</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.17081111075942</v>
+        <v>1.251256619853082</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.479666704594283</v>
+        <v>3.527934010050481</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992662</v>
+        <v>3.845169808992663</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.214633241347343</v>
+        <v>-3.006725842553411</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.492227109617187</v>
+        <v>1.575390069134759</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.18183845575684</v>
+        <v>1.262283964850502</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.487539903923975</v>
+        <v>3.535807209380172</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636288</v>
+        <v>3.82866144563629</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.160888426920138</v>
+        <v>-2.952981028126207</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.67428280640928</v>
+        <v>1.757445765926852</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.191901765197302</v>
+        <v>1.272347274290964</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.654135660609463</v>
+        <v>3.702402966065661</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957627</v>
+        <v>3.813222820957629</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.086106165895125</v>
+        <v>-2.878198767101194</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.824308620037102</v>
+        <v>1.907471579554674</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.266684026222314</v>
+        <v>1.347129535315976</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.819117926442288</v>
+        <v>3.867385231898485</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998758</v>
+        <v>3.81423072799876</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.060022081631317</v>
+        <v>-2.852114682837386</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.826450229756484</v>
+        <v>1.909613189274056</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.266684026222314</v>
+        <v>1.347129535315976</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.810825902456147</v>
+        <v>3.859093207912344</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896933</v>
+        <v>3.803397818896935</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.972144168522197</v>
+        <v>-2.764236769728265</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.859794590583912</v>
+        <v>1.942957550101484</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.382609668645665</v>
+        <v>1.463055177739327</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.878574483493937</v>
+        <v>3.926841788950134</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959861</v>
+        <v>3.796264143959863</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.963251707128913</v>
+        <v>-2.755344308334982</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.880905980868016</v>
+        <v>1.964068940385589</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.382609668645665</v>
+        <v>1.463055177739327</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.896128889220729</v>
+        <v>3.944396194676925</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945368</v>
+        <v>3.79442494194537</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.131727824098791</v>
+        <v>-2.92382042530486</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.805370581484649</v>
+        <v>1.888533541002222</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.354661832929085</v>
+        <v>1.435107342022747</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.871215235195364</v>
+        <v>3.919482540651561</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782712</v>
+        <v>3.795574066782714</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.685471631469351</v>
+        <v>-2.47756423267542</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.965142755724287</v>
+        <v>2.04830571524186</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.259943163259452</v>
+        <v>1.340388672353114</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.795653730581446</v>
+        <v>3.843921036037643</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632639</v>
+        <v>3.784671345632641</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.662750527786199</v>
+        <v>-2.454843128992267</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.964895219694453</v>
+        <v>2.048058179212025</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.259943163259452</v>
+        <v>1.340388672353114</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.786317753078351</v>
+        <v>3.834585058534548</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777676</v>
+        <v>3.783205696777678</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.791952341080241</v>
+        <v>-2.58404494228631</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.072120620228005</v>
+        <v>2.155283579745577</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.13074134996541</v>
+        <v>1.211186859059072</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.867702790953095</v>
+        <v>3.915970096409292</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644415</v>
+        <v>3.779933725644417</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.946733347858497</v>
+        <v>-2.738825949064565</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.047286040010349</v>
+        <v>2.130448999527921</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.097373675910934</v>
+        <v>1.177819185004596</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.884760009014055</v>
+        <v>3.933027314470253</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799968</v>
+        <v>3.769443619799969</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.939678657643323</v>
+        <v>-2.731771258849392</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.046783272085964</v>
+        <v>2.129946231603536</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.104428366126107</v>
+        <v>1.184873875219769</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.885668179132705</v>
+        <v>3.933935484588902</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331118</v>
+        <v>3.76667349633112</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.912727433316835</v>
+        <v>-2.704820034522904</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.0675699154613</v>
+        <v>2.150732874978873</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.119308712153827</v>
+        <v>1.199754221247489</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.904602540394078</v>
+        <v>3.952869845850275</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784111</v>
+        <v>3.768052067784113</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.048680441373151</v>
+        <v>-2.84077304257922</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.197291844383733</v>
+        <v>2.280454803901306</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.119308712153827</v>
+        <v>1.199754221247489</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.088705672539038</v>
+        <v>4.136972977995235</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714429</v>
+        <v>3.743925505714431</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.071088559178023</v>
+        <v>-2.863181160384092</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.180445292164778</v>
+        <v>2.26360825168235</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.119308712153827</v>
+        <v>1.199754221247489</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.080822367442031</v>
+        <v>4.129089672898228</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155035</v>
+        <v>3.719118627155037</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.099312794755624</v>
+        <v>-2.891405395961693</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.171209597483375</v>
+        <v>2.254372557000948</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.137285464605135</v>
+        <v>1.217730973698797</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.093662418462453</v>
+        <v>4.141929723918651</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.72945228516198</v>
+        <v>3.729452285161982</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.108753720644154</v>
+        <v>-2.900846321850223</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.22368694484981</v>
+        <v>2.306849904367382</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.259712582148527</v>
+        <v>1.340158091242189</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.223372406710335</v>
+        <v>4.271639712166532</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321637</v>
+        <v>3.714941193321639</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.161027327979795</v>
+        <v>-2.953119929185864</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.205668596460855</v>
+        <v>2.288831555978427</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.207438974812885</v>
+        <v>1.287884483906547</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.194899336854252</v>
+        <v>4.243166642310449</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347707</v>
+        <v>3.727898186347709</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.237357305580701</v>
+        <v>-3.02944990678677</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.173248418314268</v>
+        <v>2.25641137783184</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.207438974812885</v>
+        <v>1.287884483906547</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.193011149748027</v>
+        <v>4.241278455204224</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887751</v>
+        <v>3.710654104887753</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.439611025905054</v>
+        <v>-3.231703627111123</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.087167159787389</v>
+        <v>2.170330119304961</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.005185254488532</v>
+        <v>1.085630763582194</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.066479147156277</v>
+        <v>4.114746452612474</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343069</v>
+        <v>3.712897612343071</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.601179451432309</v>
+        <v>-3.393272052638378</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.020973799786639</v>
+        <v>2.104136759304211</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8784023306906524</v>
+        <v>0.9588478397843144</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.988843403087701</v>
+        <v>4.037110708543898</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389352</v>
+        <v>3.754596135389354</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.733480743529863</v>
+        <v>-3.525573344735931</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.981126689813536</v>
+        <v>2.064289649331108</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8784023306906524</v>
+        <v>0.9588478397843144</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.00191680995362</v>
+        <v>4.050184115409817</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378396</v>
+        <v>3.749882691378398</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.919349054369093</v>
+        <v>-3.711441655575161</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.898784562260784</v>
+        <v>1.981947521778356</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7198367373707047</v>
+        <v>0.8002822464643667</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.898782650744591</v>
+        <v>3.947049956200789</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006979</v>
+        <v>3.71581989500698</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.947249841478566</v>
+        <v>-3.739342442684634</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.886148288543997</v>
+        <v>1.969311248061569</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6852398132277699</v>
+        <v>0.7656853223214319</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.876548537385832</v>
+        <v>3.92481584284203</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.68489577878739</v>
+        <v>3.684895778787391</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.06977594418146</v>
+        <v>-3.861868545387528</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.833902291440038</v>
+        <v>1.91706525095761</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5627137105248761</v>
+        <v>0.6431592196185381</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.799797319741295</v>
+        <v>3.848064625197492</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585941</v>
+        <v>3.619348081585943</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.300290440367049</v>
+        <v>-4.092383041573116</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.808402452556306</v>
+        <v>1.891565412073879</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3321992143392873</v>
+        <v>0.4126447234329493</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.728194581620445</v>
+        <v>3.776461887076643</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814668</v>
+        <v>3.64075008781467</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.557011258361873</v>
+        <v>-4.349103859567941</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.846025844360223</v>
+        <v>1.929188803877796</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2237846401954725</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.803457556136004</v>
+        <v>3.851724861592201</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237097</v>
+        <v>3.668289004237098</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.710997676138014</v>
+        <v>-4.503090277344081</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.853411546395407</v>
+        <v>1.936574505912979</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2237846401954725</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.872437825281644</v>
+        <v>3.920705130737841</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.61992301642339</v>
+        <v>3.619923016423392</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.660475772310348</v>
+        <v>-4.452568373516415</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.859671510046594</v>
+        <v>1.942834469564167</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2237846401954725</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.858489027401764</v>
+        <v>3.906756332857962</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609756</v>
+        <v>3.656332733609758</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.912950926318072</v>
+        <v>-4.70504352752414</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.770551937498918</v>
+        <v>1.853714897016491</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2237846401954725</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.870359516457178</v>
+        <v>3.918626821913375</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.67402853597316</v>
+        <v>3.674028535973162</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.100588481456414</v>
+        <v>-4.997939284003552</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.696707449962525</v>
+        <v>1.73776712894367</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2237846401954725</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.871570050976122</v>
+        <v>3.919837356432319</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251948</v>
+        <v>3.66350945725195</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.258132553185855</v>
+        <v>-5.155483355732994</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.637811563498071</v>
+        <v>1.678871242479214</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.156882835055198</v>
+        <v>0.23732834414886</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.835550710119279</v>
+        <v>3.883818015575476</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916205</v>
+        <v>3.652149152916206</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.536096948769129</v>
+        <v>-5.433447751316267</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.52170365800095</v>
+        <v>1.562763336982095</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.06726310076971376</v>
+        <v>0.1477086098633758</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.776856722284178</v>
+        <v>3.825124027740375</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830331</v>
+        <v>3.667962306830333</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.65306464140802</v>
+        <v>-5.550415443955158</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.637120637644438</v>
+        <v>1.678180316625582</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.06726310076971376</v>
+        <v>0.1477086098633758</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.939060778983221</v>
+        <v>3.987328084439419</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071554</v>
+        <v>3.696539468071555</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.737782583628973</v>
+        <v>-5.635133386176111</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.598080098719871</v>
+        <v>1.639139777701015</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.01785292815833261</v>
+        <v>0.06259258093532938</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.882837799590208</v>
+        <v>3.931105105046405</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868149</v>
+        <v>3.75004401586815</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.819717401897856</v>
+        <v>-5.717068204444995</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.575535588980809</v>
+        <v>1.616595267961953</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.0277876737454128</v>
+        <v>0.05265783534824919</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.887106369806451</v>
+        <v>3.935373675262649</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332693</v>
+        <v>3.783632867332694</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.921693524146264</v>
+        <v>-5.819044326693402</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.543670778537348</v>
+        <v>1.584730457518492</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.1297637959938204</v>
+        <v>-0.04931828690015838</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.834846334913309</v>
+        <v>3.883113640369506</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231811</v>
+        <v>3.798296784231812</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.811687240669042</v>
+        <v>-5.70903804321618</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.579826179172412</v>
+        <v>1.620885858153557</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.1065592240765452</v>
+        <v>-0.02611371498288317</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.840921965307849</v>
+        <v>3.889189270764047</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818525</v>
+        <v>3.785563924818526</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.668627664928117</v>
+        <v>-5.565978467475255</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.641300020190757</v>
+        <v>1.682359699171901</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.09854579748656589</v>
+        <v>-0.0181002883929039</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.849980031983812</v>
+        <v>3.898247337440008</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.77723741205179</v>
+        <v>3.777237412051792</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.367180939456279</v>
+        <v>-5.264531742003418</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.769139593262028</v>
+        <v>1.810199272243172</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2029009279852714</v>
+        <v>0.2833464370789334</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.03810895014945</v>
+        <v>4.086376255605647</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679627</v>
+        <v>3.812635940679629</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.391771183691463</v>
+        <v>-5.289121986238602</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.760274673320665</v>
+        <v>1.801334352301809</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2029009279852714</v>
+        <v>0.2833464370789334</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.03908012790216</v>
+        <v>4.087347433358357</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474162</v>
+        <v>3.821184182474163</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.340732807684943</v>
+        <v>-5.238083610232081</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.781532928103028</v>
+        <v>1.822592607084172</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2029009279852714</v>
+        <v>0.2833464370789334</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.039923032281916</v>
+        <v>4.088190337738113</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969545</v>
+        <v>3.831734516969547</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.299593512818312</v>
+        <v>-5.19694431536545</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.817026744923826</v>
+        <v>1.85808642390497</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.2440402228519022</v>
+        <v>0.3244857319455642</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.083644708076039</v>
+        <v>4.131912013532236</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700481</v>
+        <v>3.825752932700483</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.18898737273871</v>
+        <v>-5.086338175285849</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.677453197079601</v>
+        <v>1.718512876060745</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.3546463629315042</v>
+        <v>0.4350918720251662</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.966192388247735</v>
+        <v>4.014459693703932</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077643</v>
+        <v>3.804688961077645</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.319568107269553</v>
+        <v>-5.216918909816691</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.628722947341228</v>
+        <v>1.669782626322372</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.2240656284006617</v>
+        <v>0.3045111374943237</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.891345991603193</v>
+        <v>3.939613297059391</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.77502886083346</v>
+        <v>3.775028860833462</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.155071773078591</v>
+        <v>-5.052422575625729</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.678948300093695</v>
+        <v>1.720007979074839</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.2240656284006617</v>
+        <v>0.3045111374943237</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.875772810679276</v>
+        <v>3.924040116135473</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077631</v>
+        <v>3.821030660077633</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.182441705763023</v>
+        <v>-5.079792508310161</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.667188037456352</v>
+        <v>1.708247716437496</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.2240656284006617</v>
+        <v>0.3045111374943237</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.874960521115705</v>
+        <v>3.923227826571903</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147912</v>
+        <v>3.832307024147914</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.192826900652912</v>
+        <v>-5.090177703200051</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.672902738625468</v>
+        <v>1.713962417606613</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.2136804335107724</v>
+        <v>0.2941259426044344</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.878598183306845</v>
+        <v>3.926865488763042</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735285</v>
+        <v>3.834415493735286</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.211415059375137</v>
+        <v>-5.108765861922276</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.736304480913004</v>
+        <v>1.777364159894148</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.195092274788547</v>
+        <v>0.275537783882209</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.938282293849935</v>
+        <v>3.986549599306132</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496557</v>
+        <v>3.855120535496559</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.211713606071173</v>
+        <v>-5.109064408618312</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.733054073052888</v>
+        <v>1.774113752034032</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.195092274788547</v>
+        <v>0.275537783882209</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.935151304668233</v>
+        <v>3.98341861012443</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.81564321210886</v>
+        <v>3.815643212108862</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.110890472380746</v>
+        <v>-5.008241274927884</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.77791422146845</v>
+        <v>1.818973900449595</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.2075564902729009</v>
+        <v>0.2880019993665628</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.947160728898236</v>
+        <v>3.995428034354433</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121469</v>
+        <v>3.807356168121471</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.920109111628339</v>
+        <v>-4.817459914175477</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.854356019247956</v>
+        <v>1.895415698229101</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.3983378510253082</v>
+        <v>0.4787833601189702</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.061758798828224</v>
+        <v>4.110026104284421</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906082</v>
+        <v>3.775233033906084</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.901592257586518</v>
+        <v>-4.798943060133657</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.841599606602281</v>
+        <v>1.882659285583425</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.4112679804505164</v>
+        <v>0.4917134895441784</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.049353722220946</v>
+        <v>4.097621027677143</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912988</v>
+        <v>3.785761685912989</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.8763990730852</v>
+        <v>-4.773749875632339</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.886643817014867</v>
+        <v>1.927703495996011</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.4364611649518348</v>
+        <v>0.5169066740454967</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.099436569533795</v>
+        <v>4.147703874989992</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539897</v>
+        <v>3.743767956539899</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.864344946172237</v>
+        <v>-4.761695748719376</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.885152035681489</v>
+        <v>1.926211714662634</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.4485152918647976</v>
+        <v>0.5289608009584595</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.100355613583011</v>
+        <v>4.148622919039208</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811012</v>
+        <v>3.725010844811013</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.870968192862596</v>
+        <v>-4.768318995409734</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.884383367189482</v>
+        <v>1.925443046170626</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.4418920451744393</v>
+        <v>0.5223375542681012</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.098262295752932</v>
+        <v>4.146529601209129</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382922</v>
+        <v>3.612322444382924</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.768087603334003</v>
+        <v>-4.665438405881141</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.938386628878802</v>
+        <v>1.979446307859946</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.5447726347030322</v>
+        <v>0.6252181437966942</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.17284167534797</v>
+        <v>4.221108980804167</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760318</v>
+        <v>3.64685760776032</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.79152964251409</v>
+        <v>-4.688880445061228</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.949212483380361</v>
+        <v>1.990272162361506</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.5447726347030322</v>
+        <v>0.6252181437966942</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.193044345521564</v>
+        <v>4.241311650977761</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781709</v>
+        <v>3.666767386781711</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.809602150805701</v>
+        <v>-4.70695295335284</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.941983480063716</v>
+        <v>1.983043159044861</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.5447726347030322</v>
+        <v>0.6252181437966942</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.193044345521564</v>
+        <v>4.241311650977761</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082838</v>
+        <v>3.67006888808284</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.040775944682333</v>
+        <v>-4.938126747229472</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.809765876106531</v>
+        <v>1.850825555087675</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.5447726347030322</v>
+        <v>0.6252181437966942</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.153296259115031</v>
+        <v>4.201563564571228</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943589</v>
+        <v>3.745593333943591</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.009489924141878</v>
+        <v>-4.906840726689016</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.829302903319653</v>
+        <v>1.870362582300797</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.5760586552434875</v>
+        <v>0.6565041643371495</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.179090490436244</v>
+        <v>4.227357795892441</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677827</v>
+        <v>3.730590658677829</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.856464532028594</v>
+        <v>-4.753815334575732</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.98968405973787</v>
+        <v>2.030743738719015</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.7290840473567717</v>
+        <v>0.8095295564504337</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.370076725277118</v>
+        <v>4.418344030733316</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073886</v>
+        <v>3.741298518073888</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.884771845901864</v>
+        <v>-4.782122648449002</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.165827359096855</v>
+        <v>2.206887038077999</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.7290840473567717</v>
+        <v>0.8095295564504337</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.557542950185411</v>
+        <v>4.605810255641608</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903171</v>
+        <v>3.699135800903173</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.051365071015386</v>
+        <v>-4.948715873562525</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.068593020405528</v>
+        <v>2.109652699386673</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.5624908222432492</v>
+        <v>0.6429363313369112</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.426989966471379</v>
+        <v>4.475257271927576</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568386</v>
+        <v>3.708202704568388</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.878300691633086</v>
+        <v>-4.775651494180225</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.141495174820166</v>
+        <v>2.18255485380131</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.5624908222432492</v>
+        <v>0.6429363313369112</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.430666369133097</v>
+        <v>4.478933674589294</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.440186952535867</v>
+        <v>3.740601586682209</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.651714325434441</v>
+        <v>-4.746405513724528</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.229747776423119</v>
+        <v>2.191871301107084</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.5624908222432492</v>
+        <v>0.6429363313369112</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.428284424256592</v>
+        <v>4.476551729712789</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,19 +48833,19 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>4.011536684755269</v>
+        <v>3.854709003843972</v>
       </c>
       <c r="C2056" t="n">
         <v>4.235672898969511</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.651714325434441</v>
+        <v>-4.746405513724528</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.229747776423119</v>
+        <v>2.191871301107084</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.5624908222432492</v>
+        <v>0.6429363313369112</v>
       </c>
       <c r="G2056" t="n">
         <v>4.228736695955879</v>

--- a/tame_output/ON/bt/strategyON_20240814.xlsx
+++ b/tame_output/ON/bt/strategyON_20240814.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>111.9%</t>
+          <t>112.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.6%</t>
+          <t>-77.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>107.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.3%</t>
+          <t>123.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.0%</t>
+          <t>-46.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-72.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-636.2%</t>
+          <t>-625.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-34.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>102.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-157.0%</t>
+          <t>-152.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>98.7%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-303.9%</t>
+          <t>-106.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-159.7%</t>
+          <t>-150.9%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>80.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-23.2%</t>
+          <t>-22.7%</t>
         </is>
       </c>
     </row>
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.134073016460297</v>
+        <v>-5.031287292619461</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.062693345031047</v>
+        <v>1.103807634567381</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.3313998427407806</v>
+        <v>-0.2437534472249054</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.917839070284444</v>
+        <v>2.97042690759397</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.542661793640976</v>
+        <v>-5.439876069800139</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.8980193781735339</v>
+        <v>0.9391336677098687</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.6523422244055839</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.671447347990797</v>
+        <v>2.724035185300322</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191732</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.656422205663841</v>
+        <v>-5.553636481823004</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.8477006458358489</v>
+        <v>0.8888149353721837</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.6523422244055839</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.666632780462257</v>
+        <v>2.719220617771782</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.072814079950838</v>
+        <v>-5.970028356110001</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6791379467299272</v>
+        <v>0.720252236266262</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.6523422244055839</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.664626831071135</v>
+        <v>2.71721466838066</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097815</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.433987709767826</v>
+        <v>-6.331201985926989</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5449271854718107</v>
+        <v>0.5860414750081455</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.6523422244055839</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.674885521739814</v>
+        <v>2.727473359049339</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.37443904309411</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.777246229410845</v>
+        <v>-6.674460505570008</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.4037233427602986</v>
+        <v>0.4448376322966334</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.6523422244055839</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.670985086885509</v>
+        <v>2.723572924195034</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.825449046653189</v>
+        <v>-6.722663322812352</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3828471359183618</v>
+        <v>0.4239614254546966</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.6523422244055839</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.669390006940509</v>
+        <v>2.721977844250035</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.122110388463386</v>
+        <v>-7.019324664622549</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2679615751234912</v>
+        <v>0.3090758646598259</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.8087317556553376</v>
+        <v>-0.7210853601394625</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.631923101429391</v>
+        <v>2.684510938738916</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.308830096772689</v>
+        <v>-7.206044372931852</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1892473872653668</v>
+        <v>0.2303616768017016</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.8087317556553376</v>
+        <v>-0.7210853601394625</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.627896796894988</v>
+        <v>2.680484634204513</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.69183148551532</v>
+        <v>-7.589045761674483</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.03594473044673041</v>
+        <v>0.07705901998306519</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.8087317556553376</v>
+        <v>-0.7210853601394625</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.627794695573404</v>
+        <v>2.680382532882929</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.696317930716709</v>
+        <v>-7.593532206875872</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.03672166833760526</v>
+        <v>0.07783595787394004</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.8132182008567264</v>
+        <v>-0.7255718053408511</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.627674344424</v>
+        <v>2.680262181733525</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737164</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.055848253220711</v>
+        <v>-7.953062529379873</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1017401573659455</v>
+        <v>-0.06062586782961077</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.8132182008567264</v>
+        <v>-0.7255718053408511</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.63302464772205</v>
+        <v>2.685612485031576</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341307</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.106197316674933</v>
+        <v>-8.003411592834095</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1139637627904571</v>
+        <v>-0.07284947325412183</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.8635672643109484</v>
+        <v>-0.7759208687950732</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.610731229606695</v>
+        <v>2.66331906691622</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.203816594096329</v>
+        <v>-8.101030870255492</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1499697231372465</v>
+        <v>-0.1088554336009118</v>
       </c>
       <c r="F1876" t="n">
-        <v>-0.9611865417323451</v>
+        <v>-0.8735401462164698</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.555201413775626</v>
+        <v>2.607789251085151</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.257888093604688</v>
+        <v>-8.155102369763851</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.168704766619018</v>
+        <v>-0.1275904770826832</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.015258041240704</v>
+        <v>-0.9276116457248292</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.525652070392182</v>
+        <v>2.578239907701708</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.462146268934552</v>
+        <v>-8.359360545093715</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2448948396323209</v>
+        <v>-0.2037805500959862</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.142896985854693</v>
+        <v>-1.055250590338818</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.454581900742431</v>
+        <v>2.507169738051957</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.495799107443025</v>
+        <v>-8.393013383602188</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2538734205512743</v>
+        <v>-0.2127591310149395</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.243310353771731</v>
+        <v>-1.155663958255855</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.398816434476645</v>
+        <v>2.45140427178617</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.422329275775576</v>
+        <v>-8.319543551934739</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2091137863908736</v>
+        <v>-0.1679994968545389</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.169840522104282</v>
+        <v>-1.082194126588407</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.458270034970535</v>
+        <v>2.51085787228006</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.597453693162119</v>
+        <v>-8.494667969321283</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.264608332597974</v>
+        <v>-0.2234940430616392</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.344964939490826</v>
+        <v>-1.257318543974951</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.367750605286126</v>
+        <v>2.420338442595651</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.831905787176609</v>
+        <v>-8.729120063335772</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3656083351053661</v>
+        <v>-0.3244940455690313</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.344964939490826</v>
+        <v>-1.257318543974951</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.36053144038453</v>
+        <v>2.413119277694055</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.936280518203056</v>
+        <v>-8.833494794362219</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4140304182899208</v>
+        <v>-0.372916128753586</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.449339670517272</v>
+        <v>-1.361693275001396</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.291234410994686</v>
+        <v>2.343822248304211</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.09879398390164</v>
+        <v>-8.996008260060803</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.477920014730798</v>
+        <v>-0.4368057251944633</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.546973100935959</v>
+        <v>-1.459326705420083</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.23377014258203</v>
+        <v>2.286357979891556</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.224830777269929</v>
+        <v>-9.122045053429092</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5256410034489991</v>
+        <v>-0.4845267139126643</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.521721478126216</v>
+        <v>-1.434075082610341</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.25161484489699</v>
+        <v>2.304202682206515</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.167759005373998</v>
+        <v>-9.064973281533161</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4988219590042262</v>
+        <v>-0.4577076694678914</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.521721478126216</v>
+        <v>-1.434075082610341</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.255605180583391</v>
+        <v>2.308193017892917</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.309430847098119</v>
+        <v>-9.206645123257282</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.556965922592616</v>
+        <v>-0.5158516330562812</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.521721478126216</v>
+        <v>-1.434075082610341</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.254129953684649</v>
+        <v>2.306717790994175</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.259840002673284</v>
+        <v>-9.157054278832447</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5220761746578098</v>
+        <v>-0.480961885121475</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.472130633701382</v>
+        <v>-1.384484238185507</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.298937870504422</v>
+        <v>2.351525707813948</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770577</v>
+        <v>3.676841549770576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.110921668201428</v>
+        <v>-9.008135944360591</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4755599745157504</v>
+        <v>-0.4344456849794156</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.440881042966209</v>
+        <v>-1.353234647450334</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.304636491298843</v>
+        <v>2.357224328608368</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68516138161528</v>
+        <v>3.685161381615279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.885076515482016</v>
+        <v>-8.782290791641181</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3756428403917771</v>
+        <v>-0.3345285508554428</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.398954367379046</v>
+        <v>-1.31130797186317</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.33937156968735</v>
+        <v>2.391959406996875</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812099</v>
+        <v>3.684843823812098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.760497859144424</v>
+        <v>-8.657712135303589</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3246722333006811</v>
+        <v>-0.2835579437643472</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.398954367379046</v>
+        <v>-1.31130797186317</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.340510714243409</v>
+        <v>2.393098551552934</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.813393147188711</v>
+        <v>-8.710607423347875</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3431965743562881</v>
+        <v>-0.3020822848199542</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.393999021290599</v>
+        <v>-1.306352625774724</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.346117696058584</v>
+        <v>2.398705533368109</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611565</v>
+        <v>3.768951674611564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.741259971900829</v>
+        <v>-8.638474248059994</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3086096000024994</v>
+        <v>-0.267495310466165</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.393999021290599</v>
+        <v>-1.306352625774724</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.351851400297221</v>
+        <v>2.404439237606746</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.669893579291182</v>
+        <v>-8.567107855450347</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2898003053525056</v>
+        <v>-0.2486860158161717</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.234986233165076</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.384933973469144</v>
+        <v>2.437521810778669</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.576434545305958</v>
+        <v>-8.473648821465122</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2623001730713233</v>
+        <v>-0.2211858835349894</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.234986233165076</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.375050492156237</v>
+        <v>2.427638329465762</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.490679767185721</v>
+        <v>-8.387894043344886</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2298328223226025</v>
+        <v>-0.1887185327862686</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.234986233165076</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.373215931656863</v>
+        <v>2.425803768966388</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311944</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.392772728509231</v>
+        <v>-8.289987004668395</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1909703218254672</v>
+        <v>-0.1498560322891329</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.254646878820395</v>
+        <v>-1.16700048330452</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.413707066599736</v>
+        <v>2.466294903909261</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097239</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.368819187533273</v>
+        <v>-8.266033463692438</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1807203992895903</v>
+        <v>-0.1396061097532564</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.230693337844438</v>
+        <v>-1.143046942328562</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.428747697330804</v>
+        <v>2.481335534640329</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017767</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.104759249210476</v>
+        <v>-8.001973525369642</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.08835674012222361</v>
+        <v>-0.04724245058589016</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.9666333995216414</v>
+        <v>-0.8789870040057659</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.57392334416273</v>
+        <v>2.626511181472255</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.83325274783972</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.397679625705638</v>
+        <v>-7.294893901864804</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1916880756194108</v>
+        <v>0.2328023651557443</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.9666333995216414</v>
+        <v>-0.8789870040057659</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.571136310502429</v>
+        <v>2.623724147811954</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388724</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.357495327339447</v>
+        <v>-7.254709603498614</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2081054188537284</v>
+        <v>0.2492197083900618</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.9264491011554506</v>
+        <v>-0.8388027056395752</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.595590513409984</v>
+        <v>2.64817835071951</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626469</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.194095456400085</v>
+        <v>-7.091309732559251</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2728321884502303</v>
+        <v>0.3139464779865637</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.7630492302160882</v>
+        <v>-0.6754028347002127</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.692997257194359</v>
+        <v>2.745585094503884</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.960614234170486</v>
+        <v>-6.857828510329653</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3741491061799218</v>
+        <v>0.4152633957162557</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5295680079864896</v>
+        <v>-0.4419216124706141</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.841010419369971</v>
+        <v>2.893598256679496</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.810947843162971</v>
+        <v>-6.708162119322138</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.431123452269969</v>
+        <v>0.4722377418063024</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.4366645167439537</v>
+        <v>-0.3490181212280782</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.893860303802533</v>
+        <v>2.946448141112058</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.678672369532085</v>
+        <v>-6.575886645691251</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4794011284693505</v>
+        <v>0.5205154180056843</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.304389043113067</v>
+        <v>-0.2167426475971915</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.968593074728092</v>
+        <v>3.021180912037617</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105953</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.522934036972343</v>
+        <v>-6.420148313131509</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5445115221808838</v>
+        <v>0.5856258117172177</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1486507105533255</v>
+        <v>-0.06100431503744996</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.064851134951573</v>
+        <v>3.117438972261099</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.437969370243023</v>
+        <v>-6.33518364640219</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5914037300962707</v>
+        <v>0.6325180196326041</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.06368604382400589</v>
+        <v>0.02396035169186961</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.128736276212824</v>
+        <v>3.181324113522349</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.543559360016127</v>
+        <v>-6.440773636175295</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.42119180458781</v>
+        <v>0.4623060941241435</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.1692760335971102</v>
+        <v>-0.08162963808123475</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.937406352749742</v>
+        <v>2.989994190059268</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987901</v>
+        <v>3.770422583987899</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.4753247753907</v>
+        <v>-6.372539051549867</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4970299803150677</v>
+        <v>0.5381442698514007</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1508607107245742</v>
+        <v>-0.06321431520869875</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.99699988835035</v>
+        <v>3.049587725659876</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.3273847339831</v>
+        <v>-6.224599010142268</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4363270741899399</v>
+        <v>0.4774413637262729</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1305397948160167</v>
+        <v>-0.04289339930014119</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.889313515207317</v>
+        <v>2.941901352516843</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.274415211729112</v>
+        <v>-6.171629487888279</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.448800896838057</v>
+        <v>0.4899151863743905</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.07757027256202781</v>
+        <v>0.01007612295384769</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.912381242306233</v>
+        <v>2.964969079615758</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.108627015768821</v>
+        <v>-6.005841291927989</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.50815556312708</v>
+        <v>0.5492698526634134</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.07757027256202781</v>
+        <v>0.01007612295384769</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.90542063021114</v>
+        <v>2.958008467520665</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.075263809290052</v>
+        <v>-5.97247808544922</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5359632000997308</v>
+        <v>0.5770774896360642</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.07757027256202781</v>
+        <v>0.01007612295384769</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.919882984592283</v>
+        <v>2.972470821901808</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.967004672167531</v>
+        <v>-5.864218948326698</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5737989754079345</v>
+        <v>0.6149132649442679</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.07757027256202781</v>
+        <v>0.01007612295384769</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.914415105051478</v>
+        <v>2.967002942361003</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.8437135373504</v>
+        <v>-5.740927813509567</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6206135233453636</v>
+        <v>0.661727812881697</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.04572086225510269</v>
+        <v>0.1333672577709782</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.985887879952333</v>
+        <v>3.038475717261858</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.791016670219109</v>
+        <v>-5.688230946378276</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6493932484352052</v>
+        <v>0.6905075379715386</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.09841772938639387</v>
+        <v>0.1860641249022694</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.025206978468433</v>
+        <v>3.077794815777958</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.547251228235664</v>
+        <v>-5.444465504394832</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7426801335756337</v>
+        <v>0.7837944231119671</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.09841772938639387</v>
+        <v>0.1860641249022694</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.020987686815483</v>
+        <v>3.073575524125009</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.457475555859192</v>
+        <v>-5.35468983201836</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7807147164462385</v>
+        <v>0.8218290059825719</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.2476635698165794</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.060071667684086</v>
+        <v>3.112659504993611</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.207625161910117</v>
+        <v>-5.104839438069285</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8733969490095705</v>
+        <v>0.914511238545904</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.2476635698165794</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.052813742667788</v>
+        <v>3.105401579977313</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011494</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.031733069442685</v>
+        <v>-4.928947345601853</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9473529095171922</v>
+        <v>0.9884671990535256</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.2476635698165794</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.056412866188436</v>
+        <v>3.109000703497962</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.860286606420222</v>
+        <v>-4.757500882579389</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.029259000780731</v>
+        <v>1.070373290317065</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.331463637323167</v>
+        <v>0.4191100328390425</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.172608250056468</v>
+        <v>3.225196087365993</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632777</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.780264319311101</v>
+        <v>-4.677478595470268</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.060288393240677</v>
+        <v>1.10140268277701</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.411485924432288</v>
+        <v>0.4991323199481634</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.219642099938238</v>
+        <v>3.272229937247763</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.716628577077167</v>
+        <v>-4.613842853236334</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.090437491188568</v>
+        <v>1.131551780724901</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4751216666662225</v>
+        <v>0.562768062182098</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.262518346332915</v>
+        <v>3.31510618364244</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074778</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.622931258860771</v>
+        <v>-4.520145535019939</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.109110677258921</v>
+        <v>1.150224966795255</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4751216666662225</v>
+        <v>0.562768062182098</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.243712605116711</v>
+        <v>3.296300442426236</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.79769488424229</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.63343388192606</v>
+        <v>-4.530648158085228</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.106652704657683</v>
+        <v>1.147766994194017</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4646190436009336</v>
+        <v>0.5522654391168091</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.239154107902415</v>
+        <v>3.29174194521194</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.561191313754866</v>
+        <v>-4.458405589914033</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.139479045760981</v>
+        <v>1.180593335297315</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4646190436009336</v>
+        <v>0.5522654391168091</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.243083421737235</v>
+        <v>3.295671259046761</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.82232699787996</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.543477626877</v>
+        <v>-4.440691903036168</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.147243104429467</v>
+        <v>1.188357393965801</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4678003724978504</v>
+        <v>0.5554467680137259</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.245670802992725</v>
+        <v>3.29825864030225</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502332</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.434672741397273</v>
+        <v>-4.331887017556441</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.187763129841352</v>
+        <v>1.228877419377685</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4678003724978504</v>
+        <v>0.5554467680137259</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.242668874212719</v>
+        <v>3.295256711522244</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675933</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.214651943360263</v>
+        <v>-4.11186621951943</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.27735048606677</v>
+        <v>1.318464775603103</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.6090202175658307</v>
+        <v>0.6966666130817062</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.328979818264121</v>
+        <v>3.381567655573646</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.081784254296985</v>
+        <v>-3.978998530456152</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.346391744493904</v>
+        <v>1.387506034030238</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.6090202175658307</v>
+        <v>0.6966666130817062</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.344874001065945</v>
+        <v>3.39746183837547</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.845047386496258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.961611170932486</v>
+        <v>-3.858825447091653</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.395606822280006</v>
+        <v>1.436721111816339</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7291933009303296</v>
+        <v>0.8168396964462051</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.418123695524946</v>
+        <v>3.470711532834471</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576999</v>
+        <v>3.791273551576995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.826357809602509</v>
+        <v>-3.723572085761676</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.459796269373437</v>
+        <v>1.50091055890977</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8644466622603068</v>
+        <v>0.9520930577761822</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.509363814884372</v>
+        <v>3.561951652193897</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.886232636960202</v>
+        <v>-3.783446913119368</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.421883829831785</v>
+        <v>1.462998119368119</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.8045718349026146</v>
+        <v>0.8922182304184901</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.459476409871182</v>
+        <v>3.512064247180708</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.766412406049364</v>
+        <v>-3.663626682208531</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.485101091430329</v>
+        <v>1.526215380966663</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.8045718349026146</v>
+        <v>0.8922182304184901</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.474765579105391</v>
+        <v>3.527353416414916</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.76888211251117</v>
+        <v>-3.666096388670337</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.391757408168048</v>
+        <v>1.432871697704382</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.8021021284408085</v>
+        <v>0.889748523956684</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.380927954550749</v>
+        <v>3.433515791860274</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003596</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.83725229883518</v>
+        <v>-3.734466574994347</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.283671195123746</v>
+        <v>1.324785484660079</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.899024222992899</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.305755235457779</v>
+        <v>3.358343072767305</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.851040351682227</v>
+        <v>-3.748254627841393</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.268592682616818</v>
+        <v>1.309706972153152</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.899024222992899</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.29619194408967</v>
+        <v>3.348779781399196</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.7109067314177</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.906560427574816</v>
+        <v>-3.803774703733983</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.383415488951985</v>
+        <v>1.424529778488318</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.899024222992899</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.433222780781873</v>
+        <v>3.485810618091398</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.731086167782347</v>
+        <v>-3.628300443941514</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.45817242486076</v>
+        <v>1.499286714397094</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.899024222992899</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.43779001277366</v>
+        <v>3.490377850083186</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.842022420423596</v>
+        <v>-3.739236696582762</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.389539952565468</v>
+        <v>1.430654242101802</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.899024222992899</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.413532041534868</v>
+        <v>3.466119878844393</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111297</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.808358874951314</v>
+        <v>-3.70557315111048</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.33154368415583</v>
+        <v>1.372657973692164</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8450413729493054</v>
+        <v>0.9326877684651809</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.362268482219687</v>
+        <v>3.414856319529212</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.748506255747591</v>
+        <v>-3.645720531906757</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.365657118269452</v>
+        <v>1.406771407805786</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8450413729493054</v>
+        <v>0.9326877684651809</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.372440868651819</v>
+        <v>3.425028705961344</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.662262792721213</v>
+        <v>-3.55947706888038</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.395100774053863</v>
+        <v>1.436215063590197</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8450413729493054</v>
+        <v>0.9326877684651809</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.367387139225679</v>
+        <v>3.419974976535205</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.707569612120193</v>
+        <v>-3.60478388827936</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.368753821738797</v>
+        <v>1.409868111275131</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.8042312099400746</v>
+        <v>0.8918776054559501</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.334676816864667</v>
+        <v>3.387264654174192</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803193</v>
+        <v>3.75357116580319</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.736602716822495</v>
+        <v>-3.633816992981661</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.357692452890978</v>
+        <v>1.398806742427311</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.8042312099400746</v>
+        <v>0.8918776054559501</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.335228689897768</v>
+        <v>3.387816527207293</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809501</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.643792235371635</v>
+        <v>-3.541006511530802</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.324089337362687</v>
+        <v>1.365203626899021</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8970416913909339</v>
+        <v>0.9846880869068094</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.320187670659649</v>
+        <v>3.372775507969174</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.688181704701063</v>
+        <v>-3.58539598086023</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.308207025555517</v>
+        <v>1.349321315091851</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8526522220615063</v>
+        <v>0.9402986175773818</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.295427464986593</v>
+        <v>3.348015302296119</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.804723309806406</v>
+        <v>-3.701937585965573</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.256666092025103</v>
+        <v>1.297780381561436</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7361106169561635</v>
+        <v>0.823757012472039</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.220578210435111</v>
+        <v>3.273166047744636</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.844647404388978</v>
+        <v>-3.741861680548144</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.246187750022741</v>
+        <v>1.287302039559075</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7361106169561635</v>
+        <v>0.823757012472039</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.226069506265778</v>
+        <v>3.278657343575303</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.872427802290331</v>
+        <v>-3.769642078449497</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.246572792630739</v>
+        <v>1.287687082167073</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7083302190548104</v>
+        <v>0.7959766145706859</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.220898469293505</v>
+        <v>3.27348630660303</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.990808475020469</v>
+        <v>-3.888022751179636</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.037576243539337</v>
+        <v>1.078690533075671</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6411123669038342</v>
+        <v>0.7287587624197097</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.018923478003573</v>
+        <v>3.071511315313098</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.0994225534638</v>
+        <v>-3.996636829622967</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.11428027288121</v>
+        <v>1.155394562417544</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6411123669038342</v>
+        <v>0.7287587624197097</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.139073138722778</v>
+        <v>3.191660976032304</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.064013515215657</v>
+        <v>-3.961227791374824</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.14295691428279</v>
+        <v>1.184071203819124</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6411123669038342</v>
+        <v>0.7287587624197097</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.153586164825101</v>
+        <v>3.206174002134627</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.025629852657506</v>
+        <v>-3.922844128816673</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.15572982064842</v>
+        <v>1.196844110184753</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6794960294619854</v>
+        <v>0.7671424249778609</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.174035803702361</v>
+        <v>3.226623641011886</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532487</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.84851352262234</v>
+        <v>-3.745727798781507</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.223305381507788</v>
+        <v>1.264419671044122</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6794960294619854</v>
+        <v>0.7671424249778609</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.170764832547663</v>
+        <v>3.223352669857188</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.893605767455885</v>
+        <v>-3.790820043615052</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.205951875336283</v>
+        <v>1.247066164872616</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6175999862925956</v>
+        <v>0.7052463818084711</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.134310598407942</v>
+        <v>3.186898435717467</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.714230346217118</v>
+        <v>-3.611444622376284</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.271489019138204</v>
+        <v>1.312603308674538</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7743767444633143</v>
+        <v>0.8620231399791898</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.222163628616787</v>
+        <v>3.274751465926313</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.759244559737724</v>
+        <v>-3.656458835896891</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.234290789061552</v>
+        <v>1.275405078597885</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7440278491487097</v>
+        <v>0.8316742446645852</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.184761746759615</v>
+        <v>3.23734958406914</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.026249070010159</v>
+        <v>-3.923463346169326</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.133180547291523</v>
+        <v>1.174294836827857</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5496648111057612</v>
+        <v>0.6373112066216367</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.073835486272791</v>
+        <v>3.126423323582316</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760815</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.127446851447332</v>
+        <v>-4.024661127606499</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.091905356613155</v>
+        <v>1.133019646149489</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.481255997560442</v>
+        <v>0.5689023930763175</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.031994120042101</v>
+        <v>3.084581957351626</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815459</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.12093588483302</v>
+        <v>-4.018150160992186</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.092109704813197</v>
+        <v>1.133223994349531</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.481255997560442</v>
+        <v>0.5689023930763175</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.029594081596418</v>
+        <v>3.082181918905943</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.101897757125722</v>
+        <v>-3.999112033284889</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.096249675104361</v>
+        <v>1.137363964640695</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4230723862292474</v>
+        <v>0.510718781745123</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.991208634005946</v>
+        <v>3.043796471315471</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131253</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.154413559400543</v>
+        <v>-4.051627835559709</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.194537755828623</v>
+        <v>1.235652045364957</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4230723862292474</v>
+        <v>0.510718781745123</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.110503035640136</v>
+        <v>3.163090872949661</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.168280320734461</v>
+        <v>-4.065494596893627</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.18982438028119</v>
+        <v>1.230938669817523</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3852144694954245</v>
+        <v>0.4728608650113</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.088621614585976</v>
+        <v>3.141209451895501</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.123476149194531</v>
+        <v>-4.020690425353697</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.213754579294088</v>
+        <v>1.254868868830421</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3852144694954245</v>
+        <v>0.4728608650113</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.094630144982902</v>
+        <v>3.147217982292427</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.78150125051991</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.975733178959528</v>
+        <v>-3.872947455118695</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.170801988665288</v>
+        <v>1.211916278201622</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5530218267303076</v>
+        <v>0.6406682222461832</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.093264780601031</v>
+        <v>3.145852617910557</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181172</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.059554400234227</v>
+        <v>-3.956768676393393</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.14006712168689</v>
+        <v>1.181181411223223</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5530218267303076</v>
+        <v>0.6406682222461832</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.096058402132512</v>
+        <v>3.148646239442038</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.053401694181442</v>
+        <v>-3.950615970340609</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.143190552499662</v>
+        <v>1.184304842035995</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5591745327830919</v>
+        <v>0.6468209282989675</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.100412374155841</v>
+        <v>3.153000211465367</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890614</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.070210992331944</v>
+        <v>-3.96742526849111</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.135547309979571</v>
+        <v>1.176661599515905</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5423652346325902</v>
+        <v>0.630011630148466</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.08940727200565</v>
+        <v>3.141995109315176</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.007912993555822</v>
+        <v>-3.905127269714988</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.226802063286841</v>
+        <v>1.267916352823175</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5876594989070323</v>
+        <v>0.675305894422908</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.182919384367136</v>
+        <v>3.235507221676662</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.806122795890664</v>
+        <v>-3.70333707204983</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.109810144067031</v>
+        <v>1.150924433603365</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7856776910761867</v>
+        <v>0.8733240865920624</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.104022301382756</v>
+        <v>3.156610138692282</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852428</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.857009508576859</v>
+        <v>-3.754223784736025</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.159745691314728</v>
+        <v>1.200859980851062</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7347909783899922</v>
+        <v>0.8224373739058679</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.143780506093215</v>
+        <v>3.19636834340274</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319547</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.770398765927051</v>
+        <v>-3.667613042086218</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.209017724490695</v>
+        <v>1.250132014027029</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8134167095951504</v>
+        <v>0.9010631051110262</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.205583680932353</v>
+        <v>3.258171518241879</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.830608063932336</v>
+        <v>-3.727822340091502</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.183469986113253</v>
+        <v>1.224584275649587</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7532074115898659</v>
+        <v>0.8408538071057416</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.167994082953854</v>
+        <v>3.22058192026338</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.754186017500409</v>
+        <v>-3.651400293659576</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.212530422725952</v>
+        <v>1.253644712262286</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7532074115898659</v>
+        <v>0.8408538071057416</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.166485700993783</v>
+        <v>3.219073538303308</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316251</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.70981288586184</v>
+        <v>-3.607027162021007</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.230142542816816</v>
+        <v>1.27125683235315</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7975805432284345</v>
+        <v>0.8852269387443102</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.19297244741236</v>
+        <v>3.245560284721886</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105969</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.732293236720725</v>
+        <v>-3.629507512879892</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.215544196611852</v>
+        <v>1.256658486148186</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7975805432284345</v>
+        <v>0.8852269387443102</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.187366241550951</v>
+        <v>3.239954078860476</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190328</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.68463750615967</v>
+        <v>-3.581851782318836</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.240988245864079</v>
+        <v>1.282102535400413</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8452362737894902</v>
+        <v>0.9328826693053659</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.222341436915389</v>
+        <v>3.274929274224914</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.82267821056962</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.584119347660915</v>
+        <v>-3.481333623820081</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.286087882638306</v>
+        <v>1.32720217217464</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9457544322882447</v>
+        <v>1.03340082780412</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.287544705389366</v>
+        <v>3.340132542698892</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557297</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.568214018228562</v>
+        <v>-3.465428294387729</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.279204686887119</v>
+        <v>1.320318976423453</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8666417715790058</v>
+        <v>0.9542881670948815</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.226831781439695</v>
+        <v>3.279419618749221</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932772</v>
+        <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.523375616620164</v>
+        <v>-3.420589892779331</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.301237750141107</v>
+        <v>1.342352039677441</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8711852045238753</v>
+        <v>0.958831600039751</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.233655543817246</v>
+        <v>3.286243381126771</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917055</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.542874072862173</v>
+        <v>-3.440088349021339</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.297599307275382</v>
+        <v>1.338713596811716</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.823100563243971</v>
+        <v>0.9107469587598467</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.208965698680381</v>
+        <v>3.261553535989906</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405963</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.498671235776272</v>
+        <v>-3.395885511935438</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.321160044637579</v>
+        <v>1.362274334173913</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8673034003298714</v>
+        <v>0.9549497958457471</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.241367003459758</v>
+        <v>3.293954840769284</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265647</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.506230901613319</v>
+        <v>-3.403445177772485</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.316546178772008</v>
+        <v>1.357660468308342</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9221068043396907</v>
+        <v>1.009753199855566</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.272659046334898</v>
+        <v>3.325246883644423</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284882</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.347939484074047</v>
+        <v>-3.245153760233213</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.431110510970756</v>
+        <v>1.47222480050709</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9221068043396907</v>
+        <v>1.009753199855566</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.323906811517937</v>
+        <v>3.376494648827463</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321026</v>
+        <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.140297480439571</v>
+        <v>-3.037511756598737</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.5126080170188</v>
+        <v>1.553722306555134</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.129748807974167</v>
+        <v>1.217395203490043</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.446932718292876</v>
+        <v>3.499520555602401</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475142</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.089265387717043</v>
+        <v>-2.986479663876209</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.527969082346081</v>
+        <v>1.569083371882415</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.180780900696695</v>
+        <v>1.26842729621257</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.472500202164663</v>
+        <v>3.525088039474188</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404856</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.024041206589837</v>
+        <v>-2.921255482749003</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.571246158889668</v>
+        <v>1.612360448426003</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.246005081823901</v>
+        <v>1.333651477339776</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.528822114933691</v>
+        <v>3.581409952243217</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.84006118688256</v>
+        <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.986614186518703</v>
+        <v>-2.883828462677869</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.582177939217402</v>
+        <v>1.623292228753736</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.251256619853082</v>
+        <v>1.338903015368958</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.527934010050481</v>
+        <v>3.580521847360006</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992663</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.006725842553411</v>
+        <v>-2.903940118712578</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.575390069134759</v>
+        <v>1.616504358671093</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.262283964850502</v>
+        <v>1.349930360366377</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.535807209380172</v>
+        <v>3.588395046689698</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.82866144563629</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.952981028126207</v>
+        <v>-2.850195304285373</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.757445765926852</v>
+        <v>1.798560055463186</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.272347274290964</v>
+        <v>1.359993669806839</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.702402966065661</v>
+        <v>3.754990803375186</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957629</v>
+        <v>3.813222820957625</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.878198767101194</v>
+        <v>-2.77541304326036</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.907471579554674</v>
+        <v>1.948585869091009</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.347129535315976</v>
+        <v>1.434775930831852</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.867385231898485</v>
+        <v>3.919973069208011</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799876</v>
+        <v>3.814230727998757</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.852114682837386</v>
+        <v>-2.749328958996552</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.909613189274056</v>
+        <v>1.95072747881039</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.347129535315976</v>
+        <v>1.434775930831852</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.859093207912344</v>
+        <v>3.91168104522187</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896935</v>
+        <v>3.803397818896931</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.764236769728265</v>
+        <v>-2.661451045887432</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.942957550101484</v>
+        <v>1.984071839637818</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.463055177739327</v>
+        <v>1.550701573255203</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.926841788950134</v>
+        <v>3.97942962625966</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959863</v>
+        <v>3.796264143959859</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.755344308334982</v>
+        <v>-2.652558584494148</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.964068940385589</v>
+        <v>2.005183229921923</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.463055177739327</v>
+        <v>1.550701573255203</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.944396194676925</v>
+        <v>3.996984031986451</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.79442494194537</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.92382042530486</v>
+        <v>-2.821034701464026</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.888533541002222</v>
+        <v>1.929647830538555</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.435107342022747</v>
+        <v>1.522753737538622</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.919482540651561</v>
+        <v>3.972070377961087</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782714</v>
+        <v>3.79557406678271</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.47756423267542</v>
+        <v>-2.374778508834586</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.04830571524186</v>
+        <v>2.089420004778193</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.340388672353114</v>
+        <v>1.428035067868989</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.843921036037643</v>
+        <v>3.896508873347169</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632641</v>
+        <v>3.784671345632638</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.454843128992267</v>
+        <v>-2.352057405151434</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.048058179212025</v>
+        <v>2.089172468748359</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.340388672353114</v>
+        <v>1.428035067868989</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.834585058534548</v>
+        <v>3.887172895844073</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777678</v>
+        <v>3.783205696777674</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.58404494228631</v>
+        <v>-2.481259218445476</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.155283579745577</v>
+        <v>2.196397869281911</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.211186859059072</v>
+        <v>1.298833254574947</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.915970096409292</v>
+        <v>3.968557933718817</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644417</v>
+        <v>3.779933725644414</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.738825949064565</v>
+        <v>-2.636040225223732</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.130448999527921</v>
+        <v>2.171563289064255</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.177819185004596</v>
+        <v>1.265465580520471</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.933027314470253</v>
+        <v>3.985615151779778</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799969</v>
+        <v>3.769443619799966</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.731771258849392</v>
+        <v>-2.628985535008558</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.129946231603536</v>
+        <v>2.17106052113987</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.184873875219769</v>
+        <v>1.272520270735645</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.933935484588902</v>
+        <v>3.986523321898427</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.76667349633112</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.704820034522904</v>
+        <v>-2.60203431068207</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.150732874978873</v>
+        <v>2.191847164515207</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.199754221247489</v>
+        <v>1.287400616763364</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.952869845850275</v>
+        <v>4.005457683159801</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784113</v>
+        <v>3.768052067784109</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.84077304257922</v>
+        <v>-2.737987318738386</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.280454803901306</v>
+        <v>2.32156909343764</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.199754221247489</v>
+        <v>1.287400616763364</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.136972977995235</v>
+        <v>4.18956081530476</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714431</v>
+        <v>3.743925505714428</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.863181160384092</v>
+        <v>-2.760395436543258</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.26360825168235</v>
+        <v>2.304722541218684</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.199754221247489</v>
+        <v>1.287400616763364</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.129089672898228</v>
+        <v>4.181677510207753</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155037</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.891405395961693</v>
+        <v>-2.788619672120859</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.254372557000948</v>
+        <v>2.295486846537282</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.217730973698797</v>
+        <v>1.305377369214673</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.141929723918651</v>
+        <v>4.194517561228176</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161982</v>
+        <v>3.729452285161979</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.900846321850223</v>
+        <v>-2.798060598009389</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.306849904367382</v>
+        <v>2.347964193903717</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.340158091242189</v>
+        <v>1.427804486758064</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.271639712166532</v>
+        <v>4.324227549476058</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321639</v>
+        <v>3.714941193321636</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.953119929185864</v>
+        <v>-2.85033420534503</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.288831555978427</v>
+        <v>2.329945845514761</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.287884483906547</v>
+        <v>1.375530879422423</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.243166642310449</v>
+        <v>4.295754479619974</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347709</v>
+        <v>3.727898186347705</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.02944990678677</v>
+        <v>-2.926664182945936</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.25641137783184</v>
+        <v>2.297525667368174</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.287884483906547</v>
+        <v>1.375530879422423</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.241278455204224</v>
+        <v>4.293866292513749</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887753</v>
+        <v>3.710654104887749</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.231703627111123</v>
+        <v>-3.128917903270289</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.170330119304961</v>
+        <v>2.211444408841295</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.085630763582194</v>
+        <v>1.173277159098069</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.114746452612474</v>
+        <v>4.167334289922</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343071</v>
+        <v>3.712897612343068</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.393272052638378</v>
+        <v>-3.290486328797544</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.104136759304211</v>
+        <v>2.145251048840545</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9588478397843144</v>
+        <v>1.04649423530019</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.037110708543898</v>
+        <v>4.089698545853424</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389354</v>
+        <v>3.754596135389351</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.525573344735931</v>
+        <v>-3.422787620895098</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.064289649331108</v>
+        <v>2.105403938867442</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9588478397843144</v>
+        <v>1.04649423530019</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.050184115409817</v>
+        <v>4.102771952719342</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378398</v>
+        <v>3.749882691378394</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.711441655575161</v>
+        <v>-3.608655931734328</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.981947521778356</v>
+        <v>2.02306181131469</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8002822464643667</v>
+        <v>0.8879286419802424</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.947049956200789</v>
+        <v>3.999637793510314</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.71581989500698</v>
+        <v>3.715819895006977</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.739342442684634</v>
+        <v>-3.636556718843801</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.969311248061569</v>
+        <v>2.010425537597903</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7656853223214319</v>
+        <v>0.8533317178373075</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.92481584284203</v>
+        <v>3.977403680151555</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787391</v>
+        <v>3.684895778787388</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.861868545387528</v>
+        <v>-3.759082821546694</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.91706525095761</v>
+        <v>1.958179540493944</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6431592196185381</v>
+        <v>0.7308056151344137</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.848064625197492</v>
+        <v>3.900652462507018</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585943</v>
+        <v>3.619348081585939</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.092383041573116</v>
+        <v>-3.989597317732283</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.891565412073879</v>
+        <v>1.932679701610213</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4126447234329493</v>
+        <v>0.5002911189488249</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.776461887076643</v>
+        <v>3.829049724386168</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.64075008781467</v>
+        <v>3.640750087814666</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.349103859567941</v>
+        <v>-4.246318135727107</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.929188803877796</v>
+        <v>1.97030309341413</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.3918765448050101</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.851724861592201</v>
+        <v>3.904312698901726</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237098</v>
+        <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.503090277344081</v>
+        <v>-4.400304553503248</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.936574505912979</v>
+        <v>1.977688795449314</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.3918765448050101</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.920705130737841</v>
+        <v>3.973292968047366</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423392</v>
+        <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.452568373516415</v>
+        <v>-4.349782649675582</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.942834469564167</v>
+        <v>1.983948759100501</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.3918765448050101</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.906756332857962</v>
+        <v>3.959344170167487</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609758</v>
+        <v>3.656332733609754</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.70504352752414</v>
+        <v>-4.602257803683306</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.853714897016491</v>
+        <v>1.894829186552825</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.3918765448050101</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.918626821913375</v>
+        <v>3.971214659222901</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973162</v>
+        <v>3.674028535973158</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.997939284003552</v>
+        <v>-4.895153560162719</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.73776712894367</v>
+        <v>1.778881418480004</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.3918765448050101</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.919837356432319</v>
+        <v>3.972425193741844</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.66350945725195</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.155483355732994</v>
+        <v>-5.05269763189216</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.678871242479214</v>
+        <v>1.719985532015549</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.23732834414886</v>
+        <v>0.3249747396647356</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.883818015575476</v>
+        <v>3.936405852885001</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916206</v>
+        <v>3.652149152916203</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.433447751316267</v>
+        <v>-5.330662027475434</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.562763336982095</v>
+        <v>1.603877626518429</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1477086098633758</v>
+        <v>0.2353550053792514</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.825124027740375</v>
+        <v>3.8777118650499</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830333</v>
+        <v>3.667962306830329</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.550415443955158</v>
+        <v>-5.447629720114325</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.678180316625582</v>
+        <v>1.719294606161916</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1477086098633758</v>
+        <v>0.2353550053792514</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.987328084439419</v>
+        <v>4.039915921748944</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071555</v>
+        <v>3.696539468071552</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.635133386176111</v>
+        <v>-5.532347662335278</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.639139777701015</v>
+        <v>1.680254067237349</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.06259258093532938</v>
+        <v>0.150238976451205</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.931105105046405</v>
+        <v>3.983692942355931</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.75004401586815</v>
+        <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.717068204444995</v>
+        <v>-5.614282480604161</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.616595267961953</v>
+        <v>1.657709557498287</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.05265783534824919</v>
+        <v>0.1403042308641248</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.935373675262649</v>
+        <v>3.987961512572173</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332694</v>
+        <v>3.783632867332691</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.819044326693402</v>
+        <v>-5.716258602852569</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.584730457518492</v>
+        <v>1.625844747054827</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.04931828690015838</v>
+        <v>0.03832810861571723</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.883113640369506</v>
+        <v>3.935701477679031</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231812</v>
+        <v>3.798296784231809</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.70903804321618</v>
+        <v>-5.606252319375347</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.620885858153557</v>
+        <v>1.66200014768989</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.02611371498288317</v>
+        <v>0.06153268053299243</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.889189270764047</v>
+        <v>3.941777108073572</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818526</v>
+        <v>3.785563924818523</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.565978467475255</v>
+        <v>-5.463192743634422</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.682359699171901</v>
+        <v>1.723473988708235</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.0181002883929039</v>
+        <v>0.06954610712297171</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.898247337440008</v>
+        <v>3.950835174749534</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051792</v>
+        <v>3.777237412051789</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.264531742003418</v>
+        <v>-5.161746018162584</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.810199272243172</v>
+        <v>1.851313561779506</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2833464370789334</v>
+        <v>0.370992832594809</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.086376255605647</v>
+        <v>4.138964092915172</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679629</v>
+        <v>3.812635940679625</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.289121986238602</v>
+        <v>-5.186336262397768</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.801334352301809</v>
+        <v>1.842448641838143</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2833464370789334</v>
+        <v>0.370992832594809</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.087347433358357</v>
+        <v>4.139935270667883</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474163</v>
+        <v>3.82118418247416</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.238083610232081</v>
+        <v>-5.135297886391248</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.822592607084172</v>
+        <v>1.863706896620506</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2833464370789334</v>
+        <v>0.370992832594809</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.088190337738113</v>
+        <v>4.140778175047638</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969547</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.19694431536545</v>
+        <v>-5.094158591524617</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.85808642390497</v>
+        <v>1.899200713441304</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3244857319455642</v>
+        <v>0.4121321274614398</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.131912013532236</v>
+        <v>4.184499850841762</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700483</v>
+        <v>3.825752932700479</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.086338175285849</v>
+        <v>-4.983552451445015</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.718512876060745</v>
+        <v>1.759627165597079</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4350918720251662</v>
+        <v>0.5227382675410418</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.014459693703932</v>
+        <v>4.067047531013458</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077645</v>
+        <v>3.804688961077641</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.216918909816691</v>
+        <v>-5.114133185975858</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.669782626322372</v>
+        <v>1.710896915858706</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3045111374943237</v>
+        <v>0.3921575330101993</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.939613297059391</v>
+        <v>3.992201134368916</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833462</v>
+        <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.052422575625729</v>
+        <v>-4.949636851784896</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.720007979074839</v>
+        <v>1.761122268611173</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3045111374943237</v>
+        <v>0.3921575330101993</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.924040116135473</v>
+        <v>3.976627953444998</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077633</v>
+        <v>3.821030660077629</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.079792508310161</v>
+        <v>-4.977006784469328</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.708247716437496</v>
+        <v>1.74936200597383</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3045111374943237</v>
+        <v>0.3921575330101993</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.923227826571903</v>
+        <v>3.975815663881428</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147914</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.090177703200051</v>
+        <v>-4.987391979359217</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.713962417606613</v>
+        <v>1.755076707142947</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.2941259426044344</v>
+        <v>0.38177233812031</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.926865488763042</v>
+        <v>3.979453326072567</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735286</v>
+        <v>3.834415493735283</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.108765861922276</v>
+        <v>-5.005980138081442</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.777364159894148</v>
+        <v>1.818478449430482</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.275537783882209</v>
+        <v>0.3631841793980846</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.986549599306132</v>
+        <v>4.039137436615657</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496559</v>
+        <v>3.855120535496555</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.109064408618312</v>
+        <v>-5.006278684777478</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.774113752034032</v>
+        <v>1.815228041570366</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.275537783882209</v>
+        <v>0.3631841793980846</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.98341861012443</v>
+        <v>4.036006447433955</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108862</v>
+        <v>3.815643212108858</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.008241274927884</v>
+        <v>-4.905455551087051</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.818973900449595</v>
+        <v>1.860088189985929</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.2880019993665628</v>
+        <v>0.3756483948824385</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.995428034354433</v>
+        <v>4.048015871663959</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121471</v>
+        <v>3.807356168121467</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.817459914175477</v>
+        <v>-4.714674190334644</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.895415698229101</v>
+        <v>1.936529987765435</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.4787833601189702</v>
+        <v>0.5664297556348459</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.110026104284421</v>
+        <v>4.162613941593947</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906084</v>
+        <v>3.775233033906081</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.798943060133657</v>
+        <v>-4.696157336292823</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.882659285583425</v>
+        <v>1.92377357511976</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.4917134895441784</v>
+        <v>0.5793598850600541</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.097621027677143</v>
+        <v>4.150208864986668</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912989</v>
+        <v>3.785761685912986</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.773749875632339</v>
+        <v>-4.670964151791505</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.927703495996011</v>
+        <v>1.968817785532345</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.5169066740454967</v>
+        <v>0.6045530695613724</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.147703874989992</v>
+        <v>4.200291712299518</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539899</v>
+        <v>3.743767956539895</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.761695748719376</v>
+        <v>-4.658910024878542</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.926211714662634</v>
+        <v>1.967326004198968</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.5289608009584595</v>
+        <v>0.6166071964743353</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.148622919039208</v>
+        <v>4.201210756348734</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811013</v>
+        <v>3.72501084481101</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.768318995409734</v>
+        <v>-4.665533271568901</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.925443046170626</v>
+        <v>1.966557335706961</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5223375542681012</v>
+        <v>0.609983949783977</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.146529601209129</v>
+        <v>4.199117438518654</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382924</v>
+        <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.665438405881141</v>
+        <v>-4.562652682040308</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.979446307859946</v>
+        <v>2.02056059739628</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6252181437966942</v>
+        <v>0.7128645393125699</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.221108980804167</v>
+        <v>4.273696818113693</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.64685760776032</v>
+        <v>3.646857607760317</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.688880445061228</v>
+        <v>-4.586094721220395</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.990272162361506</v>
+        <v>2.03138645189784</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6252181437966942</v>
+        <v>0.7128645393125699</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.241311650977761</v>
+        <v>4.293899488287287</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781711</v>
+        <v>3.666767386781707</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.70695295335284</v>
+        <v>-4.604167229512006</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.983043159044861</v>
+        <v>2.024157448581195</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6252181437966942</v>
+        <v>0.7128645393125699</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.241311650977761</v>
+        <v>4.293899488287287</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.67006888808284</v>
+        <v>3.670068888082836</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.938126747229472</v>
+        <v>-4.835341023388638</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.850825555087675</v>
+        <v>1.891939844624009</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6252181437966942</v>
+        <v>0.7128645393125699</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.201563564571228</v>
+        <v>4.254151401880753</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943591</v>
+        <v>3.745593333943587</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.906840726689016</v>
+        <v>-4.804055002848183</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.870362582300797</v>
+        <v>1.911476871837131</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.6565041643371495</v>
+        <v>0.7441505598530253</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.227357795892441</v>
+        <v>4.279945633201966</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677829</v>
+        <v>3.730590658677825</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.753815334575732</v>
+        <v>-4.651029610734899</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.030743738719015</v>
+        <v>2.071858028255349</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.8095295564504337</v>
+        <v>0.8971759519663094</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.418344030733316</v>
+        <v>4.47093186804284</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073888</v>
+        <v>3.741298518073885</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.782122648449002</v>
+        <v>-4.679336924608169</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.206887038077999</v>
+        <v>2.248001327614333</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.8095295564504337</v>
+        <v>0.8971759519663094</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.605810255641608</v>
+        <v>4.658398092951133</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903173</v>
+        <v>3.69913580090317</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.948715873562525</v>
+        <v>-4.845930149721691</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.109652699386673</v>
+        <v>2.150766988923007</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.6429363313369112</v>
+        <v>0.7305827268527869</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.475257271927576</v>
+        <v>4.527845109237102</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568388</v>
+        <v>3.708202704568384</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.775651494180225</v>
+        <v>-4.672865770339391</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.18255485380131</v>
+        <v>2.223669143337644</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.6429363313369112</v>
+        <v>0.7305827268527869</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.478933674589294</v>
+        <v>4.53152151189882</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682209</v>
+        <v>3.740601586682206</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.746405513724528</v>
+        <v>-4.643619789883695</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.191871301107084</v>
+        <v>2.232985590643418</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.6429363313369112</v>
+        <v>0.7305827268527869</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.476551729712789</v>
+        <v>4.529139567022315</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.854709003843972</v>
+        <v>3.864221277515263</v>
       </c>
       <c r="C2056" t="n">
-        <v>4.235672898969511</v>
+        <v>4.239775435728708</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.746405513724528</v>
+        <v>-4.643619789883695</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.191871301107084</v>
+        <v>2.232985590643418</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6429363313369112</v>
+        <v>0.7305827268527869</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.228736695955879</v>
+        <v>4.232839232715076</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240814.xlsx
+++ b/tame_output/ON/bt/strategyON_20240814.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>57.3%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>78.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>112.3%</t>
+          <t>111.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.0%</t>
+          <t>-77.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.4%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.4%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.7%</t>
+          <t>-47.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.8%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.3%</t>
+          <t>430.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-625.9%</t>
+          <t>-636.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.0%</t>
+          <t>-34.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>102.4%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-152.9%</t>
+          <t>-157.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>98.7%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-26.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-106.6%</t>
+          <t>-326.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-150.9%</t>
+          <t>-152.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>79.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-22.7%</t>
+          <t>-23.7%</t>
         </is>
       </c>
     </row>
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.031287292619461</v>
+        <v>-5.134073016460297</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.103807634567381</v>
+        <v>1.062693345031047</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.2437534472249054</v>
+        <v>-0.3313998427407806</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.97042690759397</v>
+        <v>2.917839070284444</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.439876069800139</v>
+        <v>-5.542661793640976</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.9391336677098687</v>
+        <v>0.8980193781735339</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.6523422244055839</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.724035185300322</v>
+        <v>2.671447347990797</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191732</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.553636481823004</v>
+        <v>-5.656422205663841</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.8888149353721837</v>
+        <v>0.8477006458358489</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.6523422244055839</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.719220617771782</v>
+        <v>2.666632780462257</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.970028356110001</v>
+        <v>-6.072814079950838</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.720252236266262</v>
+        <v>0.6791379467299272</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.6523422244055839</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.71721466838066</v>
+        <v>2.664626831071135</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097815</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.331201985926989</v>
+        <v>-6.433987709767826</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5860414750081455</v>
+        <v>0.5449271854718107</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.6523422244055839</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.727473359049339</v>
+        <v>2.674885521739814</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309411</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.674460505570008</v>
+        <v>-6.777246229410845</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.4448376322966334</v>
+        <v>0.4037233427602986</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.6523422244055839</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.723572924195034</v>
+        <v>2.670985086885509</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.722663322812352</v>
+        <v>-6.825449046653189</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.4239614254546966</v>
+        <v>0.3828471359183618</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.6523422244055839</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.721977844250035</v>
+        <v>2.669390006940509</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.019324664622549</v>
+        <v>-7.122110388463386</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.3090758646598259</v>
+        <v>0.2679615751234912</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.7210853601394625</v>
+        <v>-0.8087317556553376</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.684510938738916</v>
+        <v>2.631923101429391</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.206044372931852</v>
+        <v>-7.308830096772689</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2303616768017016</v>
+        <v>0.1892473872653668</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.7210853601394625</v>
+        <v>-0.8087317556553376</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.680484634204513</v>
+        <v>2.627896796894988</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.589045761674483</v>
+        <v>-7.69183148551532</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.07705901998306519</v>
+        <v>0.03594473044673041</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.7210853601394625</v>
+        <v>-0.8087317556553376</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.680382532882929</v>
+        <v>2.627794695573404</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.593532206875872</v>
+        <v>-7.696317930716709</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.07783595787394004</v>
+        <v>0.03672166833760526</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.7255718053408511</v>
+        <v>-0.8132182008567264</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.680262181733525</v>
+        <v>2.627674344424</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737164</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.953062529379873</v>
+        <v>-8.055848253220711</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.06062586782961077</v>
+        <v>-0.1017401573659455</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.7255718053408511</v>
+        <v>-0.8132182008567264</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.685612485031576</v>
+        <v>2.63302464772205</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341307</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.003411592834095</v>
+        <v>-8.106197316674933</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.07284947325412183</v>
+        <v>-0.1139637627904571</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.7759208687950732</v>
+        <v>-0.8635672643109484</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.66331906691622</v>
+        <v>2.610731229606695</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.101030870255492</v>
+        <v>-8.203816594096329</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1088554336009118</v>
+        <v>-0.1499697231372465</v>
       </c>
       <c r="F1876" t="n">
-        <v>-0.8735401462164698</v>
+        <v>-0.9611865417323451</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.607789251085151</v>
+        <v>2.555201413775626</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.155102369763851</v>
+        <v>-8.257888093604688</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1275904770826832</v>
+        <v>-0.168704766619018</v>
       </c>
       <c r="F1877" t="n">
-        <v>-0.9276116457248292</v>
+        <v>-1.015258041240704</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.578239907701708</v>
+        <v>2.525652070392182</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.359360545093715</v>
+        <v>-8.462146268934552</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2037805500959862</v>
+        <v>-0.2448948396323209</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.055250590338818</v>
+        <v>-1.142896985854693</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.507169738051957</v>
+        <v>2.454581900742431</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.393013383602188</v>
+        <v>-8.495799107443025</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2127591310149395</v>
+        <v>-0.2538734205512743</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.155663958255855</v>
+        <v>-1.243310353771731</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.45140427178617</v>
+        <v>2.398816434476645</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.319543551934739</v>
+        <v>-8.422329275775576</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1679994968545389</v>
+        <v>-0.2091137863908736</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.082194126588407</v>
+        <v>-1.169840522104282</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.51085787228006</v>
+        <v>2.458270034970535</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.494667969321283</v>
+        <v>-8.597453693162119</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2234940430616392</v>
+        <v>-0.264608332597974</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.257318543974951</v>
+        <v>-1.344964939490826</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.420338442595651</v>
+        <v>2.367750605286126</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.729120063335772</v>
+        <v>-8.831905787176609</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3244940455690313</v>
+        <v>-0.3656083351053661</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.257318543974951</v>
+        <v>-1.344964939490826</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.413119277694055</v>
+        <v>2.36053144038453</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.833494794362219</v>
+        <v>-8.936280518203056</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.372916128753586</v>
+        <v>-0.4140304182899208</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.361693275001396</v>
+        <v>-1.449339670517272</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.343822248304211</v>
+        <v>2.291234410994686</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.996008260060803</v>
+        <v>-9.09879398390164</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4368057251944633</v>
+        <v>-0.477920014730798</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.459326705420083</v>
+        <v>-1.546973100935959</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.286357979891556</v>
+        <v>2.23377014258203</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.122045053429092</v>
+        <v>-9.224830777269929</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.4845267139126643</v>
+        <v>-0.5256410034489991</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.434075082610341</v>
+        <v>-1.521721478126216</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.304202682206515</v>
+        <v>2.25161484489699</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.064973281533161</v>
+        <v>-9.167759005373998</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4577076694678914</v>
+        <v>-0.4988219590042262</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.434075082610341</v>
+        <v>-1.521721478126216</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.308193017892917</v>
+        <v>2.255605180583391</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.206645123257282</v>
+        <v>-9.309430847098119</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5158516330562812</v>
+        <v>-0.556965922592616</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.434075082610341</v>
+        <v>-1.521721478126216</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.306717790994175</v>
+        <v>2.254129953684649</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.157054278832447</v>
+        <v>-9.259840002673284</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.480961885121475</v>
+        <v>-0.5220761746578098</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.384484238185507</v>
+        <v>-1.472130633701382</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.351525707813948</v>
+        <v>2.298937870504422</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.008135944360591</v>
+        <v>-9.110921668201428</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4344456849794156</v>
+        <v>-0.4755599745157504</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.353234647450334</v>
+        <v>-1.440881042966209</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.357224328608368</v>
+        <v>2.304636491298843</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.782290791641181</v>
+        <v>-8.885076515482016</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3345285508554428</v>
+        <v>-0.3756428403917771</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.31130797186317</v>
+        <v>-1.398954367379046</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.391959406996875</v>
+        <v>2.33937156968735</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.657712135303589</v>
+        <v>-8.760497859144424</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.2835579437643472</v>
+        <v>-0.3246722333006811</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.31130797186317</v>
+        <v>-1.398954367379046</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.393098551552934</v>
+        <v>2.340510714243409</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.710607423347875</v>
+        <v>-8.813393147188711</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3020822848199542</v>
+        <v>-0.3431965743562881</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.306352625774724</v>
+        <v>-1.393999021290599</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.398705533368109</v>
+        <v>2.346117696058584</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.638474248059994</v>
+        <v>-8.741259971900829</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.267495310466165</v>
+        <v>-0.3086096000024994</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.306352625774724</v>
+        <v>-1.393999021290599</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.404439237606746</v>
+        <v>2.351851400297221</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.567107855450347</v>
+        <v>-8.669893579291182</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2486860158161717</v>
+        <v>-0.2898003053525056</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.234986233165076</v>
+        <v>-1.322632628680952</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.437521810778669</v>
+        <v>2.384933973469144</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.473648821465122</v>
+        <v>-8.576434545305958</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2211858835349894</v>
+        <v>-0.2623001730713233</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.234986233165076</v>
+        <v>-1.322632628680952</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.427638329465762</v>
+        <v>2.375050492156237</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436224</v>
+        <v>3.766317079436225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.387894043344886</v>
+        <v>-8.565781363752526</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.1887185327862686</v>
+        <v>-0.2598734609493243</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.234986233165076</v>
+        <v>-1.322632628680952</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.425803768966388</v>
+        <v>2.373215931656863</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311944</v>
+        <v>3.784684521311945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.289987004668395</v>
+        <v>-8.467874325076036</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1498560322891329</v>
+        <v>-0.221010960452189</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.16700048330452</v>
+        <v>-1.254646878820395</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.466294903909261</v>
+        <v>2.413707066599736</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097239</v>
+        <v>3.80082935409724</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.266033463692438</v>
+        <v>-8.443920784100078</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1396061097532564</v>
+        <v>-0.2107610379163121</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.143046942328562</v>
+        <v>-1.230693337844438</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.481335534640329</v>
+        <v>2.428747697330804</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.001973525369642</v>
+        <v>-8.179860845777281</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.04724245058589016</v>
+        <v>-0.1183973787489458</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.8789870040057659</v>
+        <v>-0.9666333995216414</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.626511181472255</v>
+        <v>2.57392334416273</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.83325274783972</v>
+        <v>3.833252747839721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.294893901864804</v>
+        <v>-7.472781222272443</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2328023651557443</v>
+        <v>0.1616474369926886</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.8789870040057659</v>
+        <v>-0.9666333995216414</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.623724147811954</v>
+        <v>2.571136310502429</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388724</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.254709603498614</v>
+        <v>-7.432596923906252</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2492197083900618</v>
+        <v>0.1780647802270061</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.8388027056395752</v>
+        <v>-0.9264491011554506</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.64817835071951</v>
+        <v>2.595590513409984</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626469</v>
+        <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.091309732559251</v>
+        <v>-7.26919705296689</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.3139464779865637</v>
+        <v>0.242791549823508</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.6754028347002127</v>
+        <v>-0.7630492302160882</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.745585094503884</v>
+        <v>2.692997257194359</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.857828510329653</v>
+        <v>-7.035715830737291</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4152633957162557</v>
+        <v>0.3441084675532</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.4419216124706141</v>
+        <v>-0.5295680079864896</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.893598256679496</v>
+        <v>2.841010419369971</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.708162119322138</v>
+        <v>-6.886049439729776</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4722377418063024</v>
+        <v>0.4010828136432467</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.3490181212280782</v>
+        <v>-0.4366645167439537</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.946448141112058</v>
+        <v>2.893860303802533</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.575886645691251</v>
+        <v>-6.75377396609889</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.5205154180056843</v>
+        <v>0.4493604898426287</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.2167426475971915</v>
+        <v>-0.304389043113067</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.021180912037617</v>
+        <v>2.968593074728092</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.420148313131509</v>
+        <v>-6.598035633539148</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5856258117172177</v>
+        <v>0.514470883554162</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.06100431503744996</v>
+        <v>-0.1486507105533255</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.117438972261099</v>
+        <v>3.064851134951573</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.33518364640219</v>
+        <v>-6.513070966809828</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6325180196326041</v>
+        <v>0.5613630914695489</v>
       </c>
       <c r="F1907" t="n">
-        <v>0.02396035169186961</v>
+        <v>-0.06368604382400589</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.181324113522349</v>
+        <v>3.128736276212824</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.440773636175295</v>
+        <v>-6.618660956582932</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4623060941241435</v>
+        <v>0.3911511659610882</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.08162963808123475</v>
+        <v>-0.1692760335971102</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.989994190059268</v>
+        <v>2.937406352749742</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.372539051549867</v>
+        <v>-6.550426371957505</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5381442698514007</v>
+        <v>0.4669893416883455</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.06321431520869875</v>
+        <v>-0.1508607107245742</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.049587725659876</v>
+        <v>2.99699988835035</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.224599010142268</v>
+        <v>-6.402486330549905</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4774413637262729</v>
+        <v>0.4062864355632176</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.04289339930014119</v>
+        <v>-0.1305397948160167</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.941901352516843</v>
+        <v>2.889313515207317</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.171629487888279</v>
+        <v>-6.349516808295917</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4899151863743905</v>
+        <v>0.4187602582113348</v>
       </c>
       <c r="F1911" t="n">
-        <v>0.01007612295384769</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.964969079615758</v>
+        <v>2.912381242306233</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.005841291927989</v>
+        <v>-6.183728612335626</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.5492698526634134</v>
+        <v>0.4781149245003582</v>
       </c>
       <c r="F1912" t="n">
-        <v>0.01007612295384769</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.958008467520665</v>
+        <v>2.90542063021114</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.97247808544922</v>
+        <v>-6.150365405856857</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5770774896360642</v>
+        <v>0.5059225614730085</v>
       </c>
       <c r="F1913" t="n">
-        <v>0.01007612295384769</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.972470821901808</v>
+        <v>2.919882984592283</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.864218948326698</v>
+        <v>-6.042106268734336</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.6149132649442679</v>
+        <v>0.5437583367812122</v>
       </c>
       <c r="F1914" t="n">
-        <v>0.01007612295384769</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.967002942361003</v>
+        <v>2.914415105051478</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.740927813509567</v>
+        <v>-5.918815133917205</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.661727812881697</v>
+        <v>0.5905728847186418</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.1333672577709782</v>
+        <v>0.04572086225510269</v>
       </c>
       <c r="G1915" t="n">
-        <v>3.038475717261858</v>
+        <v>2.985887879952333</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.688230946378276</v>
+        <v>-5.866118266785914</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6905075379715386</v>
+        <v>0.6193526098084834</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.1860641249022694</v>
+        <v>0.09841772938639387</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.077794815777958</v>
+        <v>3.025206978468433</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.444465504394832</v>
+        <v>-5.622352824802469</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7837944231119671</v>
+        <v>0.7126394949489119</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.1860641249022694</v>
+        <v>0.09841772938639387</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.073575524125009</v>
+        <v>3.020987686815483</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.35468983201836</v>
+        <v>-5.532577152425997</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.8218290059825719</v>
+        <v>0.7506740778195167</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.2476635698165794</v>
+        <v>0.1600171743007039</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.112659504993611</v>
+        <v>3.060071667684086</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.104839438069285</v>
+        <v>-5.282726758476922</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.914511238545904</v>
+        <v>0.8433563103828488</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.2476635698165794</v>
+        <v>0.1600171743007039</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.105401579977313</v>
+        <v>3.052813742667788</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.928947345601853</v>
+        <v>-5.10683466600949</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9884671990535256</v>
+        <v>0.9173122708904704</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.2476635698165794</v>
+        <v>0.1600171743007039</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.109000703497962</v>
+        <v>3.056412866188436</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.757500882579389</v>
+        <v>-4.935388202987027</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.070373290317065</v>
+        <v>0.9992183621540094</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.4191100328390425</v>
+        <v>0.331463637323167</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.225196087365993</v>
+        <v>3.172608250056468</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.677478595470268</v>
+        <v>-4.855365915877906</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.10140268277701</v>
+        <v>1.030247754613955</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.4991323199481634</v>
+        <v>0.411485924432288</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.272229937247763</v>
+        <v>3.219642099938238</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.613842853236334</v>
+        <v>-4.791730173643971</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.131551780724901</v>
+        <v>1.060396852561846</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.562768062182098</v>
+        <v>0.4751216666662225</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.31510618364244</v>
+        <v>3.262518346332915</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074778</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.520145535019939</v>
+        <v>-4.698032855427576</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.150224966795255</v>
+        <v>1.079070038632199</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.562768062182098</v>
+        <v>0.4751216666662225</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.296300442426236</v>
+        <v>3.243712605116711</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769488424229</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.530648158085228</v>
+        <v>-4.636693222445151</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.147766994194017</v>
+        <v>1.105348968450047</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.5522654391168091</v>
+        <v>0.5364612996486477</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.29174194521194</v>
+        <v>3.282259461531043</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.458405589914033</v>
+        <v>-4.564450654273957</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.180593335297315</v>
+        <v>1.138175309553345</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.5522654391168091</v>
+        <v>0.5364612996486477</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.295671259046761</v>
+        <v>3.286188775365864</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232699787996</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.440691903036168</v>
+        <v>-4.546736967396091</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.188357393965801</v>
+        <v>1.145939368221831</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.5554467680137259</v>
+        <v>0.5396426285455646</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.29825864030225</v>
+        <v>3.288776156621354</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502332</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.331887017556441</v>
+        <v>-4.437932081916364</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.228877419377685</v>
+        <v>1.186459393633715</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.5554467680137259</v>
+        <v>0.5396426285455646</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.295256711522244</v>
+        <v>3.285774227841347</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675933</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.11186621951943</v>
+        <v>-4.217911283879354</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.318464775603103</v>
+        <v>1.276046749859134</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.6966666130817062</v>
+        <v>0.6808624736135448</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.381567655573646</v>
+        <v>3.37208517189275</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.978998530456152</v>
+        <v>-4.085043594816076</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.387506034030238</v>
+        <v>1.345088008286268</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.6966666130817062</v>
+        <v>0.6808624736135448</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.39746183837547</v>
+        <v>3.387979354694573</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496258</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.858825447091653</v>
+        <v>-3.964870511451577</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.436721111816339</v>
+        <v>1.394303086072369</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.8168396964462051</v>
+        <v>0.8010355569780437</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.470711532834471</v>
+        <v>3.461229049153574</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576995</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.723572085761676</v>
+        <v>-3.8296171501216</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.50091055890977</v>
+        <v>1.4584925331658</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.9520930577761822</v>
+        <v>0.9362889183080209</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.561951652193897</v>
+        <v>3.552469168513</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942101</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.783446913119368</v>
+        <v>-3.889491977479293</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.462998119368119</v>
+        <v>1.420580093624149</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.8922182304184901</v>
+        <v>0.8764140909503287</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.512064247180708</v>
+        <v>3.502581763499811</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.663626682208531</v>
+        <v>-3.769671746568455</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.526215380966663</v>
+        <v>1.483797355222692</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.8922182304184901</v>
+        <v>0.8764140909503287</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.527353416414916</v>
+        <v>3.517870932734019</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430689</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.666096388670337</v>
+        <v>-3.772141453030261</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.432871697704382</v>
+        <v>1.390453671960412</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.889748523956684</v>
+        <v>0.8739443844885226</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.433515791860274</v>
+        <v>3.424033308179377</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003596</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.734466574994347</v>
+        <v>-3.840511639354271</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.324785484660079</v>
+        <v>1.282367458916109</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.899024222992899</v>
+        <v>0.8832200835247376</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.358343072767305</v>
+        <v>3.348860589086407</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508365</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.748254627841393</v>
+        <v>-3.854299692201318</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.309706972153152</v>
+        <v>1.267288946409182</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.899024222992899</v>
+        <v>0.8832200835247376</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.348779781399196</v>
+        <v>3.339297297718299</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.803774703733983</v>
+        <v>-3.909819768093907</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.424529778488318</v>
+        <v>1.382111752744348</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.899024222992899</v>
+        <v>0.8832200835247376</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.485810618091398</v>
+        <v>3.476328134410501</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.628300443941514</v>
+        <v>-3.734345508301438</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.499286714397094</v>
+        <v>1.456868688653124</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.899024222992899</v>
+        <v>0.8832200835247376</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.490377850083186</v>
+        <v>3.480895366402289</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322544</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.739236696582762</v>
+        <v>-3.845281760942687</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.430654242101802</v>
+        <v>1.388236216357831</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.899024222992899</v>
+        <v>0.8832200835247376</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.466119878844393</v>
+        <v>3.456637395163496</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.70557315111048</v>
+        <v>-3.811618215470405</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.372657973692164</v>
+        <v>1.330239947948194</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.9326877684651809</v>
+        <v>0.9168836289970195</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.414856319529212</v>
+        <v>3.405373835848315</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.645720531906757</v>
+        <v>-3.751765596266682</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.406771407805786</v>
+        <v>1.364353382061815</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.9326877684651809</v>
+        <v>0.9168836289970195</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.425028705961344</v>
+        <v>3.415546222280447</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.55947706888038</v>
+        <v>-3.665522133240304</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.436215063590197</v>
+        <v>1.393797037846227</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.9326877684651809</v>
+        <v>0.9168836289970195</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.419974976535205</v>
+        <v>3.410492492854308</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.60478388827936</v>
+        <v>-3.710828952639284</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.409868111275131</v>
+        <v>1.36745008553116</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.8918776054559501</v>
+        <v>0.8760734659877887</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.387264654174192</v>
+        <v>3.377782170493295</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.75357116580319</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.633816992981661</v>
+        <v>-3.739862057341586</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.398806742427311</v>
+        <v>1.356388716683341</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.8918776054559501</v>
+        <v>0.8760734659877887</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.387816527207293</v>
+        <v>3.378334043526396</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.541006511530802</v>
+        <v>-3.647051575890726</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.365203626899021</v>
+        <v>1.322785601155051</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.9846880869068094</v>
+        <v>0.968883947438648</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.372775507969174</v>
+        <v>3.363293024288278</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.58539598086023</v>
+        <v>-3.691441045220154</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.349321315091851</v>
+        <v>1.30690328934788</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.9402986175773818</v>
+        <v>0.9244944781092204</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.348015302296119</v>
+        <v>3.338532818615222</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.701937585965573</v>
+        <v>-3.807982650325497</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.297780381561436</v>
+        <v>1.255362355817466</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.823757012472039</v>
+        <v>0.8079528730038776</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.273166047744636</v>
+        <v>3.263683564063739</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.741861680548144</v>
+        <v>-3.847906744908069</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.287302039559075</v>
+        <v>1.244884013815105</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.823757012472039</v>
+        <v>0.8079528730038776</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.278657343575303</v>
+        <v>3.269174859894406</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.769642078449497</v>
+        <v>-3.875687142809422</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.287687082167073</v>
+        <v>1.245269056423103</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7959766145706859</v>
+        <v>0.7801724751025245</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.27348630660303</v>
+        <v>3.264003822922134</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.888022751179636</v>
+        <v>-3.99406781553956</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.078690533075671</v>
+        <v>1.036272507331701</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.7287587624197097</v>
+        <v>0.7129546229515483</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.071511315313098</v>
+        <v>3.062028831632201</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.996636829622967</v>
+        <v>-4.102681893982892</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.155394562417544</v>
+        <v>1.112976536673574</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.7287587624197097</v>
+        <v>0.7129546229515483</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.191660976032304</v>
+        <v>3.182178492351407</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.961227791374824</v>
+        <v>-4.067272855734749</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.184071203819124</v>
+        <v>1.141653178075154</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.7287587624197097</v>
+        <v>0.7129546229515483</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.206174002134627</v>
+        <v>3.19669151845373</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.922844128816673</v>
+        <v>-4.028889193176598</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.196844110184753</v>
+        <v>1.154426084440783</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7671424249778609</v>
+        <v>0.7513382855096995</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.226623641011886</v>
+        <v>3.217141157330989</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.745727798781507</v>
+        <v>-3.851772863141432</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.264419671044122</v>
+        <v>1.222001645300151</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7671424249778609</v>
+        <v>0.7513382855096995</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.223352669857188</v>
+        <v>3.213870186176291</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.790820043615052</v>
+        <v>-3.896865107974977</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.247066164872616</v>
+        <v>1.204648139128646</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.7052463818084711</v>
+        <v>0.6894422423403097</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.186898435717467</v>
+        <v>3.17741595203657</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.611444622376284</v>
+        <v>-3.71748968673621</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.312603308674538</v>
+        <v>1.270185282930568</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.8620231399791898</v>
+        <v>0.8462190005110284</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.274751465926313</v>
+        <v>3.265268982245416</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.656458835896891</v>
+        <v>-3.762503900256816</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.275405078597885</v>
+        <v>1.232987052853915</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.8316742446645852</v>
+        <v>0.8158701051964238</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.23734958406914</v>
+        <v>3.227867100388243</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.923463346169326</v>
+        <v>-4.029508410529251</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.174294836827857</v>
+        <v>1.131876811083886</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.6373112066216367</v>
+        <v>0.6215070671534753</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.126423323582316</v>
+        <v>3.11694083990142</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.024661127606499</v>
+        <v>-4.130706191966424</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.133019646149489</v>
+        <v>1.090601620405519</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5689023930763175</v>
+        <v>0.5530982536081561</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.084581957351626</v>
+        <v>3.07509947367073</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.018150160992186</v>
+        <v>-4.124195225352111</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.133223994349531</v>
+        <v>1.09080596860556</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5689023930763175</v>
+        <v>0.5530982536081561</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.082181918905943</v>
+        <v>3.072699435225046</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.999112033284889</v>
+        <v>-4.105157097644814</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.137363964640695</v>
+        <v>1.094945938896724</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.510718781745123</v>
+        <v>0.4949146422769616</v>
       </c>
       <c r="G1962" t="n">
-        <v>3.043796471315471</v>
+        <v>3.034313987634574</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.051627835559709</v>
+        <v>-4.157672899919635</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.235652045364957</v>
+        <v>1.193234019620987</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.510718781745123</v>
+        <v>0.4949146422769616</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.163090872949661</v>
+        <v>3.153608389268765</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.065494596893627</v>
+        <v>-4.171539661253552</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.230938669817523</v>
+        <v>1.188520644073553</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4728608650113</v>
+        <v>0.4570567255431386</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.141209451895501</v>
+        <v>3.131726968214605</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.020690425353697</v>
+        <v>-4.126735489713623</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.254868868830421</v>
+        <v>1.212450843086451</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4728608650113</v>
+        <v>0.4570567255431386</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.147217982292427</v>
+        <v>3.13773549861153</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.872947455118695</v>
+        <v>-3.97899251947862</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.211916278201622</v>
+        <v>1.169498252457651</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.6406682222461832</v>
+        <v>0.6248640827780219</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.145852617910557</v>
+        <v>3.13637013422966</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.956768676393393</v>
+        <v>-4.062813740753318</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.181181411223223</v>
+        <v>1.138763385479253</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.6406682222461832</v>
+        <v>0.6248640827780219</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.148646239442038</v>
+        <v>3.139163755761141</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.950615970340609</v>
+        <v>-4.056661034700534</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.184304842035995</v>
+        <v>1.141886816292025</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.6468209282989675</v>
+        <v>0.6310167888308061</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.153000211465367</v>
+        <v>3.14351772778447</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.96742526849111</v>
+        <v>-4.073470332851036</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.176661599515905</v>
+        <v>1.134243573771935</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.630011630148466</v>
+        <v>0.6142074906803046</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.141995109315176</v>
+        <v>3.132512625634279</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.905127269714988</v>
+        <v>-4.011172334074914</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.267916352823175</v>
+        <v>1.225498327079204</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.675305894422908</v>
+        <v>0.6595017549547466</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.235507221676662</v>
+        <v>3.226024737995765</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.70333707204983</v>
+        <v>-3.809382136409756</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.150924433603365</v>
+        <v>1.108506407859394</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.8733240865920624</v>
+        <v>0.857519947123901</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.156610138692282</v>
+        <v>3.147127655011385</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.754223784736025</v>
+        <v>-3.86026884909595</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.200859980851062</v>
+        <v>1.158441955107092</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.8224373739058679</v>
+        <v>0.8066332344377065</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.19636834340274</v>
+        <v>3.186885859721843</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.667613042086218</v>
+        <v>-3.773658106446143</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.250132014027029</v>
+        <v>1.207713988283058</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.9010631051110262</v>
+        <v>0.8852589656428648</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.258171518241879</v>
+        <v>3.248689034560982</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.727822340091502</v>
+        <v>-3.833867404451428</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.224584275649587</v>
+        <v>1.182166249905616</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.8408538071057416</v>
+        <v>0.8250496676375803</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.22058192026338</v>
+        <v>3.211099436582483</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.651400293659576</v>
+        <v>-3.757445358019501</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.253644712262286</v>
+        <v>1.211226686518315</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.8408538071057416</v>
+        <v>0.8250496676375803</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.219073538303308</v>
+        <v>3.209591054622412</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316248</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.607027162021007</v>
+        <v>-3.713072226380932</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.27125683235315</v>
+        <v>1.228838806609179</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8852269387443102</v>
+        <v>0.8694227992761488</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.245560284721886</v>
+        <v>3.236077801040989</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.629507512879892</v>
+        <v>-3.735552577239817</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.256658486148186</v>
+        <v>1.214240460404216</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8852269387443102</v>
+        <v>0.8694227992761488</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.239954078860476</v>
+        <v>3.230471595179579</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.581851782318836</v>
+        <v>-3.687896846678761</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.282102535400413</v>
+        <v>1.239684509656443</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.9328826693053659</v>
+        <v>0.9170785298372045</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.274929274224914</v>
+        <v>3.265446790544018</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.481333623820081</v>
+        <v>-3.587378688180006</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.32720217217464</v>
+        <v>1.28478414643067</v>
       </c>
       <c r="F1979" t="n">
-        <v>1.03340082780412</v>
+        <v>1.017596688335959</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.340132542698892</v>
+        <v>3.330650059017995</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.465428294387729</v>
+        <v>-3.571473358747654</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.320318976423453</v>
+        <v>1.277900950679483</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.9542881670948815</v>
+        <v>0.9384840276267201</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.279419618749221</v>
+        <v>3.269937135068324</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.420589892779331</v>
+        <v>-3.526634957139256</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.342352039677441</v>
+        <v>1.299934013933471</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.958831600039751</v>
+        <v>0.9430274605715896</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.286243381126771</v>
+        <v>3.276760897445874</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.440088349021339</v>
+        <v>-3.546133413381264</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.338713596811716</v>
+        <v>1.296295571067745</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.9107469587598467</v>
+        <v>0.8949428192916853</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.261553535989906</v>
+        <v>3.25207105230901</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.395885511935438</v>
+        <v>-3.501930576295364</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.362274334173913</v>
+        <v>1.319856308429943</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.9549497958457471</v>
+        <v>0.9391456563775857</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.293954840769284</v>
+        <v>3.284472357088387</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.403445177772485</v>
+        <v>-3.509490242132411</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.357660468308342</v>
+        <v>1.315242442564371</v>
       </c>
       <c r="F1984" t="n">
-        <v>1.009753199855566</v>
+        <v>0.993949060387405</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.325246883644423</v>
+        <v>3.315764399963526</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.245153760233213</v>
+        <v>-3.351198824593138</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.47222480050709</v>
+        <v>1.42980677476312</v>
       </c>
       <c r="F1985" t="n">
-        <v>1.009753199855566</v>
+        <v>0.993949060387405</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.376494648827463</v>
+        <v>3.367012165146566</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.037511756598737</v>
+        <v>-3.143556820958662</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.553722306555134</v>
+        <v>1.511304280811163</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.217395203490043</v>
+        <v>1.201591064021881</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.499520555602401</v>
+        <v>3.490038071921505</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.986479663876209</v>
+        <v>-3.092524728236134</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.569083371882415</v>
+        <v>1.526665346138445</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.26842729621257</v>
+        <v>1.252623156744409</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.525088039474188</v>
+        <v>3.515605555793291</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404853</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.921255482749003</v>
+        <v>-3.027300547108928</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.612360448426003</v>
+        <v>1.569942422682032</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.333651477339776</v>
+        <v>1.317847337871615</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.581409952243217</v>
+        <v>3.57192746856232</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882557</v>
+        <v>3.840061186882558</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.883828462677869</v>
+        <v>-2.989873527037795</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.623292228753736</v>
+        <v>1.580874203009766</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.338903015368958</v>
+        <v>1.323098875900797</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.580521847360006</v>
+        <v>3.571039363679109</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992661</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.903940118712578</v>
+        <v>-3.009985183072503</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.616504358671093</v>
+        <v>1.574086332927123</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.349930360366377</v>
+        <v>1.334126220898216</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.588395046689698</v>
+        <v>3.578912563008801</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.850195304285373</v>
+        <v>-2.956240368645298</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.798560055463186</v>
+        <v>1.756142029719215</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.359993669806839</v>
+        <v>1.344189530338678</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.754990803375186</v>
+        <v>3.745508319694289</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957625</v>
+        <v>3.813222820957626</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.77541304326036</v>
+        <v>-2.881458107620285</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.948585869091009</v>
+        <v>1.906167843347038</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.434775930831852</v>
+        <v>1.418971791363691</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.919973069208011</v>
+        <v>3.910490585527114</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998757</v>
+        <v>3.814230727998756</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.749328958996552</v>
+        <v>-2.855374023356477</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.95072747881039</v>
+        <v>1.90830945306642</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.434775930831852</v>
+        <v>1.418971791363691</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.91168104522187</v>
+        <v>3.902198561540973</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896931</v>
+        <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.661451045887432</v>
+        <v>-2.767496110247357</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.984071839637818</v>
+        <v>1.941653813893848</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.550701573255203</v>
+        <v>1.534897433787042</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.97942962625966</v>
+        <v>3.969947142578762</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959859</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.652558584494148</v>
+        <v>-2.758603648854073</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.005183229921923</v>
+        <v>1.962765204177952</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.550701573255203</v>
+        <v>1.534897433787042</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.996984031986451</v>
+        <v>3.987501548305554</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.821034701464026</v>
+        <v>-2.927079765823951</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.929647830538555</v>
+        <v>1.887229804794585</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.522753737538622</v>
+        <v>1.506949598070461</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.972070377961087</v>
+        <v>3.96258789428019</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.79557406678271</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.374778508834586</v>
+        <v>-2.480823573194511</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.089420004778193</v>
+        <v>2.047001979034223</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.428035067868989</v>
+        <v>1.412230928400828</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.896508873347169</v>
+        <v>3.887026389666272</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632638</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.352057405151434</v>
+        <v>-2.458102469511359</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.089172468748359</v>
+        <v>2.046754443004389</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.428035067868989</v>
+        <v>1.412230928400828</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.887172895844073</v>
+        <v>3.877690412163177</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777674</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.481259218445476</v>
+        <v>-2.587304282805401</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.196397869281911</v>
+        <v>2.15397984353794</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.298833254574947</v>
+        <v>1.283029115106786</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.968557933718817</v>
+        <v>3.95907545003792</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644414</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.636040225223732</v>
+        <v>-2.742085289583657</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.171563289064255</v>
+        <v>2.129145263320285</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.265465580520471</v>
+        <v>1.24966144105231</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.985615151779778</v>
+        <v>3.976132668098881</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799966</v>
+        <v>3.769443619799964</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.628985535008558</v>
+        <v>-2.735030599368483</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.17106052113987</v>
+        <v>2.1286424953959</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.272520270735645</v>
+        <v>1.256716131267484</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.986523321898427</v>
+        <v>3.977040838217531</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.60203431068207</v>
+        <v>-2.708079375041995</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.191847164515207</v>
+        <v>2.149429138771236</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.287400616763364</v>
+        <v>1.271596477295203</v>
       </c>
       <c r="G2002" t="n">
-        <v>4.005457683159801</v>
+        <v>3.995975199478903</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784109</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.737987318738386</v>
+        <v>-2.844032383098312</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.32156909343764</v>
+        <v>2.279151067693669</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.287400616763364</v>
+        <v>1.271596477295203</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.18956081530476</v>
+        <v>4.180078331623863</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714428</v>
+        <v>3.743925505714426</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.760395436543258</v>
+        <v>-2.866440500903184</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.304722541218684</v>
+        <v>2.262304515474714</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.287400616763364</v>
+        <v>1.271596477295203</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.181677510207753</v>
+        <v>4.172195026526857</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.788619672120859</v>
+        <v>-2.894664736480784</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.295486846537282</v>
+        <v>2.253068820793311</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.305377369214673</v>
+        <v>1.289573229746511</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.194517561228176</v>
+        <v>4.185035077547279</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161979</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.798060598009389</v>
+        <v>-2.904105662369314</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.347964193903717</v>
+        <v>2.305546168159746</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.427804486758064</v>
+        <v>1.412000347289903</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.324227549476058</v>
+        <v>4.314745065795162</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321636</v>
+        <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.85033420534503</v>
+        <v>-2.956379269704955</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.329945845514761</v>
+        <v>2.287527819770791</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.375530879422423</v>
+        <v>1.359726739954262</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.295754479619974</v>
+        <v>4.286271995939077</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347705</v>
+        <v>3.727898186347704</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.926664182945936</v>
+        <v>-3.032709247305861</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.297525667368174</v>
+        <v>2.255107641624203</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.375530879422423</v>
+        <v>1.359726739954262</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.293866292513749</v>
+        <v>4.284383808832852</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887749</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.128917903270289</v>
+        <v>-3.234962967630215</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.211444408841295</v>
+        <v>2.169026383097324</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.173277159098069</v>
+        <v>1.157473019629908</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.167334289922</v>
+        <v>4.157851806241102</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343068</v>
+        <v>3.712897612343067</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.290486328797544</v>
+        <v>-3.39653139315747</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.145251048840545</v>
+        <v>2.102833023096575</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.04649423530019</v>
+        <v>1.030690095832029</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.089698545853424</v>
+        <v>4.080216062172528</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389351</v>
+        <v>3.75459613538935</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.422787620895098</v>
+        <v>-3.528832685255023</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.105403938867442</v>
+        <v>2.062985913123472</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.04649423530019</v>
+        <v>1.030690095832029</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.102771952719342</v>
+        <v>4.093289469038446</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378394</v>
+        <v>3.749882691378392</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.608655931734328</v>
+        <v>-3.714700996094253</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.02306181131469</v>
+        <v>1.98064378557072</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8879286419802424</v>
+        <v>0.8721245025120812</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.999637793510314</v>
+        <v>3.990155309829417</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006977</v>
+        <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.636556718843801</v>
+        <v>-3.742601783203726</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.010425537597903</v>
+        <v>1.968007511853933</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8533317178373075</v>
+        <v>0.8375275783691464</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.977403680151555</v>
+        <v>3.967921196470659</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787388</v>
+        <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.759082821546694</v>
+        <v>-3.86512788590662</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.958179540493944</v>
+        <v>1.915761514749974</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7308056151344137</v>
+        <v>0.7150014756662525</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.900652462507018</v>
+        <v>3.891169978826121</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585939</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.989597317732283</v>
+        <v>-4.095642382092208</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.932679701610213</v>
+        <v>1.890261675866242</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5002911189488249</v>
+        <v>0.4844869794806638</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.829049724386168</v>
+        <v>3.819567240705271</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814666</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.246318135727107</v>
+        <v>-4.352363200087032</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.97030309341413</v>
+        <v>1.92788506767016</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3918765448050101</v>
+        <v>0.3760724053368489</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.904312698901726</v>
+        <v>3.894830215220829</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237095</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.400304553503248</v>
+        <v>-4.506349617863172</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.977688795449314</v>
+        <v>1.935270769705344</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3918765448050101</v>
+        <v>0.3760724053368489</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.973292968047366</v>
+        <v>3.963810484366469</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423388</v>
+        <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.349782649675582</v>
+        <v>-4.455827714035506</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.983948759100501</v>
+        <v>1.941530733356531</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3918765448050101</v>
+        <v>0.3760724053368489</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.959344170167487</v>
+        <v>3.949861686486591</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609754</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.602257803683306</v>
+        <v>-4.708302868043231</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.894829186552825</v>
+        <v>1.852411160808855</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3918765448050101</v>
+        <v>0.3760724053368489</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.971214659222901</v>
+        <v>3.961732175542005</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973158</v>
+        <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.895153560162719</v>
+        <v>-5.001198624522643</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.778881418480004</v>
+        <v>1.736463392736034</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3918765448050101</v>
+        <v>0.3760724053368489</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.972425193741844</v>
+        <v>3.962942710060948</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.05269763189216</v>
+        <v>-5.158742696252085</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.719985532015549</v>
+        <v>1.677567506271579</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3249747396647356</v>
+        <v>0.3091706001965744</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.936405852885001</v>
+        <v>3.926923369204105</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916203</v>
+        <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.330662027475434</v>
+        <v>-5.436707091835358</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.603877626518429</v>
+        <v>1.561459600774459</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2353550053792514</v>
+        <v>0.2195508659110902</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.8777118650499</v>
+        <v>3.868229381369003</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830329</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.447629720114325</v>
+        <v>-5.553674784474249</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.719294606161916</v>
+        <v>1.676876580417946</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2353550053792514</v>
+        <v>0.2195508659110902</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.039915921748944</v>
+        <v>4.030433438068048</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071552</v>
+        <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.532347662335278</v>
+        <v>-5.638392726695202</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.680254067237349</v>
+        <v>1.637836041493379</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.150238976451205</v>
+        <v>0.1344348369830438</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.983692942355931</v>
+        <v>3.974210458675034</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.614282480604161</v>
+        <v>-5.720327544964086</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.657709557498287</v>
+        <v>1.615291531754317</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1403042308641248</v>
+        <v>0.1245000913959636</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.987961512572173</v>
+        <v>3.978479028891277</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332691</v>
+        <v>3.783632867332692</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.716258602852569</v>
+        <v>-5.822303667212493</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.625844747054827</v>
+        <v>1.583426721310857</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.03832810861571723</v>
+        <v>0.02252396914755606</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.935701477679031</v>
+        <v>3.926218993998135</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.606252319375347</v>
+        <v>-5.712297383735272</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.66200014768989</v>
+        <v>1.61958212194592</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.06153268053299243</v>
+        <v>0.04572854106483126</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.941777108073572</v>
+        <v>3.932294624392675</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818523</v>
+        <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.463192743634422</v>
+        <v>-5.569237807994346</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.723473988708235</v>
+        <v>1.681055962964265</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.06954610712297171</v>
+        <v>0.05374196765481054</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.950835174749534</v>
+        <v>3.941352691068637</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051789</v>
+        <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.161746018162584</v>
+        <v>-5.267791082522509</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.851313561779506</v>
+        <v>1.808895536035536</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.370992832594809</v>
+        <v>0.3551886931266478</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.138964092915172</v>
+        <v>4.129481609234276</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679625</v>
+        <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.186336262397768</v>
+        <v>-5.292381326757693</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.842448641838143</v>
+        <v>1.800030616094173</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.370992832594809</v>
+        <v>0.3551886931266478</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.139935270667883</v>
+        <v>4.130452786986986</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.82118418247416</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.135297886391248</v>
+        <v>-5.241342950751172</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.863706896620506</v>
+        <v>1.821288870876536</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.370992832594809</v>
+        <v>0.3551886931266478</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.140778175047638</v>
+        <v>4.131295691366741</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.094158591524617</v>
+        <v>-5.200203655884541</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.899200713441304</v>
+        <v>1.856782687697334</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4121321274614398</v>
+        <v>0.3963279879932786</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.184499850841762</v>
+        <v>4.175017367160866</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.983552451445015</v>
+        <v>-5.08959751580494</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.759627165597079</v>
+        <v>1.717209139853109</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5227382675410418</v>
+        <v>0.5069341280728806</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.067047531013458</v>
+        <v>4.057565047332561</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.114133185975858</v>
+        <v>-5.220178250335782</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.710896915858706</v>
+        <v>1.668478890114736</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3921575330101993</v>
+        <v>0.3763533935420381</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.992201134368916</v>
+        <v>3.982718650688019</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.949636851784896</v>
+        <v>-5.05568191614482</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.761122268611173</v>
+        <v>1.718704242867203</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3921575330101993</v>
+        <v>0.3763533935420381</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.976627953444998</v>
+        <v>3.967145469764102</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077629</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.977006784469328</v>
+        <v>-5.083051848829252</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.74936200597383</v>
+        <v>1.70694398022986</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3921575330101993</v>
+        <v>0.3763533935420381</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.975815663881428</v>
+        <v>3.966333180200531</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.987391979359217</v>
+        <v>-5.093437043719142</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.755076707142947</v>
+        <v>1.712658681398977</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.38177233812031</v>
+        <v>0.3659681986521488</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.979453326072567</v>
+        <v>3.96997084239167</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.005980138081442</v>
+        <v>-5.112025202441367</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.818478449430482</v>
+        <v>1.776060423686512</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.3631841793980846</v>
+        <v>0.3473800399299234</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.039137436615657</v>
+        <v>4.02965495293476</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496555</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.006278684777478</v>
+        <v>-5.112323749137403</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.815228041570366</v>
+        <v>1.772810015826396</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.3631841793980846</v>
+        <v>0.3473800399299234</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.036006447433955</v>
+        <v>4.026523963753059</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.905455551087051</v>
+        <v>-5.011500615446975</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.860088189985929</v>
+        <v>1.817670164241958</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.3756483948824385</v>
+        <v>0.3598442554142773</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.048015871663959</v>
+        <v>4.038533387983063</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.714674190334644</v>
+        <v>-4.820719254694568</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.936529987765435</v>
+        <v>1.894111962021465</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.5664297556348459</v>
+        <v>0.5506256161666847</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.162613941593947</v>
+        <v>4.15313145791305</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.696157336292823</v>
+        <v>-4.802202400652748</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.92377357511976</v>
+        <v>1.881355549375789</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5793598850600541</v>
+        <v>0.5635557455918929</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.150208864986668</v>
+        <v>4.140726381305772</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912986</v>
+        <v>3.785761685912985</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.670964151791505</v>
+        <v>-4.77700921615143</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.968817785532345</v>
+        <v>1.926399759788375</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6045530695613724</v>
+        <v>0.5887489300932113</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.200291712299518</v>
+        <v>4.190809228618621</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539895</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.658910024878542</v>
+        <v>-4.764955089238467</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.967326004198968</v>
+        <v>1.924907978454998</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6166071964743353</v>
+        <v>0.6008030570061741</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.201210756348734</v>
+        <v>4.191728272667836</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.72501084481101</v>
+        <v>3.725010844811009</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.665533271568901</v>
+        <v>-4.771578335928825</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.966557335706961</v>
+        <v>1.924139309962991</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.609983949783977</v>
+        <v>0.5941798103158158</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.199117438518654</v>
+        <v>4.189634954837757</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.562652682040308</v>
+        <v>-4.668697746400232</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.02056059739628</v>
+        <v>1.97814257165231</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7128645393125699</v>
+        <v>0.6970603998444087</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.273696818113693</v>
+        <v>4.264214334432795</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760317</v>
+        <v>3.646857607760315</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.586094721220395</v>
+        <v>-4.692139785580319</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.03138645189784</v>
+        <v>1.988968426153869</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7128645393125699</v>
+        <v>0.6970603998444087</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.293899488287287</v>
+        <v>4.284417004606389</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781707</v>
+        <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.604167229512006</v>
+        <v>-4.710212293871931</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.024157448581195</v>
+        <v>1.981739422837225</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7128645393125699</v>
+        <v>0.6970603998444087</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.293899488287287</v>
+        <v>4.284417004606389</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082836</v>
+        <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.835341023388638</v>
+        <v>-4.941386087748563</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.891939844624009</v>
+        <v>1.849521818880039</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7128645393125699</v>
+        <v>0.6970603998444087</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.254151401880753</v>
+        <v>4.244668918199856</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943587</v>
+        <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.804055002848183</v>
+        <v>-4.910100067208107</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.911476871837131</v>
+        <v>1.869058846093161</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.7441505598530253</v>
+        <v>0.7283464203848641</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.279945633201966</v>
+        <v>4.27046314952107</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677825</v>
+        <v>3.730590658677824</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.651029610734899</v>
+        <v>-4.757074675094823</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.071858028255349</v>
+        <v>2.029440002511379</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.8971759519663094</v>
+        <v>0.8813718124981482</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.47093186804284</v>
+        <v>4.461449384361944</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073885</v>
+        <v>3.741298518073883</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.679336924608169</v>
+        <v>-4.785381988968093</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.248001327614333</v>
+        <v>2.205583301870363</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.8971759519663094</v>
+        <v>0.8813718124981482</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.658398092951133</v>
+        <v>4.648915609270237</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.69913580090317</v>
+        <v>3.699135800903168</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.845930149721691</v>
+        <v>-4.951975214081616</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.150766988923007</v>
+        <v>2.108348963179036</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7305827268527869</v>
+        <v>0.7147785873846257</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.527845109237102</v>
+        <v>4.518362625556206</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568384</v>
+        <v>3.708202704568382</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.672865770339391</v>
+        <v>-4.778910834699316</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.223669143337644</v>
+        <v>2.181251117593674</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7305827268527869</v>
+        <v>0.7147785873846257</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.53152151189882</v>
+        <v>4.522039028217923</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682206</v>
+        <v>3.740601586682203</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.643619789883695</v>
+        <v>-4.749664854243619</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.232985590643418</v>
+        <v>2.190567564899448</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7305827268527869</v>
+        <v>0.7147785873846257</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.529139567022315</v>
+        <v>4.519657083341419</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.864221277515263</v>
+        <v>3.854020110481672</v>
       </c>
       <c r="C2056" t="n">
-        <v>4.239775435728708</v>
+        <v>4.230006750173276</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.643619789883695</v>
+        <v>-4.749664854243619</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.232985590643418</v>
+        <v>2.190567564899448</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7305827268527869</v>
+        <v>0.7147785873846257</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.232839232715076</v>
+        <v>4.223070547159644</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240814.xlsx
+++ b/tame_output/ON/bt/strategyON_20240814.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>78.5%</t>
+          <t>77.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>111.4%</t>
+          <t>97.2%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.7%</t>
+          <t>-77.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>108.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-73.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.4%</t>
+          <t>427.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-636.5%</t>
+          <t>-625.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-157.2%</t>
+          <t>-153.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-326.1%</t>
+          <t>-304.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-152.5%</t>
+          <t>-141.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>86.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>12.1%</t>
         </is>
       </c>
     </row>
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.636693222445151</v>
+        <v>-4.708535478492865</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.105348968450047</v>
+        <v>1.076612066030961</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.5364612996486477</v>
+        <v>0.4646190436009336</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.282259461531043</v>
+        <v>3.239154107902415</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.564450654273957</v>
+        <v>-4.636292910321671</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.138175309553345</v>
+        <v>1.109438407134259</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.5364612996486477</v>
+        <v>0.4646190436009336</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.286188775365864</v>
+        <v>3.243083421737235</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.546736967396091</v>
+        <v>-4.618579223443805</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.145939368221831</v>
+        <v>1.117202465802746</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.5396426285455646</v>
+        <v>0.4678003724978504</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.288776156621354</v>
+        <v>3.245670802992725</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.437932081916364</v>
+        <v>-4.509774337964078</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.186459393633715</v>
+        <v>1.15772249121463</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.5396426285455646</v>
+        <v>0.4678003724978504</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.285774227841347</v>
+        <v>3.242668874212719</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.217911283879354</v>
+        <v>-4.289753539927068</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.276046749859134</v>
+        <v>1.247309847440048</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.6808624736135448</v>
+        <v>0.6090202175658307</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.37208517189275</v>
+        <v>3.328979818264121</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.085043594816076</v>
+        <v>-4.15688585086379</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.345088008286268</v>
+        <v>1.316351105867182</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.6808624736135448</v>
+        <v>0.6090202175658307</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.387979354694573</v>
+        <v>3.344874001065945</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.964870511451577</v>
+        <v>-4.036712767499291</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.394303086072369</v>
+        <v>1.365566183653284</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.8010355569780437</v>
+        <v>0.7291933009303296</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.461229049153574</v>
+        <v>3.418123695524946</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.8296171501216</v>
+        <v>-3.901459406169314</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.4584925331658</v>
+        <v>1.429755630746715</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.9362889183080209</v>
+        <v>0.8644466622603068</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.552469168513</v>
+        <v>3.509363814884372</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.889491977479293</v>
+        <v>-3.961334233527007</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.420580093624149</v>
+        <v>1.391843191205064</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.8764140909503287</v>
+        <v>0.8045718349026146</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.502581763499811</v>
+        <v>3.459476409871182</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.769671746568455</v>
+        <v>-3.841514002616169</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.483797355222692</v>
+        <v>1.455060452803607</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.8764140909503287</v>
+        <v>0.8045718349026146</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.517870932734019</v>
+        <v>3.474765579105391</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.772141453030261</v>
+        <v>-3.843983709077975</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.390453671960412</v>
+        <v>1.361716769541326</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.8739443844885226</v>
+        <v>0.8021021284408085</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.424033308179377</v>
+        <v>3.380927954550749</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.840511639354271</v>
+        <v>-3.912353895401985</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.282367458916109</v>
+        <v>1.253630556497024</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.8832200835247376</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.348860589086407</v>
+        <v>3.305755235457779</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.854299692201318</v>
+        <v>-3.926141948249032</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.267288946409182</v>
+        <v>1.238552043990096</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.8832200835247376</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.339297297718299</v>
+        <v>3.29619194408967</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.909819768093907</v>
+        <v>-3.981662024141621</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.382111752744348</v>
+        <v>1.353374850325263</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.8832200835247376</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.476328134410501</v>
+        <v>3.433222780781873</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.734345508301438</v>
+        <v>-3.806187764349152</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.456868688653124</v>
+        <v>1.428131786234038</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.8832200835247376</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.480895366402289</v>
+        <v>3.43779001277366</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.845281760942687</v>
+        <v>-3.9171240169904</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.388236216357831</v>
+        <v>1.359499313938746</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.8832200835247376</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.456637395163496</v>
+        <v>3.413532041534868</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.811618215470405</v>
+        <v>-3.883460471518119</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.330239947948194</v>
+        <v>1.301503045529108</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.9168836289970195</v>
+        <v>0.8450413729493054</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.405373835848315</v>
+        <v>3.362268482219687</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.751765596266682</v>
+        <v>-3.823607852314395</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.364353382061815</v>
+        <v>1.33561647964273</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.9168836289970195</v>
+        <v>0.8450413729493054</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.415546222280447</v>
+        <v>3.372440868651819</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.665522133240304</v>
+        <v>-3.737364389288018</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.393797037846227</v>
+        <v>1.365060135427141</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.9168836289970195</v>
+        <v>0.8450413729493054</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.410492492854308</v>
+        <v>3.367387139225679</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.710828952639284</v>
+        <v>-3.782671208686998</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.36745008553116</v>
+        <v>1.338713183112075</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.8760734659877887</v>
+        <v>0.8042312099400746</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.377782170493295</v>
+        <v>3.334676816864667</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.739862057341586</v>
+        <v>-3.8117043133893</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.356388716683341</v>
+        <v>1.327651814264256</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.8760734659877887</v>
+        <v>0.8042312099400746</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.378334043526396</v>
+        <v>3.335228689897768</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.647051575890726</v>
+        <v>-3.71889383193844</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.322785601155051</v>
+        <v>1.294048698735965</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.968883947438648</v>
+        <v>0.8970416913909339</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.363293024288278</v>
+        <v>3.320187670659649</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.691441045220154</v>
+        <v>-3.763283301267868</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.30690328934788</v>
+        <v>1.278166386928795</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.9244944781092204</v>
+        <v>0.8526522220615063</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.338532818615222</v>
+        <v>3.295427464986593</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.807982650325497</v>
+        <v>-3.879824906373211</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.255362355817466</v>
+        <v>1.226625453398381</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.8079528730038776</v>
+        <v>0.7361106169561635</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.263683564063739</v>
+        <v>3.220578210435111</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.847906744908069</v>
+        <v>-3.919749000955782</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.244884013815105</v>
+        <v>1.216147111396019</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.8079528730038776</v>
+        <v>0.7361106169561635</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.269174859894406</v>
+        <v>3.226069506265778</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.875687142809422</v>
+        <v>-3.947529398857136</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.245269056423103</v>
+        <v>1.216532154004017</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7801724751025245</v>
+        <v>0.7083302190548104</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.264003822922134</v>
+        <v>3.220898469293505</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.99406781553956</v>
+        <v>-4.065910071587274</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.036272507331701</v>
+        <v>1.007535604912615</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.7129546229515483</v>
+        <v>0.6411123669038342</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.062028831632201</v>
+        <v>3.018923478003573</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.102681893982892</v>
+        <v>-4.174524150030605</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.112976536673574</v>
+        <v>1.084239634254488</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.7129546229515483</v>
+        <v>0.6411123669038342</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.182178492351407</v>
+        <v>3.139073138722778</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.067272855734749</v>
+        <v>-4.139115111782462</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.141653178075154</v>
+        <v>1.112916275656068</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.7129546229515483</v>
+        <v>0.6411123669038342</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.19669151845373</v>
+        <v>3.153586164825101</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.028889193176598</v>
+        <v>-4.100731449224311</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.154426084440783</v>
+        <v>1.125689182021698</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7513382855096995</v>
+        <v>0.6794960294619854</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.217141157330989</v>
+        <v>3.174035803702361</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.851772863141432</v>
+        <v>-3.923615119189145</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.222001645300151</v>
+        <v>1.193264742881066</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7513382855096995</v>
+        <v>0.6794960294619854</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.213870186176291</v>
+        <v>3.170764832547663</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.896865107974977</v>
+        <v>-3.96870736402269</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.204648139128646</v>
+        <v>1.175911236709561</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6894422423403097</v>
+        <v>0.6175999862925956</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.17741595203657</v>
+        <v>3.134310598407942</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.71748968673621</v>
+        <v>-3.789331942783923</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.270185282930568</v>
+        <v>1.241448380511482</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.8462190005110284</v>
+        <v>0.7743767444633143</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.265268982245416</v>
+        <v>3.222163628616787</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.762503900256816</v>
+        <v>-3.834346156304529</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.232987052853915</v>
+        <v>1.20425015043483</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.8158701051964238</v>
+        <v>0.7440278491487097</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.227867100388243</v>
+        <v>3.184761746759615</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.029508410529251</v>
+        <v>-4.101350666576964</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.131876811083886</v>
+        <v>1.103139908664801</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.6215070671534753</v>
+        <v>0.5496648111057612</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.11694083990142</v>
+        <v>3.073835486272791</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.130706191966424</v>
+        <v>-4.202548448014137</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.090601620405519</v>
+        <v>1.061864717986433</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5530982536081561</v>
+        <v>0.481255997560442</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.07509947367073</v>
+        <v>3.031994120042101</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.124195225352111</v>
+        <v>-4.196037481399824</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.09080596860556</v>
+        <v>1.062069066186475</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5530982536081561</v>
+        <v>0.481255997560442</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.072699435225046</v>
+        <v>3.029594081596418</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.105157097644814</v>
+        <v>-4.176999353692527</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.094945938896724</v>
+        <v>1.066209036477639</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4949146422769616</v>
+        <v>0.4230723862292474</v>
       </c>
       <c r="G1962" t="n">
-        <v>3.034313987634574</v>
+        <v>2.991208634005946</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.157672899919635</v>
+        <v>-4.229515155967348</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.193234019620987</v>
+        <v>1.164497117201901</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4949146422769616</v>
+        <v>0.4230723862292474</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.153608389268765</v>
+        <v>3.110503035640136</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.171539661253552</v>
+        <v>-4.243381917301265</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.188520644073553</v>
+        <v>1.159783741654468</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4570567255431386</v>
+        <v>0.3852144694954245</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.131726968214605</v>
+        <v>3.088621614585976</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.126735489713623</v>
+        <v>-4.198577745761336</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.212450843086451</v>
+        <v>1.183713940667366</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4570567255431386</v>
+        <v>0.3852144694954245</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.13773549861153</v>
+        <v>3.094630144982902</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.97899251947862</v>
+        <v>-4.050834775526333</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.169498252457651</v>
+        <v>1.140761350038566</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.6248640827780219</v>
+        <v>0.5530218267303076</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.13637013422966</v>
+        <v>3.093264780601031</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.062813740753318</v>
+        <v>-4.134655996801031</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.138763385479253</v>
+        <v>1.110026483060168</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.6248640827780219</v>
+        <v>0.5530218267303076</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.139163755761141</v>
+        <v>3.096058402132512</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.056661034700534</v>
+        <v>-4.128503290748247</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.141886816292025</v>
+        <v>1.11314991387294</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.6310167888308061</v>
+        <v>0.5591745327830919</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.14351772778447</v>
+        <v>3.100412374155841</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.073470332851036</v>
+        <v>-4.145312588898749</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.134243573771935</v>
+        <v>1.105506671352849</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.6142074906803046</v>
+        <v>0.5423652346325902</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.132512625634279</v>
+        <v>3.08940727200565</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.011172334074914</v>
+        <v>-4.083014590122627</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.225498327079204</v>
+        <v>1.196761424660119</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.6595017549547466</v>
+        <v>0.5876594989070323</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.226024737995765</v>
+        <v>3.182919384367136</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.809382136409756</v>
+        <v>-3.881224392457469</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.108506407859394</v>
+        <v>1.079769505440309</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.857519947123901</v>
+        <v>0.7856776910761867</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.147127655011385</v>
+        <v>3.104022301382756</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.86026884909595</v>
+        <v>-3.932111105143663</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.158441955107092</v>
+        <v>1.129705052688007</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.8066332344377065</v>
+        <v>0.7347909783899922</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.186885859721843</v>
+        <v>3.143780506093215</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.773658106446143</v>
+        <v>-3.845500362493856</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.207713988283058</v>
+        <v>1.178977085863973</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8852589656428648</v>
+        <v>0.8134167095951504</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.248689034560982</v>
+        <v>3.205583680932353</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.833867404451428</v>
+        <v>-3.905709660499141</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.182166249905616</v>
+        <v>1.153429347486531</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.8250496676375803</v>
+        <v>0.7532074115898659</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.211099436582483</v>
+        <v>3.167994082953854</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.757445358019501</v>
+        <v>-3.829287614067214</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.211226686518315</v>
+        <v>1.18248978409923</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.8250496676375803</v>
+        <v>0.7532074115898659</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.209591054622412</v>
+        <v>3.166485700993783</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.713072226380932</v>
+        <v>-3.784914482428645</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.228838806609179</v>
+        <v>1.200101904190094</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8694227992761488</v>
+        <v>0.7975805432284345</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.236077801040989</v>
+        <v>3.19297244741236</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.735552577239817</v>
+        <v>-3.80739483328753</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.214240460404216</v>
+        <v>1.185503557985131</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8694227992761488</v>
+        <v>0.7975805432284345</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.230471595179579</v>
+        <v>3.187366241550951</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.687896846678761</v>
+        <v>-3.759739102726474</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.239684509656443</v>
+        <v>1.210947607237358</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.9170785298372045</v>
+        <v>0.8452362737894902</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.265446790544018</v>
+        <v>3.222341436915389</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.587378688180006</v>
+        <v>-3.659220944227719</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.28478414643067</v>
+        <v>1.256047244011584</v>
       </c>
       <c r="F1979" t="n">
-        <v>1.017596688335959</v>
+        <v>0.9457544322882447</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.330650059017995</v>
+        <v>3.287544705389366</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.571473358747654</v>
+        <v>-3.643315614795367</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.277900950679483</v>
+        <v>1.249164048260397</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.9384840276267201</v>
+        <v>0.8666417715790058</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.269937135068324</v>
+        <v>3.226831781439695</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.526634957139256</v>
+        <v>-3.598477213186969</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.299934013933471</v>
+        <v>1.271197111514385</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.9430274605715896</v>
+        <v>0.8711852045238753</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.276760897445874</v>
+        <v>3.233655543817246</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.546133413381264</v>
+        <v>-3.617975669428977</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.296295571067745</v>
+        <v>1.26755866864866</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8949428192916853</v>
+        <v>0.823100563243971</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.25207105230901</v>
+        <v>3.208965698680381</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.501930576295364</v>
+        <v>-3.573772832343077</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.319856308429943</v>
+        <v>1.291119406010857</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.9391456563775857</v>
+        <v>0.8673034003298714</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.284472357088387</v>
+        <v>3.241367003459758</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.509490242132411</v>
+        <v>-3.581332498180124</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.315242442564371</v>
+        <v>1.286505540145286</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.993949060387405</v>
+        <v>0.9221068043396907</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.315764399963526</v>
+        <v>3.272659046334898</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.351198824593138</v>
+        <v>-3.423041080640851</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.42980677476312</v>
+        <v>1.401069872344035</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.993949060387405</v>
+        <v>0.9221068043396907</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.367012165146566</v>
+        <v>3.323906811517937</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.143556820958662</v>
+        <v>-3.215399077006375</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.511304280811163</v>
+        <v>1.482567378392078</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.201591064021881</v>
+        <v>1.129748807974167</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.490038071921505</v>
+        <v>3.446932718292876</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.092524728236134</v>
+        <v>-3.164366984283847</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.526665346138445</v>
+        <v>1.497928443719359</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.252623156744409</v>
+        <v>1.180780900696695</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.515605555793291</v>
+        <v>3.472500202164663</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.027300547108928</v>
+        <v>-3.099142803156641</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.569942422682032</v>
+        <v>1.541205520262947</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.317847337871615</v>
+        <v>1.246005081823901</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.57192746856232</v>
+        <v>3.528822114933691</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.989873527037795</v>
+        <v>-3.061715783085508</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.580874203009766</v>
+        <v>1.552137300590681</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.323098875900797</v>
+        <v>1.251256619853082</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.571039363679109</v>
+        <v>3.527934010050481</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.009985183072503</v>
+        <v>-3.081827439120216</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.574086332927123</v>
+        <v>1.545349430508038</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.334126220898216</v>
+        <v>1.262283964850502</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.578912563008801</v>
+        <v>3.535807209380172</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.956240368645298</v>
+        <v>-3.028082624693011</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.756142029719215</v>
+        <v>1.72740512730013</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.344189530338678</v>
+        <v>1.272347274290964</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.745508319694289</v>
+        <v>3.702402966065661</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.881458107620285</v>
+        <v>-2.953300363667998</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.906167843347038</v>
+        <v>1.877430940927953</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.418971791363691</v>
+        <v>1.347129535315976</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.910490585527114</v>
+        <v>3.867385231898485</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.855374023356477</v>
+        <v>-2.92721627940419</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.90830945306642</v>
+        <v>1.879572550647335</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.418971791363691</v>
+        <v>1.347129535315976</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.902198561540973</v>
+        <v>3.859093207912344</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.767496110247357</v>
+        <v>-2.83933836629507</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.941653813893848</v>
+        <v>1.912916911474762</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.534897433787042</v>
+        <v>1.463055177739327</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.969947142578762</v>
+        <v>3.926841788950134</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.758603648854073</v>
+        <v>-2.830445904901786</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.962765204177952</v>
+        <v>1.934028301758867</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.534897433787042</v>
+        <v>1.463055177739327</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.987501548305554</v>
+        <v>3.944396194676925</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.927079765823951</v>
+        <v>-2.998922021871664</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.887229804794585</v>
+        <v>1.8584929023755</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.506949598070461</v>
+        <v>1.435107342022747</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.96258789428019</v>
+        <v>3.919482540651561</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.480823573194511</v>
+        <v>-2.552665829242224</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.047001979034223</v>
+        <v>2.018265076615138</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.412230928400828</v>
+        <v>1.340388672353114</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.887026389666272</v>
+        <v>3.843921036037643</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.458102469511359</v>
+        <v>-2.529944725559072</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.046754443004389</v>
+        <v>2.018017540585303</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.412230928400828</v>
+        <v>1.340388672353114</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.877690412163177</v>
+        <v>3.834585058534548</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.587304282805401</v>
+        <v>-2.659146538853114</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.15397984353794</v>
+        <v>2.125242941118855</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.283029115106786</v>
+        <v>1.211186859059072</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.95907545003792</v>
+        <v>3.915970096409292</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.742085289583657</v>
+        <v>-2.81392754563137</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.129145263320285</v>
+        <v>2.100408360901199</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.24966144105231</v>
+        <v>1.177819185004596</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.976132668098881</v>
+        <v>3.933027314470253</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.735030599368483</v>
+        <v>-2.806872855416196</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.1286424953959</v>
+        <v>2.099905592976814</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.256716131267484</v>
+        <v>1.184873875219769</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.977040838217531</v>
+        <v>3.933935484588902</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.708079375041995</v>
+        <v>-2.779921631089708</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.149429138771236</v>
+        <v>2.120692236352151</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.271596477295203</v>
+        <v>1.199754221247489</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.995975199478903</v>
+        <v>3.952869845850275</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.844032383098312</v>
+        <v>-2.915874639146025</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.279151067693669</v>
+        <v>2.250414165274584</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.271596477295203</v>
+        <v>1.199754221247489</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.180078331623863</v>
+        <v>4.136972977995235</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.866440500903184</v>
+        <v>-2.938282756950897</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.262304515474714</v>
+        <v>2.233567613055628</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.271596477295203</v>
+        <v>1.199754221247489</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.172195026526857</v>
+        <v>4.129089672898228</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.894664736480784</v>
+        <v>-2.966506992528497</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.253068820793311</v>
+        <v>2.224331918374226</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.289573229746511</v>
+        <v>1.217730973698797</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.185035077547279</v>
+        <v>4.141929723918651</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.904105662369314</v>
+        <v>-2.975947918417027</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.305546168159746</v>
+        <v>2.276809265740661</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.412000347289903</v>
+        <v>1.340158091242189</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.314745065795162</v>
+        <v>4.271639712166532</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.956379269704955</v>
+        <v>-3.028221525752668</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.287527819770791</v>
+        <v>2.258790917351705</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.359726739954262</v>
+        <v>1.287884483906547</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.286271995939077</v>
+        <v>4.243166642310449</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.032709247305861</v>
+        <v>-3.104551503353574</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.255107641624203</v>
+        <v>2.226370739205118</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.359726739954262</v>
+        <v>1.287884483906547</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.284383808832852</v>
+        <v>4.241278455204224</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.234962967630215</v>
+        <v>-3.306805223677928</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.169026383097324</v>
+        <v>2.140289480678239</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.157473019629908</v>
+        <v>1.085630763582194</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.157851806241102</v>
+        <v>4.114746452612474</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.39653139315747</v>
+        <v>-3.468373649205183</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.102833023096575</v>
+        <v>2.074096120677489</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.030690095832029</v>
+        <v>0.9588478397843144</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.080216062172528</v>
+        <v>4.037110708543898</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.528832685255023</v>
+        <v>-3.600674941302736</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.062985913123472</v>
+        <v>2.034249010704387</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.030690095832029</v>
+        <v>0.9588478397843144</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.093289469038446</v>
+        <v>4.050184115409817</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.714700996094253</v>
+        <v>-3.786543252141966</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.98064378557072</v>
+        <v>1.951906883151635</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8721245025120812</v>
+        <v>0.8002822464643667</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.990155309829417</v>
+        <v>3.947049956200789</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.742601783203726</v>
+        <v>-3.814444039251439</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.968007511853933</v>
+        <v>1.939270609434848</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8375275783691464</v>
+        <v>0.7656853223214319</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.967921196470659</v>
+        <v>3.92481584284203</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.86512788590662</v>
+        <v>-3.936970141954333</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.915761514749974</v>
+        <v>1.887024612330889</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7150014756662525</v>
+        <v>0.6431592196185381</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.891169978826121</v>
+        <v>3.848064625197492</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.095642382092208</v>
+        <v>-4.167484638139921</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.890261675866242</v>
+        <v>1.861524773447157</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4844869794806638</v>
+        <v>0.4126447234329493</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.819567240705271</v>
+        <v>3.776461887076643</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.352363200087032</v>
+        <v>-4.424205456134745</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.92788506767016</v>
+        <v>1.899148165251075</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3760724053368489</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.894830215220829</v>
+        <v>3.851724861592201</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.506349617863172</v>
+        <v>-4.578191873910885</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.935270769705344</v>
+        <v>1.906533867286258</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3760724053368489</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.963810484366469</v>
+        <v>3.920705130737841</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.455827714035506</v>
+        <v>-4.527669970083219</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.941530733356531</v>
+        <v>1.912793830937445</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3760724053368489</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.949861686486591</v>
+        <v>3.906756332857962</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.708302868043231</v>
+        <v>-4.780145124090944</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.852411160808855</v>
+        <v>1.82367425838977</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3760724053368489</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.961732175542005</v>
+        <v>3.918626821913375</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.001198624522643</v>
+        <v>-5.073040880570356</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.736463392736034</v>
+        <v>1.707726490316948</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3760724053368489</v>
+        <v>0.3042301492891345</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.962942710060948</v>
+        <v>3.919837356432319</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.158742696252085</v>
+        <v>-5.230584952299798</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.677567506271579</v>
+        <v>1.648830603852494</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3091706001965744</v>
+        <v>0.23732834414886</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.926923369204105</v>
+        <v>3.883818015575476</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.436707091835358</v>
+        <v>-5.508549347883071</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.561459600774459</v>
+        <v>1.532722698355373</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2195508659110902</v>
+        <v>0.1477086098633758</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.868229381369003</v>
+        <v>3.825124027740375</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.553674784474249</v>
+        <v>-5.625517040521962</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.676876580417946</v>
+        <v>1.648139677998861</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2195508659110902</v>
+        <v>0.1477086098633758</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.030433438068048</v>
+        <v>3.987328084439419</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.638392726695202</v>
+        <v>-5.710234982742915</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.637836041493379</v>
+        <v>1.609099139074294</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1344348369830438</v>
+        <v>0.06259258093532938</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.974210458675034</v>
+        <v>3.931105105046405</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.720327544964086</v>
+        <v>-5.792169801011799</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.615291531754317</v>
+        <v>1.586554629335232</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1245000913959636</v>
+        <v>0.05265783534824919</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.978479028891277</v>
+        <v>3.935373675262649</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.822303667212493</v>
+        <v>-5.894145923260206</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.583426721310857</v>
+        <v>1.554689818891771</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.02252396914755606</v>
+        <v>-0.04931828690015838</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.926218993998135</v>
+        <v>3.883113640369506</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.712297383735272</v>
+        <v>-5.784139639782985</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.61958212194592</v>
+        <v>1.590845219526835</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.04572854106483126</v>
+        <v>-0.02611371498288317</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.932294624392675</v>
+        <v>3.889189270764047</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.569237807994346</v>
+        <v>-5.641080064042059</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.681055962964265</v>
+        <v>1.65231906054518</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.05374196765481054</v>
+        <v>-0.0181002883929039</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.941352691068637</v>
+        <v>3.898247337440008</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.267791082522509</v>
+        <v>-5.339633338570222</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.808895536035536</v>
+        <v>1.780158633616451</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3551886931266478</v>
+        <v>0.2833464370789334</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.129481609234276</v>
+        <v>4.086376255605647</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.292381326757693</v>
+        <v>-5.364223582805406</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.800030616094173</v>
+        <v>1.771293713675088</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3551886931266478</v>
+        <v>0.2833464370789334</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.130452786986986</v>
+        <v>4.087347433358357</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.241342950751172</v>
+        <v>-5.313185206798885</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.821288870876536</v>
+        <v>1.792551968457451</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3551886931266478</v>
+        <v>0.2833464370789334</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.131295691366741</v>
+        <v>4.088190337738113</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.200203655884541</v>
+        <v>-5.272045911932254</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.856782687697334</v>
+        <v>1.828045785278249</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3963279879932786</v>
+        <v>0.3244857319455642</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.175017367160866</v>
+        <v>4.131912013532236</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.08959751580494</v>
+        <v>-5.161439771852653</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.717209139853109</v>
+        <v>1.688472237434024</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5069341280728806</v>
+        <v>0.4350918720251662</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.057565047332561</v>
+        <v>4.014459693703932</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.220178250335782</v>
+        <v>-5.292020506383495</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.668478890114736</v>
+        <v>1.639741987695651</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3763533935420381</v>
+        <v>0.3045111374943237</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.982718650688019</v>
+        <v>3.939613297059391</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.05568191614482</v>
+        <v>-5.127524172192533</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.718704242867203</v>
+        <v>1.689967340448118</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3763533935420381</v>
+        <v>0.3045111374943237</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.967145469764102</v>
+        <v>3.924040116135473</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.083051848829252</v>
+        <v>-5.154894104876965</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.70694398022986</v>
+        <v>1.678207077810775</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3763533935420381</v>
+        <v>0.3045111374943237</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.966333180200531</v>
+        <v>3.923227826571903</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.093437043719142</v>
+        <v>-5.165279299766855</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.712658681398977</v>
+        <v>1.683921778979891</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3659681986521488</v>
+        <v>0.2941259426044344</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.96997084239167</v>
+        <v>3.926865488763042</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.112025202441367</v>
+        <v>-5.18386745848908</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.776060423686512</v>
+        <v>1.747323521267427</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.3473800399299234</v>
+        <v>0.275537783882209</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.02965495293476</v>
+        <v>3.986549599306132</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.112323749137403</v>
+        <v>-5.184166005185116</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.772810015826396</v>
+        <v>1.744073113407311</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.3473800399299234</v>
+        <v>0.275537783882209</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.026523963753059</v>
+        <v>3.98341861012443</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.011500615446975</v>
+        <v>-5.083342871494688</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.817670164241958</v>
+        <v>1.788933261822873</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.3598442554142773</v>
+        <v>0.2880019993665628</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.038533387983063</v>
+        <v>3.995428034354433</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.820719254694568</v>
+        <v>-4.892561510742281</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.894111962021465</v>
+        <v>1.865375059602379</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.5506256161666847</v>
+        <v>0.4787833601189702</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.15313145791305</v>
+        <v>4.110026104284421</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.802202400652748</v>
+        <v>-4.874044656700461</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.881355549375789</v>
+        <v>1.852618646956704</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5635557455918929</v>
+        <v>0.4917134895441784</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.140726381305772</v>
+        <v>4.097621027677143</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.77700921615143</v>
+        <v>-4.848851472199143</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.926399759788375</v>
+        <v>1.89766285736929</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.5887489300932113</v>
+        <v>0.5169066740454967</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.190809228618621</v>
+        <v>4.147703874989992</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.764955089238467</v>
+        <v>-4.83679734528618</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.924907978454998</v>
+        <v>1.896171076035913</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6008030570061741</v>
+        <v>0.5289608009584595</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.191728272667836</v>
+        <v>4.148622919039208</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.771578335928825</v>
+        <v>-4.843420591976538</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.924139309962991</v>
+        <v>1.895402407543905</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5941798103158158</v>
+        <v>0.5223375542681012</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.189634954837757</v>
+        <v>4.146529601209129</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.668697746400232</v>
+        <v>-4.740540002447945</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.97814257165231</v>
+        <v>1.949405669233225</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6970603998444087</v>
+        <v>0.6252181437966942</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.264214334432795</v>
+        <v>4.221108980804167</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.692139785580319</v>
+        <v>-4.763982041628032</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.988968426153869</v>
+        <v>1.960231523734784</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6970603998444087</v>
+        <v>0.6252181437966942</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.284417004606389</v>
+        <v>4.241311650977761</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.710212293871931</v>
+        <v>-4.782054549919644</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.981739422837225</v>
+        <v>1.953002520418139</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6970603998444087</v>
+        <v>0.6252181437966942</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.284417004606389</v>
+        <v>4.241311650977761</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.941386087748563</v>
+        <v>-5.013228343796276</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.849521818880039</v>
+        <v>1.820784916460954</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6970603998444087</v>
+        <v>0.6252181437966942</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.244668918199856</v>
+        <v>4.201563564571228</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.910100067208107</v>
+        <v>-4.98194232325582</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.869058846093161</v>
+        <v>1.840321943674076</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.7283464203848641</v>
+        <v>0.6565041643371495</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.27046314952107</v>
+        <v>4.227357795892441</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.757074675094823</v>
+        <v>-4.828916931142536</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.029440002511379</v>
+        <v>2.000703100092293</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.8813718124981482</v>
+        <v>0.8095295564504337</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.461449384361944</v>
+        <v>4.418344030733316</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.785381988968093</v>
+        <v>-4.857224245015806</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.205583301870363</v>
+        <v>2.176846399451278</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.8813718124981482</v>
+        <v>0.8095295564504337</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.648915609270237</v>
+        <v>4.605810255641608</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.951975214081616</v>
+        <v>-5.023817470129329</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.108348963179036</v>
+        <v>2.079612060759951</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7147785873846257</v>
+        <v>0.6429363313369112</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.518362625556206</v>
+        <v>4.475257271927576</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.778910834699316</v>
+        <v>-4.850753090747029</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.181251117593674</v>
+        <v>2.152514215174589</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7147785873846257</v>
+        <v>0.6429363313369112</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.522039028217923</v>
+        <v>4.478933674589294</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.749664854243619</v>
+        <v>-4.821507110291332</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.190567564899448</v>
+        <v>2.161830662480363</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7147785873846257</v>
+        <v>0.6429363313369112</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.519657083341419</v>
+        <v>4.476551729712789</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.854020110481672</v>
+        <v>3.446247247433312</v>
       </c>
       <c r="C2056" t="n">
-        <v>4.230006750173276</v>
+        <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.749664854243619</v>
+        <v>-4.643255210174052</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.190567564899448</v>
+        <v>2.23042466168491</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7147785873846257</v>
+        <v>0.8211882314541905</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.223070547159644</v>
+        <v>4.580796108940793</v>
       </c>
     </row>
   </sheetData>
